--- a/resources/variable_schema_data_individual_nutrition_template.xlsx
+++ b/resources/variable_schema_data_individual_nutrition_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CF1C4D9-DBCE-48F8-98CD-872B4624DA1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68016751-6CD7-4916-AC73-283DB21F97B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="495" yWindow="2925" windowWidth="13815" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1216" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="302">
   <si>
     <t>rule_type</t>
   </si>
@@ -854,6 +854,78 @@
   </si>
   <si>
     <t>nut_mfaz</t>
+  </si>
+  <si>
+    <t>nut_ecfies_cat</t>
+  </si>
+  <si>
+    <t>nut_ecfies_score</t>
+  </si>
+  <si>
+    <t>mild</t>
+  </si>
+  <si>
+    <t>moderate</t>
+  </si>
+  <si>
+    <t>severe</t>
+  </si>
+  <si>
+    <t>none,⧫No Food Insecurity⧫</t>
+  </si>
+  <si>
+    <t>mild,⧫Mild Food Insecurity⧫</t>
+  </si>
+  <si>
+    <t>moderate,⧫Moderate Food Insecurity⧫</t>
+  </si>
+  <si>
+    <t>severe,⧫Severe Food Insecurity⧫</t>
+  </si>
+  <si>
+    <t>Early Childhood Food Insecurity Score (ECFIES)</t>
+  </si>
+  <si>
+    <t>Indice d'insécurité alimentaire chez les jeunes enfants (ECFIES)</t>
+  </si>
+  <si>
+    <t>مؤشر انعدام الأمن الغذائي في مرحلة الطفولة المبكرة (ECFIES)</t>
+  </si>
+  <si>
+    <t>No food insecurity</t>
+  </si>
+  <si>
+    <t>Mild food insecurity</t>
+  </si>
+  <si>
+    <t>Moderate food insecurity</t>
+  </si>
+  <si>
+    <t>Severe food insecurity</t>
+  </si>
+  <si>
+    <t>لا يوجد انعدام للأمن الغذائي</t>
+  </si>
+  <si>
+    <t>انعدام خفيف للأمن الغذائي</t>
+  </si>
+  <si>
+    <t>انعدام متوسط للأمن الغذائي</t>
+  </si>
+  <si>
+    <t>انعدام حاد للأمن الغذائي</t>
+  </si>
+  <si>
+    <t>Pas d'insécurité alimentaire</t>
+  </si>
+  <si>
+    <t>Insécurité alimentaire légère</t>
+  </si>
+  <si>
+    <t>Insécurité alimentaire modérée</t>
+  </si>
+  <si>
+    <t>Insécurité alimentaire grave</t>
   </si>
 </sst>
 </file>
@@ -895,7 +967,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="42">
+  <dxfs count="43">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1614,13 +1696,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S100"/>
+  <dimension ref="A1:S105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
     <col min="5" max="5" width="13.7109375" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -5349,6 +5432,9 @@
       <c r="I95" t="s">
         <v>254</v>
       </c>
+      <c r="J95" t="s">
+        <v>253</v>
+      </c>
       <c r="L95" t="s">
         <v>255</v>
       </c>
@@ -5375,6 +5461,9 @@
       <c r="I96" t="s">
         <v>254</v>
       </c>
+      <c r="J96" t="s">
+        <v>258</v>
+      </c>
       <c r="L96" t="s">
         <v>259</v>
       </c>
@@ -5385,7 +5474,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>1</v>
       </c>
@@ -5401,6 +5490,9 @@
       <c r="I97" t="s">
         <v>254</v>
       </c>
+      <c r="J97" t="s">
+        <v>262</v>
+      </c>
       <c r="L97" t="s">
         <v>263</v>
       </c>
@@ -5411,7 +5503,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>1</v>
       </c>
@@ -5427,6 +5519,9 @@
       <c r="I98" t="s">
         <v>254</v>
       </c>
+      <c r="J98" t="s">
+        <v>265</v>
+      </c>
       <c r="L98" t="s">
         <v>266</v>
       </c>
@@ -5437,7 +5532,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>1</v>
       </c>
@@ -5453,6 +5548,9 @@
       <c r="I99" t="s">
         <v>254</v>
       </c>
+      <c r="J99" t="s">
+        <v>269</v>
+      </c>
       <c r="L99" t="s">
         <v>270</v>
       </c>
@@ -5463,7 +5561,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>1</v>
       </c>
@@ -5479,6 +5577,9 @@
       <c r="I100" t="s">
         <v>254</v>
       </c>
+      <c r="J100" t="s">
+        <v>273</v>
+      </c>
       <c r="L100" t="s">
         <v>274</v>
       </c>
@@ -5489,134 +5590,321 @@
         <v>276</v>
       </c>
     </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1</v>
+      </c>
+      <c r="B101" t="s">
+        <v>278</v>
+      </c>
+      <c r="C101" t="s">
+        <v>101</v>
+      </c>
+      <c r="E101" t="s">
+        <v>20</v>
+      </c>
+      <c r="F101" t="s">
+        <v>54</v>
+      </c>
+      <c r="I101" t="s">
+        <v>283</v>
+      </c>
+      <c r="J101" t="s">
+        <v>278</v>
+      </c>
+      <c r="L101" t="s">
+        <v>287</v>
+      </c>
+      <c r="M101" t="s">
+        <v>288</v>
+      </c>
+      <c r="N101" t="s">
+        <v>289</v>
+      </c>
+      <c r="O101" t="s">
+        <v>290</v>
+      </c>
+      <c r="P101" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1</v>
+      </c>
+      <c r="B102" t="s">
+        <v>278</v>
+      </c>
+      <c r="C102" t="s">
+        <v>280</v>
+      </c>
+      <c r="E102" t="s">
+        <v>20</v>
+      </c>
+      <c r="F102" t="s">
+        <v>54</v>
+      </c>
+      <c r="I102" t="s">
+        <v>284</v>
+      </c>
+      <c r="J102" t="s">
+        <v>278</v>
+      </c>
+      <c r="L102" t="s">
+        <v>287</v>
+      </c>
+      <c r="M102" t="s">
+        <v>288</v>
+      </c>
+      <c r="N102" t="s">
+        <v>289</v>
+      </c>
+      <c r="O102" t="s">
+        <v>291</v>
+      </c>
+      <c r="P102" t="s">
+        <v>299</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1</v>
+      </c>
+      <c r="B103" t="s">
+        <v>278</v>
+      </c>
+      <c r="C103" t="s">
+        <v>281</v>
+      </c>
+      <c r="E103" t="s">
+        <v>20</v>
+      </c>
+      <c r="F103" t="s">
+        <v>54</v>
+      </c>
+      <c r="I103" t="s">
+        <v>285</v>
+      </c>
+      <c r="J103" t="s">
+        <v>278</v>
+      </c>
+      <c r="L103" t="s">
+        <v>287</v>
+      </c>
+      <c r="M103" t="s">
+        <v>288</v>
+      </c>
+      <c r="N103" t="s">
+        <v>289</v>
+      </c>
+      <c r="O103" t="s">
+        <v>292</v>
+      </c>
+      <c r="P103" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1</v>
+      </c>
+      <c r="B104" t="s">
+        <v>278</v>
+      </c>
+      <c r="C104" t="s">
+        <v>282</v>
+      </c>
+      <c r="E104" t="s">
+        <v>20</v>
+      </c>
+      <c r="F104" t="s">
+        <v>54</v>
+      </c>
+      <c r="I104" t="s">
+        <v>286</v>
+      </c>
+      <c r="J104" t="s">
+        <v>278</v>
+      </c>
+      <c r="L104" t="s">
+        <v>287</v>
+      </c>
+      <c r="M104" t="s">
+        <v>288</v>
+      </c>
+      <c r="N104" t="s">
+        <v>289</v>
+      </c>
+      <c r="O104" t="s">
+        <v>293</v>
+      </c>
+      <c r="P104" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1</v>
+      </c>
+      <c r="B105" t="s">
+        <v>279</v>
+      </c>
+      <c r="E105" t="s">
+        <v>47</v>
+      </c>
+      <c r="F105" t="s">
+        <v>54</v>
+      </c>
+      <c r="I105" t="s">
+        <v>254</v>
+      </c>
+      <c r="L105" t="s">
+        <v>287</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B9:B11 B14">
-    <cfRule type="duplicateValues" dxfId="41" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26">
+    <cfRule type="duplicateValues" dxfId="40" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B27">
     <cfRule type="duplicateValues" dxfId="39" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27">
+  <conditionalFormatting sqref="B28">
     <cfRule type="duplicateValues" dxfId="38" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B29:B39">
     <cfRule type="duplicateValues" dxfId="37" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29:B39">
-    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
+  <conditionalFormatting sqref="B40">
+    <cfRule type="duplicateValues" dxfId="36" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B40">
-    <cfRule type="duplicateValues" dxfId="35" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41:B51 B93:B141">
-    <cfRule type="duplicateValues" dxfId="34" priority="26"/>
+  <conditionalFormatting sqref="B41:B51 B93:B144">
+    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B52:B61">
+    <cfRule type="duplicateValues" dxfId="34" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B62">
     <cfRule type="duplicateValues" dxfId="33" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="32" priority="19"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B63:B94">
-    <cfRule type="duplicateValues" dxfId="31" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:C11">
-    <cfRule type="duplicateValues" dxfId="30" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C19:C23">
-    <cfRule type="duplicateValues" dxfId="29" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C29:C39">
-    <cfRule type="duplicateValues" dxfId="28" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C49:C50">
-    <cfRule type="duplicateValues" dxfId="27" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C52:C61">
-    <cfRule type="duplicateValues" dxfId="26" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="25" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H51:H61 H63:H141">
-    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
+  <conditionalFormatting sqref="H51:H61 H63:H144">
+    <cfRule type="duplicateValues" dxfId="25" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H62">
-    <cfRule type="duplicateValues" dxfId="23" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I20:I22">
-    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I29:I39">
-    <cfRule type="duplicateValues" dxfId="21" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I50">
-    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I52:I59 I61">
-    <cfRule type="duplicateValues" dxfId="19" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I60">
-    <cfRule type="duplicateValues" dxfId="18" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I66">
+    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I70">
     <cfRule type="duplicateValues" dxfId="17" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I70">
+  <conditionalFormatting sqref="I74">
     <cfRule type="duplicateValues" dxfId="16" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I74">
+  <conditionalFormatting sqref="I78">
     <cfRule type="duplicateValues" dxfId="15" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I78">
+  <conditionalFormatting sqref="I82">
     <cfRule type="duplicateValues" dxfId="14" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I82">
+  <conditionalFormatting sqref="I86">
     <cfRule type="duplicateValues" dxfId="13" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I86">
+  <conditionalFormatting sqref="I90">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I90">
-    <cfRule type="duplicateValues" dxfId="11" priority="5"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I94">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J26">
+    <cfRule type="duplicateValues" dxfId="10" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J27">
     <cfRule type="duplicateValues" dxfId="9" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J27">
+  <conditionalFormatting sqref="J28">
     <cfRule type="duplicateValues" dxfId="8" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
-    <cfRule type="duplicateValues" dxfId="7" priority="28"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="J29:J39">
-    <cfRule type="duplicateValues" dxfId="6" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J41:J50">
-    <cfRule type="duplicateValues" dxfId="5" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J51 J95:J141">
-    <cfRule type="duplicateValues" dxfId="4" priority="22"/>
+  <conditionalFormatting sqref="J51 J105:J144">
+    <cfRule type="duplicateValues" dxfId="5" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J52:J61">
-    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J62">
-    <cfRule type="duplicateValues" dxfId="2" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J63:J94">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J93:J94">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J95:J104">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/resources/variable_schema_data_individual_nutrition_template.xlsx
+++ b/resources/variable_schema_data_individual_nutrition_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68016751-6CD7-4916-AC73-283DB21F97B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F493A87F-B5FB-477E-8121-01D91F25F4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="328">
   <si>
     <t>rule_type</t>
   </si>
@@ -926,6 +926,84 @@
   </si>
   <si>
     <t>Insécurité alimentaire grave</t>
+  </si>
+  <si>
+    <t>nut_muac_cat</t>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>sam</t>
+  </si>
+  <si>
+    <t>mam</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>normal,Normal,⧫Normal⧫</t>
+  </si>
+  <si>
+    <t>mam,MAM,⧫MAM⧫</t>
+  </si>
+  <si>
+    <t>sam,SAM,⧫SAM⧫</t>
+  </si>
+  <si>
+    <t>Nutritional Status (MUAC)</t>
+  </si>
+  <si>
+    <t>État nutritionnel (circonférence brachiale)</t>
+  </si>
+  <si>
+    <t>الحالة التغذوية (محيط الذراع عند الكوع)</t>
+  </si>
+  <si>
+    <t>Moderate Acute Malnutrition</t>
+  </si>
+  <si>
+    <t>Severe Acute Malnutrition</t>
+  </si>
+  <si>
+    <t>عادي</t>
+  </si>
+  <si>
+    <t>سوء التغذية الحاد المعتدل</t>
+  </si>
+  <si>
+    <t>سوء التغذية الحاد الشديد</t>
+  </si>
+  <si>
+    <t>Malnutrition aiguë modérée</t>
+  </si>
+  <si>
+    <t>Malnutrition aiguë sévère</t>
+  </si>
+  <si>
+    <t>num_children_6_29m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linked Roster children 6-29 months </t>
+  </si>
+  <si>
+    <t xml:space="preserve">قائمة الأطفال المرتبطين من عمر 6 إلى 29 شهراً </t>
+  </si>
+  <si>
+    <t>num_children_30_59m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linked Roster children 30-59 months </t>
+  </si>
+  <si>
+    <t>قائمة الأطفال المرتبطين من عمر 30 إلى 59 شهر</t>
+  </si>
+  <si>
+    <t>roster_age_6_29m,age_6_29m</t>
+  </si>
+  <si>
+    <t>roster_age_30_59m,age_30_59m</t>
   </si>
 </sst>
 </file>
@@ -967,7 +1045,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="43">
+  <dxfs count="44">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1696,7 +1784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S105"/>
+  <dimension ref="A1:S110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
@@ -1991,37 +2079,28 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
+        <v>320</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>66</v>
+        <v>326</v>
       </c>
       <c r="L9" t="s">
-        <v>67</v>
+        <v>321</v>
       </c>
       <c r="M9" t="s">
-        <v>68</v>
+        <v>321</v>
       </c>
       <c r="N9" t="s">
-        <v>69</v>
-      </c>
-      <c r="O9" t="s">
-        <v>70</v>
-      </c>
-      <c r="P9" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>72</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2029,37 +2108,28 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" t="s">
-        <v>73</v>
+        <v>323</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>66</v>
+        <v>327</v>
       </c>
       <c r="L10" t="s">
-        <v>67</v>
+        <v>324</v>
       </c>
       <c r="M10" t="s">
-        <v>68</v>
+        <v>324</v>
       </c>
       <c r="N10" t="s">
-        <v>69</v>
-      </c>
-      <c r="O10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P10" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>76</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -2070,7 +2140,7 @@
         <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
@@ -2091,13 +2161,13 @@
         <v>69</v>
       </c>
       <c r="O11" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="P11" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="Q11" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -2105,25 +2175,37 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>64</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="L12" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="M12" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="N12" t="s">
-        <v>85</v>
+        <v>69</v>
+      </c>
+      <c r="O12" t="s">
+        <v>74</v>
+      </c>
+      <c r="P12" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -2131,25 +2213,37 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="L13" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="M13" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="N13" t="s">
-        <v>89</v>
+        <v>69</v>
+      </c>
+      <c r="O13" t="s">
+        <v>78</v>
+      </c>
+      <c r="P13" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -2157,13 +2251,25 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>277</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
         <v>47</v>
       </c>
       <c r="F14" t="s">
-        <v>54</v>
+        <v>82</v>
+      </c>
+      <c r="J14" t="s">
+        <v>83</v>
+      </c>
+      <c r="L14" t="s">
+        <v>84</v>
+      </c>
+      <c r="M14" t="s">
+        <v>84</v>
+      </c>
+      <c r="N14" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -2171,40 +2277,25 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C15" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="J15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M15" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="N15" t="s">
-        <v>94</v>
-      </c>
-      <c r="O15" t="s">
-        <v>70</v>
-      </c>
-      <c r="P15" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -2212,40 +2303,13 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" t="s">
-        <v>73</v>
+        <v>277</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" t="s">
-        <v>95</v>
-      </c>
-      <c r="J16" t="s">
-        <v>90</v>
-      </c>
-      <c r="L16" t="s">
-        <v>92</v>
-      </c>
-      <c r="M16" t="s">
-        <v>93</v>
-      </c>
-      <c r="N16" t="s">
-        <v>94</v>
-      </c>
-      <c r="O16" t="s">
-        <v>74</v>
-      </c>
-      <c r="P16" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -2253,7 +2317,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
         <v>65</v>
@@ -2268,16 +2332,16 @@
         <v>91</v>
       </c>
       <c r="J17" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="L17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="M17" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="N17" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="O17" t="s">
         <v>70</v>
@@ -2294,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
         <v>73</v>
@@ -2309,16 +2373,16 @@
         <v>95</v>
       </c>
       <c r="J18" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="L18" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="M18" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="N18" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="O18" t="s">
         <v>74</v>
@@ -2335,10 +2399,10 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="E19" t="s">
         <v>20</v>
@@ -2347,28 +2411,28 @@
         <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L19" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="M19" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="N19" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O19" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="P19" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="Q19" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -2376,10 +2440,10 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
         <v>20</v>
@@ -2388,28 +2452,28 @@
         <v>32</v>
       </c>
       <c r="I20" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="J20" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L20" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="M20" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="N20" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O20" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="P20" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="Q20" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -2420,7 +2484,7 @@
         <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="E21" t="s">
         <v>20</v>
@@ -2429,7 +2493,7 @@
         <v>32</v>
       </c>
       <c r="I21" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="J21" t="s">
         <v>100</v>
@@ -2444,13 +2508,13 @@
         <v>105</v>
       </c>
       <c r="O21" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="P21" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="Q21" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -2461,7 +2525,7 @@
         <v>100</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
         <v>20</v>
@@ -2470,7 +2534,7 @@
         <v>32</v>
       </c>
       <c r="I22" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="J22" t="s">
         <v>100</v>
@@ -2485,13 +2549,13 @@
         <v>105</v>
       </c>
       <c r="O22" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="P22" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="Q22" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -2502,7 +2566,7 @@
         <v>100</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E23" t="s">
         <v>20</v>
@@ -2511,7 +2575,7 @@
         <v>32</v>
       </c>
       <c r="I23" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="J23" t="s">
         <v>100</v>
@@ -2526,13 +2590,13 @@
         <v>105</v>
       </c>
       <c r="O23" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="P23" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -2540,10 +2604,10 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C24" t="s">
-        <v>65</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
         <v>20</v>
@@ -2552,28 +2616,28 @@
         <v>32</v>
       </c>
       <c r="I24" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="J24" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="L24" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="M24" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="N24" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="O24" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="P24" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="Q24" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -2581,10 +2645,10 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
       <c r="E25" t="s">
         <v>20</v>
@@ -2593,28 +2657,28 @@
         <v>32</v>
       </c>
       <c r="I25" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="J25" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="L25" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="M25" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="N25" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="O25" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="P25" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="Q25" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -2622,7 +2686,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C26" t="s">
         <v>65</v>
@@ -2637,16 +2701,16 @@
         <v>91</v>
       </c>
       <c r="J26" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L26" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M26" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N26" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O26" t="s">
         <v>70</v>
@@ -2663,7 +2727,7 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C27" t="s">
         <v>73</v>
@@ -2678,16 +2742,16 @@
         <v>95</v>
       </c>
       <c r="J27" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L27" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M27" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N27" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O27" t="s">
         <v>74</v>
@@ -2707,7 +2771,7 @@
         <v>130</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -2716,7 +2780,7 @@
         <v>32</v>
       </c>
       <c r="I28" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J28" t="s">
         <v>130</v>
@@ -2731,13 +2795,13 @@
         <v>133</v>
       </c>
       <c r="O28" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="P28" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Q28" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -2745,40 +2809,40 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C29" t="s">
-        <v>136</v>
+        <v>73</v>
       </c>
       <c r="E29" t="s">
         <v>20</v>
       </c>
       <c r="F29" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I29" t="s">
-        <v>136</v>
+        <v>95</v>
       </c>
       <c r="J29" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L29" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M29" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N29" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O29" t="s">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="P29" t="s">
-        <v>142</v>
+        <v>75</v>
       </c>
       <c r="Q29" t="s">
-        <v>142</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -2786,40 +2850,40 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C30" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E30" t="s">
         <v>20</v>
       </c>
       <c r="F30" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I30" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="J30" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L30" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M30" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N30" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O30" t="s">
-        <v>144</v>
+        <v>123</v>
       </c>
       <c r="P30" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="Q30" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -2830,7 +2894,7 @@
         <v>135</v>
       </c>
       <c r="C31" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E31" t="s">
         <v>20</v>
@@ -2839,7 +2903,7 @@
         <v>137</v>
       </c>
       <c r="I31" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="J31" t="s">
         <v>138</v>
@@ -2854,13 +2918,13 @@
         <v>141</v>
       </c>
       <c r="O31" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="P31" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="Q31" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -2871,7 +2935,7 @@
         <v>135</v>
       </c>
       <c r="C32" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E32" t="s">
         <v>20</v>
@@ -2880,7 +2944,7 @@
         <v>137</v>
       </c>
       <c r="I32" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="J32" t="s">
         <v>138</v>
@@ -2895,13 +2959,13 @@
         <v>141</v>
       </c>
       <c r="O32" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="P32" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="Q32" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -2912,7 +2976,7 @@
         <v>135</v>
       </c>
       <c r="C33" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E33" t="s">
         <v>20</v>
@@ -2921,7 +2985,7 @@
         <v>137</v>
       </c>
       <c r="I33" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="J33" t="s">
         <v>138</v>
@@ -2936,13 +3000,13 @@
         <v>141</v>
       </c>
       <c r="O33" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="P33" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="Q33" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -2953,7 +3017,7 @@
         <v>135</v>
       </c>
       <c r="C34" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E34" t="s">
         <v>20</v>
@@ -2962,7 +3026,7 @@
         <v>137</v>
       </c>
       <c r="I34" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="J34" t="s">
         <v>138</v>
@@ -2977,13 +3041,13 @@
         <v>141</v>
       </c>
       <c r="O34" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="P34" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="Q34" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -2994,7 +3058,7 @@
         <v>135</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E35" t="s">
         <v>20</v>
@@ -3003,7 +3067,7 @@
         <v>137</v>
       </c>
       <c r="I35" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="J35" t="s">
         <v>138</v>
@@ -3018,13 +3082,13 @@
         <v>141</v>
       </c>
       <c r="O35" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="P35" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="Q35" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -3035,7 +3099,7 @@
         <v>135</v>
       </c>
       <c r="C36" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E36" t="s">
         <v>20</v>
@@ -3044,7 +3108,7 @@
         <v>137</v>
       </c>
       <c r="I36" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="J36" t="s">
         <v>138</v>
@@ -3059,13 +3123,13 @@
         <v>141</v>
       </c>
       <c r="O36" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="P36" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="Q36" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -3076,7 +3140,7 @@
         <v>135</v>
       </c>
       <c r="C37" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E37" t="s">
         <v>20</v>
@@ -3085,7 +3149,7 @@
         <v>137</v>
       </c>
       <c r="I37" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="J37" t="s">
         <v>138</v>
@@ -3100,13 +3164,13 @@
         <v>141</v>
       </c>
       <c r="O37" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="P37" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="Q37" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -3117,7 +3181,7 @@
         <v>135</v>
       </c>
       <c r="C38" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E38" t="s">
         <v>20</v>
@@ -3126,7 +3190,7 @@
         <v>137</v>
       </c>
       <c r="I38" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="J38" t="s">
         <v>138</v>
@@ -3141,13 +3205,13 @@
         <v>141</v>
       </c>
       <c r="O38" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="P38" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="Q38" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -3158,7 +3222,7 @@
         <v>135</v>
       </c>
       <c r="C39" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E39" t="s">
         <v>20</v>
@@ -3167,7 +3231,7 @@
         <v>137</v>
       </c>
       <c r="I39" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="J39" t="s">
         <v>138</v>
@@ -3182,13 +3246,13 @@
         <v>141</v>
       </c>
       <c r="O39" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="P39" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="Q39" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -3196,28 +3260,40 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>135</v>
+      </c>
+      <c r="C40" t="s">
+        <v>159</v>
       </c>
       <c r="E40" t="s">
         <v>20</v>
       </c>
       <c r="F40" t="s">
-        <v>168</v>
-      </c>
-      <c r="G40" t="b">
-        <v>1</v>
-      </c>
-      <c r="H40" t="s">
-        <v>135</v>
+        <v>137</v>
+      </c>
+      <c r="I40" t="s">
+        <v>159</v>
+      </c>
+      <c r="J40" t="s">
+        <v>138</v>
       </c>
       <c r="L40" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M40" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="N40" t="s">
-        <v>171</v>
+        <v>141</v>
+      </c>
+      <c r="O40" t="s">
+        <v>160</v>
+      </c>
+      <c r="P40" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -3225,10 +3301,10 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="C41" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E41" t="s">
         <v>20</v>
@@ -3237,28 +3313,28 @@
         <v>137</v>
       </c>
       <c r="I41" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="J41" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="L41" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="M41" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="N41" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="O41" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="P41" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="Q41" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -3266,40 +3342,28 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>172</v>
-      </c>
-      <c r="C42" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="E42" t="s">
         <v>20</v>
       </c>
       <c r="F42" t="s">
-        <v>137</v>
-      </c>
-      <c r="I42" t="s">
-        <v>181</v>
-      </c>
-      <c r="J42" t="s">
-        <v>175</v>
+        <v>168</v>
+      </c>
+      <c r="G42" t="b">
+        <v>1</v>
+      </c>
+      <c r="H42" t="s">
+        <v>135</v>
       </c>
       <c r="L42" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="M42" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N42" t="s">
-        <v>178</v>
-      </c>
-      <c r="O42" t="s">
-        <v>182</v>
-      </c>
-      <c r="P42" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -3310,7 +3374,7 @@
         <v>172</v>
       </c>
       <c r="C43" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E43" t="s">
         <v>20</v>
@@ -3319,7 +3383,7 @@
         <v>137</v>
       </c>
       <c r="I43" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="J43" t="s">
         <v>175</v>
@@ -3334,13 +3398,13 @@
         <v>178</v>
       </c>
       <c r="O43" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="P43" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="Q43" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -3351,7 +3415,7 @@
         <v>172</v>
       </c>
       <c r="C44" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="E44" t="s">
         <v>20</v>
@@ -3360,7 +3424,7 @@
         <v>137</v>
       </c>
       <c r="I44" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="J44" t="s">
         <v>175</v>
@@ -3375,13 +3439,13 @@
         <v>178</v>
       </c>
       <c r="O44" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="P44" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="Q44" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -3392,7 +3456,7 @@
         <v>172</v>
       </c>
       <c r="C45" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E45" t="s">
         <v>20</v>
@@ -3401,7 +3465,7 @@
         <v>137</v>
       </c>
       <c r="I45" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="J45" t="s">
         <v>175</v>
@@ -3416,13 +3480,13 @@
         <v>178</v>
       </c>
       <c r="O45" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="P45" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="Q45" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -3433,7 +3497,7 @@
         <v>172</v>
       </c>
       <c r="C46" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E46" t="s">
         <v>20</v>
@@ -3442,7 +3506,7 @@
         <v>137</v>
       </c>
       <c r="I46" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J46" t="s">
         <v>175</v>
@@ -3457,13 +3521,13 @@
         <v>178</v>
       </c>
       <c r="O46" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="P46" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="Q46" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -3474,7 +3538,7 @@
         <v>172</v>
       </c>
       <c r="C47" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E47" t="s">
         <v>20</v>
@@ -3483,7 +3547,7 @@
         <v>137</v>
       </c>
       <c r="I47" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="J47" t="s">
         <v>175</v>
@@ -3498,13 +3562,13 @@
         <v>178</v>
       </c>
       <c r="O47" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="P47" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="Q47" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -3515,7 +3579,7 @@
         <v>172</v>
       </c>
       <c r="C48" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="E48" t="s">
         <v>20</v>
@@ -3524,7 +3588,7 @@
         <v>137</v>
       </c>
       <c r="I48" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="J48" t="s">
         <v>175</v>
@@ -3539,13 +3603,13 @@
         <v>178</v>
       </c>
       <c r="O48" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="P48" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="Q48" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -3556,7 +3620,7 @@
         <v>172</v>
       </c>
       <c r="C49" t="s">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="E49" t="s">
         <v>20</v>
@@ -3565,7 +3629,7 @@
         <v>137</v>
       </c>
       <c r="I49" t="s">
-        <v>122</v>
+        <v>195</v>
       </c>
       <c r="J49" t="s">
         <v>175</v>
@@ -3580,13 +3644,13 @@
         <v>178</v>
       </c>
       <c r="O49" t="s">
-        <v>123</v>
+        <v>196</v>
       </c>
       <c r="P49" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="Q49" t="s">
-        <v>125</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -3597,7 +3661,7 @@
         <v>172</v>
       </c>
       <c r="C50" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="E50" t="s">
         <v>20</v>
@@ -3606,7 +3670,7 @@
         <v>137</v>
       </c>
       <c r="I50" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="J50" t="s">
         <v>175</v>
@@ -3621,13 +3685,13 @@
         <v>178</v>
       </c>
       <c r="O50" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="P50" t="s">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="Q50" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -3635,31 +3699,40 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>200</v>
+        <v>172</v>
+      </c>
+      <c r="C51" t="s">
+        <v>134</v>
       </c>
       <c r="E51" t="s">
         <v>20</v>
       </c>
       <c r="F51" t="s">
-        <v>168</v>
-      </c>
-      <c r="G51" t="b">
-        <v>1</v>
-      </c>
-      <c r="H51" t="s">
-        <v>172</v>
+        <v>137</v>
+      </c>
+      <c r="I51" t="s">
+        <v>122</v>
       </c>
       <c r="J51" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="L51" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="M51" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="N51" t="s">
-        <v>203</v>
+        <v>178</v>
+      </c>
+      <c r="O51" t="s">
+        <v>123</v>
+      </c>
+      <c r="P51" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -3667,10 +3740,10 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="C52" t="s">
-        <v>205</v>
+        <v>159</v>
       </c>
       <c r="E52" t="s">
         <v>20</v>
@@ -3679,28 +3752,28 @@
         <v>137</v>
       </c>
       <c r="I52" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="J52" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="L52" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="M52" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="N52" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="O52" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="P52" t="s">
-        <v>209</v>
+        <v>161</v>
       </c>
       <c r="Q52" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -3708,40 +3781,31 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>204</v>
-      </c>
-      <c r="C53" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E53" t="s">
         <v>20</v>
       </c>
       <c r="F53" t="s">
-        <v>137</v>
-      </c>
-      <c r="I53" t="s">
-        <v>210</v>
+        <v>168</v>
+      </c>
+      <c r="G53" t="b">
+        <v>1</v>
+      </c>
+      <c r="H53" t="s">
+        <v>172</v>
       </c>
       <c r="J53" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L53" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="M53" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N53" t="s">
-        <v>208</v>
-      </c>
-      <c r="O53" t="s">
-        <v>211</v>
-      </c>
-      <c r="P53" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -3752,7 +3816,7 @@
         <v>204</v>
       </c>
       <c r="C54" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E54" t="s">
         <v>20</v>
@@ -3761,7 +3825,7 @@
         <v>137</v>
       </c>
       <c r="I54" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="J54" t="s">
         <v>204</v>
@@ -3776,13 +3840,13 @@
         <v>208</v>
       </c>
       <c r="O54" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="P54" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="Q54" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -3793,7 +3857,7 @@
         <v>204</v>
       </c>
       <c r="C55" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E55" t="s">
         <v>20</v>
@@ -3802,7 +3866,7 @@
         <v>137</v>
       </c>
       <c r="I55" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="J55" t="s">
         <v>204</v>
@@ -3817,13 +3881,13 @@
         <v>208</v>
       </c>
       <c r="O55" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="P55" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Q55" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -3834,7 +3898,7 @@
         <v>204</v>
       </c>
       <c r="C56" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E56" t="s">
         <v>20</v>
@@ -3843,7 +3907,7 @@
         <v>137</v>
       </c>
       <c r="I56" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="J56" t="s">
         <v>204</v>
@@ -3858,13 +3922,13 @@
         <v>208</v>
       </c>
       <c r="O56" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="P56" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="Q56" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -3875,7 +3939,7 @@
         <v>204</v>
       </c>
       <c r="C57" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="E57" t="s">
         <v>20</v>
@@ -3884,7 +3948,7 @@
         <v>137</v>
       </c>
       <c r="I57" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J57" t="s">
         <v>204</v>
@@ -3899,13 +3963,13 @@
         <v>208</v>
       </c>
       <c r="O57" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="P57" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="Q57" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -3916,7 +3980,7 @@
         <v>204</v>
       </c>
       <c r="C58" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="E58" t="s">
         <v>20</v>
@@ -3925,7 +3989,7 @@
         <v>137</v>
       </c>
       <c r="I58" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="J58" t="s">
         <v>204</v>
@@ -3940,13 +4004,13 @@
         <v>208</v>
       </c>
       <c r="O58" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P58" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="Q58" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -3957,7 +4021,7 @@
         <v>204</v>
       </c>
       <c r="C59" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="E59" t="s">
         <v>20</v>
@@ -3966,7 +4030,7 @@
         <v>137</v>
       </c>
       <c r="I59" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="J59" t="s">
         <v>204</v>
@@ -3981,13 +4045,13 @@
         <v>208</v>
       </c>
       <c r="O59" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="P59" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="Q59" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -3998,7 +4062,7 @@
         <v>204</v>
       </c>
       <c r="C60" t="s">
-        <v>159</v>
+        <v>220</v>
       </c>
       <c r="E60" t="s">
         <v>20</v>
@@ -4007,7 +4071,7 @@
         <v>137</v>
       </c>
       <c r="I60" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="J60" t="s">
         <v>204</v>
@@ -4022,13 +4086,13 @@
         <v>208</v>
       </c>
       <c r="O60" t="s">
-        <v>160</v>
+        <v>221</v>
       </c>
       <c r="P60" t="s">
-        <v>161</v>
+        <v>221</v>
       </c>
       <c r="Q60" t="s">
-        <v>162</v>
+        <v>221</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -4039,7 +4103,7 @@
         <v>204</v>
       </c>
       <c r="C61" t="s">
-        <v>163</v>
+        <v>222</v>
       </c>
       <c r="E61" t="s">
         <v>20</v>
@@ -4048,7 +4112,7 @@
         <v>137</v>
       </c>
       <c r="I61" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="J61" t="s">
         <v>204</v>
@@ -4063,13 +4127,13 @@
         <v>208</v>
       </c>
       <c r="O61" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="P61" t="s">
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="Q61" t="s">
-        <v>166</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -4077,31 +4141,40 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>225</v>
+        <v>204</v>
+      </c>
+      <c r="C62" t="s">
+        <v>159</v>
       </c>
       <c r="E62" t="s">
         <v>20</v>
       </c>
       <c r="F62" t="s">
-        <v>168</v>
-      </c>
-      <c r="G62" t="b">
-        <v>1</v>
-      </c>
-      <c r="H62" t="s">
+        <v>137</v>
+      </c>
+      <c r="I62" t="s">
+        <v>199</v>
+      </c>
+      <c r="J62" t="s">
         <v>204</v>
       </c>
-      <c r="J62" t="s">
-        <v>225</v>
-      </c>
       <c r="L62" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="M62" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="N62" t="s">
-        <v>228</v>
+        <v>208</v>
+      </c>
+      <c r="O62" t="s">
+        <v>160</v>
+      </c>
+      <c r="P62" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -4109,40 +4182,40 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="C63" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="E63" t="s">
         <v>20</v>
       </c>
       <c r="F63" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I63" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="J63" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="L63" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="M63" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="N63" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="O63" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="P63" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="Q63" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -4150,40 +4223,31 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>229</v>
-      </c>
-      <c r="C64" t="s">
-        <v>73</v>
+        <v>225</v>
       </c>
       <c r="E64" t="s">
         <v>20</v>
       </c>
       <c r="F64" t="s">
-        <v>32</v>
-      </c>
-      <c r="I64" t="s">
-        <v>95</v>
+        <v>168</v>
+      </c>
+      <c r="G64" t="b">
+        <v>1</v>
+      </c>
+      <c r="H64" t="s">
+        <v>204</v>
       </c>
       <c r="J64" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L64" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M64" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N64" t="s">
-        <v>231</v>
-      </c>
-      <c r="O64" t="s">
-        <v>74</v>
-      </c>
-      <c r="P64" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>76</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -4194,7 +4258,7 @@
         <v>229</v>
       </c>
       <c r="C65" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E65" t="s">
         <v>20</v>
@@ -4203,7 +4267,7 @@
         <v>32</v>
       </c>
       <c r="I65" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s">
         <v>229</v>
@@ -4218,13 +4282,13 @@
         <v>231</v>
       </c>
       <c r="O65" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="P65" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Q65" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -4235,7 +4299,7 @@
         <v>229</v>
       </c>
       <c r="C66" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E66" t="s">
         <v>20</v>
@@ -4244,7 +4308,7 @@
         <v>32</v>
       </c>
       <c r="I66" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="J66" t="s">
         <v>229</v>
@@ -4259,13 +4323,13 @@
         <v>231</v>
       </c>
       <c r="O66" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="P66" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Q66" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -4273,10 +4337,10 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C67" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="E67" t="s">
         <v>20</v>
@@ -4285,28 +4349,28 @@
         <v>32</v>
       </c>
       <c r="I67" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J67" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L67" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M67" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N67" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O67" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="P67" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="Q67" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -4314,10 +4378,10 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C68" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="E68" t="s">
         <v>20</v>
@@ -4326,28 +4390,28 @@
         <v>32</v>
       </c>
       <c r="I68" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="J68" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L68" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M68" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N68" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O68" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="P68" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Q68" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -4358,7 +4422,7 @@
         <v>232</v>
       </c>
       <c r="C69" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E69" t="s">
         <v>20</v>
@@ -4367,7 +4431,7 @@
         <v>32</v>
       </c>
       <c r="I69" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J69" t="s">
         <v>232</v>
@@ -4382,13 +4446,13 @@
         <v>234</v>
       </c>
       <c r="O69" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="P69" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Q69" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -4399,7 +4463,7 @@
         <v>232</v>
       </c>
       <c r="C70" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E70" t="s">
         <v>20</v>
@@ -4408,7 +4472,7 @@
         <v>32</v>
       </c>
       <c r="I70" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="J70" t="s">
         <v>232</v>
@@ -4423,13 +4487,13 @@
         <v>234</v>
       </c>
       <c r="O70" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="P70" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Q70" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -4437,10 +4501,10 @@
         <v>1</v>
       </c>
       <c r="B71" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C71" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="E71" t="s">
         <v>20</v>
@@ -4449,28 +4513,28 @@
         <v>32</v>
       </c>
       <c r="I71" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J71" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="L71" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="M71" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N71" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O71" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="P71" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="Q71" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -4478,10 +4542,10 @@
         <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C72" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="E72" t="s">
         <v>20</v>
@@ -4490,28 +4554,28 @@
         <v>32</v>
       </c>
       <c r="I72" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="J72" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="L72" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="M72" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N72" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O72" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="P72" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Q72" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -4522,7 +4586,7 @@
         <v>235</v>
       </c>
       <c r="C73" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E73" t="s">
         <v>20</v>
@@ -4531,7 +4595,7 @@
         <v>32</v>
       </c>
       <c r="I73" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J73" t="s">
         <v>235</v>
@@ -4546,13 +4610,13 @@
         <v>237</v>
       </c>
       <c r="O73" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="P73" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Q73" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -4563,7 +4627,7 @@
         <v>235</v>
       </c>
       <c r="C74" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E74" t="s">
         <v>20</v>
@@ -4572,7 +4636,7 @@
         <v>32</v>
       </c>
       <c r="I74" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="J74" t="s">
         <v>235</v>
@@ -4587,13 +4651,13 @@
         <v>237</v>
       </c>
       <c r="O74" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="P74" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Q74" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -4601,10 +4665,10 @@
         <v>1</v>
       </c>
       <c r="B75" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C75" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="E75" t="s">
         <v>20</v>
@@ -4613,28 +4677,28 @@
         <v>32</v>
       </c>
       <c r="I75" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J75" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L75" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M75" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N75" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O75" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="P75" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="Q75" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -4642,10 +4706,10 @@
         <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C76" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="E76" t="s">
         <v>20</v>
@@ -4654,28 +4718,28 @@
         <v>32</v>
       </c>
       <c r="I76" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="J76" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L76" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M76" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N76" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O76" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="P76" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Q76" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -4686,7 +4750,7 @@
         <v>238</v>
       </c>
       <c r="C77" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E77" t="s">
         <v>20</v>
@@ -4695,7 +4759,7 @@
         <v>32</v>
       </c>
       <c r="I77" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J77" t="s">
         <v>238</v>
@@ -4710,13 +4774,13 @@
         <v>240</v>
       </c>
       <c r="O77" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="P77" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Q77" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -4727,7 +4791,7 @@
         <v>238</v>
       </c>
       <c r="C78" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E78" t="s">
         <v>20</v>
@@ -4736,7 +4800,7 @@
         <v>32</v>
       </c>
       <c r="I78" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="J78" t="s">
         <v>238</v>
@@ -4751,13 +4815,13 @@
         <v>240</v>
       </c>
       <c r="O78" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="P78" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Q78" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -4765,10 +4829,10 @@
         <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C79" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="E79" t="s">
         <v>20</v>
@@ -4777,28 +4841,28 @@
         <v>32</v>
       </c>
       <c r="I79" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J79" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L79" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M79" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N79" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O79" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="P79" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="Q79" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -4806,10 +4870,10 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C80" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="E80" t="s">
         <v>20</v>
@@ -4818,28 +4882,28 @@
         <v>32</v>
       </c>
       <c r="I80" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="J80" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L80" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M80" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N80" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O80" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="P80" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Q80" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -4850,7 +4914,7 @@
         <v>241</v>
       </c>
       <c r="C81" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E81" t="s">
         <v>20</v>
@@ -4859,7 +4923,7 @@
         <v>32</v>
       </c>
       <c r="I81" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J81" t="s">
         <v>241</v>
@@ -4874,13 +4938,13 @@
         <v>243</v>
       </c>
       <c r="O81" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="P81" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Q81" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -4891,7 +4955,7 @@
         <v>241</v>
       </c>
       <c r="C82" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E82" t="s">
         <v>20</v>
@@ -4900,7 +4964,7 @@
         <v>32</v>
       </c>
       <c r="I82" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="J82" t="s">
         <v>241</v>
@@ -4915,13 +4979,13 @@
         <v>243</v>
       </c>
       <c r="O82" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="P82" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Q82" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -4929,10 +4993,10 @@
         <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C83" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="E83" t="s">
         <v>20</v>
@@ -4941,28 +5005,28 @@
         <v>32</v>
       </c>
       <c r="I83" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J83" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L83" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M83" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N83" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O83" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="P83" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="Q83" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -4970,10 +5034,10 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C84" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="E84" t="s">
         <v>20</v>
@@ -4982,28 +5046,28 @@
         <v>32</v>
       </c>
       <c r="I84" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="J84" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L84" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M84" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N84" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O84" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="P84" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Q84" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -5014,7 +5078,7 @@
         <v>244</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E85" t="s">
         <v>20</v>
@@ -5023,7 +5087,7 @@
         <v>32</v>
       </c>
       <c r="I85" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J85" t="s">
         <v>244</v>
@@ -5038,13 +5102,13 @@
         <v>246</v>
       </c>
       <c r="O85" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="P85" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Q85" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -5055,7 +5119,7 @@
         <v>244</v>
       </c>
       <c r="C86" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E86" t="s">
         <v>20</v>
@@ -5064,7 +5128,7 @@
         <v>32</v>
       </c>
       <c r="I86" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="J86" t="s">
         <v>244</v>
@@ -5079,13 +5143,13 @@
         <v>246</v>
       </c>
       <c r="O86" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="P86" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Q86" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -5093,10 +5157,10 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C87" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="E87" t="s">
         <v>20</v>
@@ -5105,28 +5169,28 @@
         <v>32</v>
       </c>
       <c r="I87" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J87" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L87" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M87" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N87" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O87" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="P87" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="Q87" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -5134,10 +5198,10 @@
         <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C88" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="E88" t="s">
         <v>20</v>
@@ -5146,28 +5210,28 @@
         <v>32</v>
       </c>
       <c r="I88" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="J88" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L88" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M88" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N88" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O88" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="P88" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Q88" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -5178,7 +5242,7 @@
         <v>247</v>
       </c>
       <c r="C89" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E89" t="s">
         <v>20</v>
@@ -5187,7 +5251,7 @@
         <v>32</v>
       </c>
       <c r="I89" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J89" t="s">
         <v>247</v>
@@ -5202,13 +5266,13 @@
         <v>249</v>
       </c>
       <c r="O89" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="P89" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Q89" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -5219,7 +5283,7 @@
         <v>247</v>
       </c>
       <c r="C90" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E90" t="s">
         <v>20</v>
@@ -5228,7 +5292,7 @@
         <v>32</v>
       </c>
       <c r="I90" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="J90" t="s">
         <v>247</v>
@@ -5243,13 +5307,13 @@
         <v>249</v>
       </c>
       <c r="O90" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="P90" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Q90" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -5257,10 +5321,10 @@
         <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C91" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="E91" t="s">
         <v>20</v>
@@ -5269,28 +5333,28 @@
         <v>32</v>
       </c>
       <c r="I91" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J91" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L91" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M91" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N91" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O91" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="P91" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="Q91" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -5298,10 +5362,10 @@
         <v>1</v>
       </c>
       <c r="B92" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C92" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="E92" t="s">
         <v>20</v>
@@ -5310,28 +5374,28 @@
         <v>32</v>
       </c>
       <c r="I92" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="J92" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L92" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M92" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N92" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O92" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="P92" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Q92" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -5342,7 +5406,7 @@
         <v>250</v>
       </c>
       <c r="C93" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E93" t="s">
         <v>20</v>
@@ -5351,7 +5415,7 @@
         <v>32</v>
       </c>
       <c r="I93" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J93" t="s">
         <v>250</v>
@@ -5366,13 +5430,13 @@
         <v>252</v>
       </c>
       <c r="O93" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="P93" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Q93" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -5383,7 +5447,7 @@
         <v>250</v>
       </c>
       <c r="C94" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E94" t="s">
         <v>20</v>
@@ -5392,7 +5456,7 @@
         <v>32</v>
       </c>
       <c r="I94" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="J94" t="s">
         <v>250</v>
@@ -5407,13 +5471,13 @@
         <v>252</v>
       </c>
       <c r="O94" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="P94" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Q94" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -5421,28 +5485,40 @@
         <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>253</v>
+        <v>250</v>
+      </c>
+      <c r="C95" t="s">
+        <v>134</v>
       </c>
       <c r="E95" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F95" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I95" t="s">
-        <v>254</v>
+        <v>122</v>
       </c>
       <c r="J95" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="L95" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="M95" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="N95" t="s">
-        <v>257</v>
+        <v>252</v>
+      </c>
+      <c r="O95" t="s">
+        <v>123</v>
+      </c>
+      <c r="P95" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -5450,28 +5526,40 @@
         <v>1</v>
       </c>
       <c r="B96" t="s">
-        <v>258</v>
+        <v>250</v>
+      </c>
+      <c r="C96" t="s">
+        <v>163</v>
       </c>
       <c r="E96" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F96" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I96" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="J96" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="L96" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="M96" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="N96" t="s">
-        <v>261</v>
+        <v>252</v>
+      </c>
+      <c r="O96" t="s">
+        <v>164</v>
+      </c>
+      <c r="P96" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -5479,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="E97" t="s">
         <v>47</v>
@@ -5491,16 +5579,16 @@
         <v>254</v>
       </c>
       <c r="J97" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="L97" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="M97" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="N97" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -5508,7 +5596,7 @@
         <v>1</v>
       </c>
       <c r="B98" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="E98" t="s">
         <v>47</v>
@@ -5520,16 +5608,16 @@
         <v>254</v>
       </c>
       <c r="J98" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="L98" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="M98" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="N98" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -5537,7 +5625,7 @@
         <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E99" t="s">
         <v>47</v>
@@ -5549,16 +5637,16 @@
         <v>254</v>
       </c>
       <c r="J99" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="L99" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M99" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="N99" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -5566,7 +5654,7 @@
         <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="E100" t="s">
         <v>47</v>
@@ -5578,16 +5666,16 @@
         <v>254</v>
       </c>
       <c r="J100" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="L100" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="M100" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="N100" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -5595,40 +5683,28 @@
         <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>278</v>
-      </c>
-      <c r="C101" t="s">
-        <v>101</v>
+        <v>269</v>
       </c>
       <c r="E101" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F101" t="s">
         <v>54</v>
       </c>
       <c r="I101" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="J101" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="L101" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="M101" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="N101" t="s">
-        <v>289</v>
-      </c>
-      <c r="O101" t="s">
-        <v>290</v>
-      </c>
-      <c r="P101" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q101" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -5636,40 +5712,28 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>278</v>
-      </c>
-      <c r="C102" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="E102" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F102" t="s">
         <v>54</v>
       </c>
       <c r="I102" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="J102" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="L102" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="M102" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="N102" t="s">
-        <v>289</v>
-      </c>
-      <c r="O102" t="s">
-        <v>291</v>
-      </c>
-      <c r="P102" t="s">
-        <v>299</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -5680,7 +5744,7 @@
         <v>278</v>
       </c>
       <c r="C103" t="s">
-        <v>281</v>
+        <v>101</v>
       </c>
       <c r="E103" t="s">
         <v>20</v>
@@ -5689,7 +5753,7 @@
         <v>54</v>
       </c>
       <c r="I103" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="J103" t="s">
         <v>278</v>
@@ -5704,13 +5768,13 @@
         <v>289</v>
       </c>
       <c r="O103" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P103" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="Q103" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -5721,7 +5785,7 @@
         <v>278</v>
       </c>
       <c r="C104" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E104" t="s">
         <v>20</v>
@@ -5730,7 +5794,7 @@
         <v>54</v>
       </c>
       <c r="I104" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J104" t="s">
         <v>278</v>
@@ -5745,13 +5809,13 @@
         <v>289</v>
       </c>
       <c r="O104" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="P104" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Q104" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -5759,149 +5823,363 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>279</v>
+        <v>278</v>
+      </c>
+      <c r="C105" t="s">
+        <v>281</v>
       </c>
       <c r="E105" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F105" t="s">
         <v>54</v>
       </c>
       <c r="I105" t="s">
-        <v>254</v>
+        <v>285</v>
+      </c>
+      <c r="J105" t="s">
+        <v>278</v>
       </c>
       <c r="L105" t="s">
         <v>287</v>
       </c>
+      <c r="M105" t="s">
+        <v>288</v>
+      </c>
+      <c r="N105" t="s">
+        <v>289</v>
+      </c>
+      <c r="O105" t="s">
+        <v>292</v>
+      </c>
+      <c r="P105" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1</v>
+      </c>
+      <c r="B106" t="s">
+        <v>278</v>
+      </c>
+      <c r="C106" t="s">
+        <v>282</v>
+      </c>
+      <c r="E106" t="s">
+        <v>20</v>
+      </c>
+      <c r="F106" t="s">
+        <v>54</v>
+      </c>
+      <c r="I106" t="s">
+        <v>286</v>
+      </c>
+      <c r="J106" t="s">
+        <v>278</v>
+      </c>
+      <c r="L106" t="s">
+        <v>287</v>
+      </c>
+      <c r="M106" t="s">
+        <v>288</v>
+      </c>
+      <c r="N106" t="s">
+        <v>289</v>
+      </c>
+      <c r="O106" t="s">
+        <v>293</v>
+      </c>
+      <c r="P106" t="s">
+        <v>301</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1</v>
+      </c>
+      <c r="B107" t="s">
+        <v>279</v>
+      </c>
+      <c r="E107" t="s">
+        <v>47</v>
+      </c>
+      <c r="F107" t="s">
+        <v>54</v>
+      </c>
+      <c r="I107" t="s">
+        <v>254</v>
+      </c>
+      <c r="L107" t="s">
+        <v>287</v>
+      </c>
+      <c r="M107" t="s">
+        <v>288</v>
+      </c>
+      <c r="N107" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1</v>
+      </c>
+      <c r="B108" t="s">
+        <v>302</v>
+      </c>
+      <c r="C108" t="s">
+        <v>306</v>
+      </c>
+      <c r="E108" t="s">
+        <v>20</v>
+      </c>
+      <c r="F108" t="s">
+        <v>54</v>
+      </c>
+      <c r="I108" t="s">
+        <v>307</v>
+      </c>
+      <c r="J108" t="s">
+        <v>302</v>
+      </c>
+      <c r="L108" t="s">
+        <v>310</v>
+      </c>
+      <c r="M108" t="s">
+        <v>311</v>
+      </c>
+      <c r="N108" t="s">
+        <v>312</v>
+      </c>
+      <c r="O108" t="s">
+        <v>303</v>
+      </c>
+      <c r="P108" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1</v>
+      </c>
+      <c r="B109" t="s">
+        <v>302</v>
+      </c>
+      <c r="C109" t="s">
+        <v>305</v>
+      </c>
+      <c r="E109" t="s">
+        <v>20</v>
+      </c>
+      <c r="F109" t="s">
+        <v>54</v>
+      </c>
+      <c r="I109" t="s">
+        <v>308</v>
+      </c>
+      <c r="J109" t="s">
+        <v>302</v>
+      </c>
+      <c r="L109" t="s">
+        <v>310</v>
+      </c>
+      <c r="M109" t="s">
+        <v>311</v>
+      </c>
+      <c r="N109" t="s">
+        <v>312</v>
+      </c>
+      <c r="O109" t="s">
+        <v>313</v>
+      </c>
+      <c r="P109" t="s">
+        <v>318</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1</v>
+      </c>
+      <c r="B110" t="s">
+        <v>302</v>
+      </c>
+      <c r="C110" t="s">
+        <v>304</v>
+      </c>
+      <c r="E110" t="s">
+        <v>20</v>
+      </c>
+      <c r="F110" t="s">
+        <v>54</v>
+      </c>
+      <c r="I110" t="s">
+        <v>309</v>
+      </c>
+      <c r="J110" t="s">
+        <v>302</v>
+      </c>
+      <c r="L110" t="s">
+        <v>310</v>
+      </c>
+      <c r="M110" t="s">
+        <v>311</v>
+      </c>
+      <c r="N110" t="s">
+        <v>312</v>
+      </c>
+      <c r="O110" t="s">
+        <v>314</v>
+      </c>
+      <c r="P110" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>317</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B9:B11 B14">
-    <cfRule type="duplicateValues" dxfId="42" priority="44"/>
+  <conditionalFormatting sqref="B11:B13 B16">
+    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12">
-    <cfRule type="duplicateValues" dxfId="41" priority="42"/>
+  <conditionalFormatting sqref="B14">
+    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B26">
+  <conditionalFormatting sqref="B28">
+    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B29">
     <cfRule type="duplicateValues" dxfId="40" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B27">
+  <conditionalFormatting sqref="B30">
     <cfRule type="duplicateValues" dxfId="39" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
+  <conditionalFormatting sqref="B31:B41">
     <cfRule type="duplicateValues" dxfId="38" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29:B39">
-    <cfRule type="duplicateValues" dxfId="37" priority="37"/>
+  <conditionalFormatting sqref="B42">
+    <cfRule type="duplicateValues" dxfId="37" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B40">
-    <cfRule type="duplicateValues" dxfId="36" priority="35"/>
+  <conditionalFormatting sqref="B43:B53 B95:B146">
+    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B41:B51 B93:B144">
-    <cfRule type="duplicateValues" dxfId="35" priority="27"/>
+  <conditionalFormatting sqref="B54:B63">
+    <cfRule type="duplicateValues" dxfId="35" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B52:B61">
+  <conditionalFormatting sqref="B64">
     <cfRule type="duplicateValues" dxfId="34" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B62">
-    <cfRule type="duplicateValues" dxfId="33" priority="20"/>
+  <conditionalFormatting sqref="B65:B96">
+    <cfRule type="duplicateValues" dxfId="33" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63:B94">
-    <cfRule type="duplicateValues" dxfId="32" priority="13"/>
+  <conditionalFormatting sqref="C11:C13">
+    <cfRule type="duplicateValues" dxfId="32" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:C11">
-    <cfRule type="duplicateValues" dxfId="31" priority="43"/>
+  <conditionalFormatting sqref="C21:C25">
+    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C19:C23">
-    <cfRule type="duplicateValues" dxfId="30" priority="41"/>
+  <conditionalFormatting sqref="C31:C41">
+    <cfRule type="duplicateValues" dxfId="30" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C29:C39">
-    <cfRule type="duplicateValues" dxfId="29" priority="36"/>
+  <conditionalFormatting sqref="C51:C52">
+    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C49:C50">
-    <cfRule type="duplicateValues" dxfId="28" priority="26"/>
+  <conditionalFormatting sqref="C54:C63">
+    <cfRule type="duplicateValues" dxfId="28" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C52:C61">
-    <cfRule type="duplicateValues" dxfId="27" priority="19"/>
+  <conditionalFormatting sqref="H42">
+    <cfRule type="duplicateValues" dxfId="27" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H40">
-    <cfRule type="duplicateValues" dxfId="26" priority="34"/>
+  <conditionalFormatting sqref="H53:H63 H65:H146">
+    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H51:H61 H63:H144">
-    <cfRule type="duplicateValues" dxfId="25" priority="24"/>
+  <conditionalFormatting sqref="H64">
+    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H62">
-    <cfRule type="duplicateValues" dxfId="24" priority="18"/>
+  <conditionalFormatting sqref="I22:I24">
+    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I20:I22">
-    <cfRule type="duplicateValues" dxfId="23" priority="28"/>
+  <conditionalFormatting sqref="I31:I41">
+    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I29:I39">
-    <cfRule type="duplicateValues" dxfId="22" priority="33"/>
+  <conditionalFormatting sqref="I52">
+    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I50">
-    <cfRule type="duplicateValues" dxfId="21" priority="25"/>
+  <conditionalFormatting sqref="I54:I61 I63">
+    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I52:I59 I61">
-    <cfRule type="duplicateValues" dxfId="20" priority="16"/>
+  <conditionalFormatting sqref="I62">
+    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I60">
-    <cfRule type="duplicateValues" dxfId="19" priority="14"/>
+  <conditionalFormatting sqref="I68">
+    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I66">
+  <conditionalFormatting sqref="I72">
     <cfRule type="duplicateValues" dxfId="18" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I70">
+  <conditionalFormatting sqref="I76">
     <cfRule type="duplicateValues" dxfId="17" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I74">
+  <conditionalFormatting sqref="I80">
     <cfRule type="duplicateValues" dxfId="16" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I78">
+  <conditionalFormatting sqref="I84">
     <cfRule type="duplicateValues" dxfId="15" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I82">
+  <conditionalFormatting sqref="I88">
     <cfRule type="duplicateValues" dxfId="14" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I86">
+  <conditionalFormatting sqref="I92">
     <cfRule type="duplicateValues" dxfId="13" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I90">
-    <cfRule type="duplicateValues" dxfId="12" priority="6"/>
+  <conditionalFormatting sqref="I96">
+    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I94">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+  <conditionalFormatting sqref="J28">
+    <cfRule type="duplicateValues" dxfId="11" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J26">
+  <conditionalFormatting sqref="J29">
     <cfRule type="duplicateValues" dxfId="10" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J27">
+  <conditionalFormatting sqref="J30">
     <cfRule type="duplicateValues" dxfId="9" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
-    <cfRule type="duplicateValues" dxfId="8" priority="29"/>
+  <conditionalFormatting sqref="J31:J41">
+    <cfRule type="duplicateValues" dxfId="8" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J29:J39">
-    <cfRule type="duplicateValues" dxfId="7" priority="32"/>
+  <conditionalFormatting sqref="J43:J52">
+    <cfRule type="duplicateValues" dxfId="7" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J41:J50">
-    <cfRule type="duplicateValues" dxfId="6" priority="22"/>
+  <conditionalFormatting sqref="J53 J107 J111:J146">
+    <cfRule type="duplicateValues" dxfId="6" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J51 J105:J144">
-    <cfRule type="duplicateValues" dxfId="5" priority="23"/>
+  <conditionalFormatting sqref="J54:J63">
+    <cfRule type="duplicateValues" dxfId="5" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J52:J61">
-    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
+  <conditionalFormatting sqref="J64">
+    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J62">
-    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
+  <conditionalFormatting sqref="J65:J96">
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J63:J94">
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+  <conditionalFormatting sqref="J95:J96">
+    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J93:J94">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <conditionalFormatting sqref="J97:J106">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J95:J104">
+  <conditionalFormatting sqref="J108:J110">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/variable_schema_data_individual_nutrition_template.xlsx
+++ b/resources/variable_schema_data_individual_nutrition_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F493A87F-B5FB-477E-8121-01D91F25F4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1531BD-6D67-45C0-82FB-848277E0221E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1335" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="458">
   <si>
     <t>rule_type</t>
   </si>
@@ -820,39 +820,12 @@
     <t>global_mfaz</t>
   </si>
   <si>
-    <t>Global MFAZ</t>
-  </si>
-  <si>
-    <t>MFAZ global</t>
-  </si>
-  <si>
-    <t>مؤشر وزن الذراع للعمر العالمي</t>
-  </si>
-  <si>
     <t>moderate_mfaz</t>
   </si>
   <si>
-    <t>Moderate MFAZ</t>
-  </si>
-  <si>
-    <t>MFAZ modéré</t>
-  </si>
-  <si>
-    <t>مؤشر وزن الذراع للعمر المعتدل</t>
-  </si>
-  <si>
     <t>severe_mfaz</t>
   </si>
   <si>
-    <t>Severe MFAZ</t>
-  </si>
-  <si>
-    <t>MFAZ sévère</t>
-  </si>
-  <si>
-    <t>مؤشر وزن الذراع للعمر الشديد</t>
-  </si>
-  <si>
     <t>nut_mfaz</t>
   </si>
   <si>
@@ -1004,6 +977,423 @@
   </si>
   <si>
     <t>roster_age_30_59m,age_30_59m</t>
+  </si>
+  <si>
+    <t>enum_id</t>
+  </si>
+  <si>
+    <t>enum_id,enumerator_id,enumerator,enum,surveyor_id</t>
+  </si>
+  <si>
+    <t>Enumerator ID</t>
+  </si>
+  <si>
+    <t>ID de l'enquêteur</t>
+  </si>
+  <si>
+    <t>معرف المعداد</t>
+  </si>
+  <si>
+    <t>device_id</t>
+  </si>
+  <si>
+    <t>device_id,deviceid,device,device_identifier</t>
+  </si>
+  <si>
+    <t>Device ID</t>
+  </si>
+  <si>
+    <t>ID de l'appareil</t>
+  </si>
+  <si>
+    <t>معرف الجهاز</t>
+  </si>
+  <si>
+    <t>date_survey</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>date_survey,today,date_dc,interview_date</t>
+  </si>
+  <si>
+    <t>Survey Date</t>
+  </si>
+  <si>
+    <t>Date de l'enquête</t>
+  </si>
+  <si>
+    <t>تاريخ الاستبيان</t>
+  </si>
+  <si>
+    <t>gps_lat</t>
+  </si>
+  <si>
+    <t>gps</t>
+  </si>
+  <si>
+    <t>gps_lat,latitude,lat,_gps_latitude,gps_latitude</t>
+  </si>
+  <si>
+    <t>GPS Latitude</t>
+  </si>
+  <si>
+    <t>Latitude GPS</t>
+  </si>
+  <si>
+    <t>خط العرض GPS</t>
+  </si>
+  <si>
+    <t>gps_lon</t>
+  </si>
+  <si>
+    <t>gps_lon,longitude,lon,lng,_gps_longitude,gps_longitude</t>
+  </si>
+  <si>
+    <t>GPS Longitude</t>
+  </si>
+  <si>
+    <t>Longitude GPS</t>
+  </si>
+  <si>
+    <t>خط الطول GPS</t>
+  </si>
+  <si>
+    <t>gps_precision</t>
+  </si>
+  <si>
+    <t>gps_precision,gps_accuracy,accuracy</t>
+  </si>
+  <si>
+    <t>GPS Precision</t>
+  </si>
+  <si>
+    <t>Précision GPS</t>
+  </si>
+  <si>
+    <t>دقة GPS</t>
+  </si>
+  <si>
+    <t>GPS precision</t>
+  </si>
+  <si>
+    <t>weight</t>
+  </si>
+  <si>
+    <t>weight,sampling_weight,survey_weight,wt</t>
+  </si>
+  <si>
+    <t>Sampling Weight</t>
+  </si>
+  <si>
+    <t>Poids d'échantillonnage</t>
+  </si>
+  <si>
+    <t>وزن العينة</t>
+  </si>
+  <si>
+    <t>Sampling weight</t>
+  </si>
+  <si>
+    <t>stratum</t>
+  </si>
+  <si>
+    <t>stratum,strata,survey_stratum</t>
+  </si>
+  <si>
+    <t>Stratum</t>
+  </si>
+  <si>
+    <t>Strate</t>
+  </si>
+  <si>
+    <t>الطبقة</t>
+  </si>
+  <si>
+    <t>Survey stratum</t>
+  </si>
+  <si>
+    <t>cluster_id</t>
+  </si>
+  <si>
+    <t>cluster_id,cluster,psu,primary_sampling_unit</t>
+  </si>
+  <si>
+    <t>Cluster ID</t>
+  </si>
+  <si>
+    <t>ID de la grappe</t>
+  </si>
+  <si>
+    <t>معرف العنقود</t>
+  </si>
+  <si>
+    <t>Primary sampling unit</t>
+  </si>
+  <si>
+    <t>cluster_id_numeric</t>
+  </si>
+  <si>
+    <t>site</t>
+  </si>
+  <si>
+    <t>site,location,assessment_site,site_name</t>
+  </si>
+  <si>
+    <t>Survey Site</t>
+  </si>
+  <si>
+    <t>Site d'enquête</t>
+  </si>
+  <si>
+    <t>موقع الاستبيان</t>
+  </si>
+  <si>
+    <t>Assessment site</t>
+  </si>
+  <si>
+    <t>admin1</t>
+  </si>
+  <si>
+    <t>admin1,adm1,region,state,province,governorate</t>
+  </si>
+  <si>
+    <t>Administrative Area 1</t>
+  </si>
+  <si>
+    <t>Zone administrative 1</t>
+  </si>
+  <si>
+    <t>المنطقة الإدارية 1</t>
+  </si>
+  <si>
+    <t>admin2</t>
+  </si>
+  <si>
+    <t>admin2,adm2,district,county,zone</t>
+  </si>
+  <si>
+    <t>Administrative Area 2</t>
+  </si>
+  <si>
+    <t>Zone administrative 2</t>
+  </si>
+  <si>
+    <t>المنطقة الإدارية 2</t>
+  </si>
+  <si>
+    <t>admin3</t>
+  </si>
+  <si>
+    <t>admin3,adm3,sub_district,commune,ward</t>
+  </si>
+  <si>
+    <t>Administrative Area 3</t>
+  </si>
+  <si>
+    <t>Zone administrative 3</t>
+  </si>
+  <si>
+    <t>المنطقة الإدارية 3</t>
+  </si>
+  <si>
+    <t>admin4</t>
+  </si>
+  <si>
+    <t>admin4,adm4,village,locality</t>
+  </si>
+  <si>
+    <t>Administrative Area 4</t>
+  </si>
+  <si>
+    <t>Zone administrative 4</t>
+  </si>
+  <si>
+    <t>المنطقة الإدارية 4</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat</t>
+  </si>
+  <si>
+    <t>nut_mfaz_noflag</t>
+  </si>
+  <si>
+    <t>nut_mfaz_cat_noflag</t>
+  </si>
+  <si>
+    <t>severe_mfaz_noflag</t>
+  </si>
+  <si>
+    <t>moderate_mfaz_noflag</t>
+  </si>
+  <si>
+    <t>global_mfaz_noflag</t>
+  </si>
+  <si>
+    <t>gam_muac_noflag</t>
+  </si>
+  <si>
+    <t>mam_muac_noflag</t>
+  </si>
+  <si>
+    <t>sam_muac_noflag</t>
+  </si>
+  <si>
+    <t>GAM by MUAC without flags</t>
+  </si>
+  <si>
+    <t>MAM by MUAC without flags</t>
+  </si>
+  <si>
+    <t>SAM by MUAC without flags</t>
+  </si>
+  <si>
+    <t>SAM من MUAC بدون علامات</t>
+  </si>
+  <si>
+    <t>MAM من MUAC بدون علامات</t>
+  </si>
+  <si>
+    <t>GAM من MUAC بدون علامات</t>
+  </si>
+  <si>
+    <t>GAM par MUAC sans valeurs aberrantes</t>
+  </si>
+  <si>
+    <t>MAM par MUAC sans valeurs aberrantes</t>
+  </si>
+  <si>
+    <t>SAM par MUAC sans valeurs aberrantes</t>
+  </si>
+  <si>
+    <t>GAM by MFAZ</t>
+  </si>
+  <si>
+    <t>Moderate Malnutrition by MFAZ</t>
+  </si>
+  <si>
+    <t>Severe Malnutritionby MFAZ</t>
+  </si>
+  <si>
+    <t>Normal without flags</t>
+  </si>
+  <si>
+    <t>Moderate Malnutrition by MFAZ without flags</t>
+  </si>
+  <si>
+    <t>Severe Malnutritionby MFAZ without flags</t>
+  </si>
+  <si>
+    <t>طبيعي</t>
+  </si>
+  <si>
+    <t>سوء التغذية المعتدل حسب مؤشر MFAZ</t>
+  </si>
+  <si>
+    <t>سوء التغذية الحاد حسب مؤشر MFAZ</t>
+  </si>
+  <si>
+    <t>طبيعي بدون علامات</t>
+  </si>
+  <si>
+    <t>سوء التغذية المعتدل حسب مؤشر MFAZ بدون علامات</t>
+  </si>
+  <si>
+    <t>سوء التغذية الحاد حسب مؤشر MFAZ بدون علامات</t>
+  </si>
+  <si>
+    <t>Nutrition Status by MFAZ</t>
+  </si>
+  <si>
+    <t>Nutrition Status by MFAZ without flags</t>
+  </si>
+  <si>
+    <t>الحالة التغذوية حسب منطقة MFAZ</t>
+  </si>
+  <si>
+    <t>الحالة التغذوية حسب منطقة MFAZ بدون علامات</t>
+  </si>
+  <si>
+    <t>État nutritionnel par MFAZ</t>
+  </si>
+  <si>
+    <t>État nutritionnel par MFAZ sans indicateurs</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-Score</t>
+  </si>
+  <si>
+    <t>MUAC-for-Age Z-Score without flags</t>
+  </si>
+  <si>
+    <t>Score Z du périmètre brachial par rapport à l'âge</t>
+  </si>
+  <si>
+    <t>Score Z du périmètre brachial par rapport à l'âge (sans indicateurs)</t>
+  </si>
+  <si>
+    <t>مؤشر Z لمحيط الذراع عند عمر معين</t>
+  </si>
+  <si>
+    <t>مؤشر Z لمحيط الذراع عند عمر معين بدون علامات</t>
+  </si>
+  <si>
+    <t>SAM by MFAZ</t>
+  </si>
+  <si>
+    <t>MAM by MFAZ</t>
+  </si>
+  <si>
+    <t>GAM by MFAZ without flags</t>
+  </si>
+  <si>
+    <t>MAM by MFAZ without flags</t>
+  </si>
+  <si>
+    <t>SAM by MFAZ without flags</t>
+  </si>
+  <si>
+    <t>SAM من MFAZ</t>
+  </si>
+  <si>
+    <t>SAM من MFAZ بدون أعلام</t>
+  </si>
+  <si>
+    <t>MAM من MFAZ</t>
+  </si>
+  <si>
+    <t>MAM من MFAZ بدون أعلام</t>
+  </si>
+  <si>
+    <t>GAM من MFAZ</t>
+  </si>
+  <si>
+    <t>GAM من MFAZ بدون أعلام</t>
+  </si>
+  <si>
+    <t>SAM par MFAZ</t>
+  </si>
+  <si>
+    <t>SAM par MFAZ sans valeurs aberrantes</t>
+  </si>
+  <si>
+    <t>MAM par MFAZ</t>
+  </si>
+  <si>
+    <t>MAM par MFAZ sans valeurs aberrantes</t>
+  </si>
+  <si>
+    <t>GAM par MFAZ</t>
+  </si>
+  <si>
+    <t>GAM par MFAZ sans valeurs aberrantes</t>
+  </si>
+  <si>
+    <t>nut_mfaz,mfaz</t>
+  </si>
+  <si>
+    <t>nut_mfaz_noflag,mfaz_noflag</t>
   </si>
 </sst>
 </file>
@@ -1045,7 +1435,87 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="52">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1784,7 +2254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S110"/>
+  <dimension ref="A1:S138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
@@ -1887,31 +2357,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="b">
-        <v>1</v>
+        <v>319</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
-        <v>21</v>
+      <c r="G3" t="b">
+        <v>0</v>
       </c>
       <c r="J3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
+        <v>320</v>
       </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>321</v>
       </c>
       <c r="M3" t="s">
-        <v>28</v>
+        <v>322</v>
       </c>
       <c r="N3" t="s">
-        <v>29</v>
+        <v>323</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -1919,40 +2386,28 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" t="s">
-        <v>31</v>
+        <v>324</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="F4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
+      <c r="G4" t="b">
+        <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>34</v>
+        <v>325</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>326</v>
       </c>
       <c r="M4" t="s">
-        <v>36</v>
+        <v>327</v>
       </c>
       <c r="N4" t="s">
-        <v>37</v>
-      </c>
-      <c r="O4" t="s">
-        <v>38</v>
-      </c>
-      <c r="P4" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>40</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1960,40 +2415,31 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>41</v>
+        <v>329</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>20</v>
+        <v>330</v>
       </c>
       <c r="F5" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" t="s">
-        <v>42</v>
+        <v>330</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>34</v>
+        <v>331</v>
       </c>
       <c r="L5" t="s">
-        <v>35</v>
+        <v>332</v>
       </c>
       <c r="M5" t="s">
-        <v>36</v>
+        <v>333</v>
       </c>
       <c r="N5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O5" t="s">
-        <v>43</v>
-      </c>
-      <c r="P5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>45</v>
+        <v>334</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -2001,25 +2447,31 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>335</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
       </c>
       <c r="E6" t="s">
         <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>48</v>
+        <v>336</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>337</v>
       </c>
       <c r="L6" t="s">
-        <v>50</v>
+        <v>338</v>
       </c>
       <c r="M6" t="s">
-        <v>51</v>
+        <v>339</v>
       </c>
       <c r="N6" t="s">
-        <v>52</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -2027,25 +2479,31 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>341</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
       </c>
       <c r="E7" t="s">
         <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>336</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>55</v>
+        <v>342</v>
       </c>
       <c r="L7" t="s">
-        <v>56</v>
+        <v>343</v>
       </c>
       <c r="M7" t="s">
-        <v>57</v>
+        <v>344</v>
       </c>
       <c r="N7" t="s">
-        <v>58</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -2053,25 +2511,34 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>346</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
       </c>
       <c r="E8" t="s">
         <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>336</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>60</v>
+        <v>347</v>
       </c>
       <c r="L8" t="s">
-        <v>61</v>
+        <v>348</v>
       </c>
       <c r="M8" t="s">
-        <v>62</v>
+        <v>349</v>
       </c>
       <c r="N8" t="s">
-        <v>63</v>
+        <v>350</v>
+      </c>
+      <c r="R8" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -2079,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2087,20 +2554,26 @@
       <c r="E9" t="s">
         <v>47</v>
       </c>
+      <c r="F9" t="s">
+        <v>54</v>
+      </c>
       <c r="G9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="L9" t="s">
-        <v>321</v>
+        <v>354</v>
       </c>
       <c r="M9" t="s">
-        <v>321</v>
+        <v>355</v>
       </c>
       <c r="N9" t="s">
-        <v>322</v>
+        <v>356</v>
+      </c>
+      <c r="R9" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2108,28 +2581,31 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>323</v>
+        <v>358</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>327</v>
+        <v>359</v>
       </c>
       <c r="L10" t="s">
-        <v>324</v>
+        <v>360</v>
       </c>
       <c r="M10" t="s">
-        <v>324</v>
+        <v>361</v>
       </c>
       <c r="N10" t="s">
-        <v>325</v>
+        <v>362</v>
+      </c>
+      <c r="R10" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -2137,37 +2613,31 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>65</v>
+        <v>364</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
       </c>
       <c r="E11" t="s">
         <v>20</v>
       </c>
-      <c r="F11" t="s">
-        <v>32</v>
+      <c r="G11" t="b">
+        <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>66</v>
+        <v>365</v>
       </c>
       <c r="L11" t="s">
-        <v>67</v>
+        <v>366</v>
       </c>
       <c r="M11" t="s">
-        <v>68</v>
+        <v>367</v>
       </c>
       <c r="N11" t="s">
-        <v>69</v>
-      </c>
-      <c r="O11" t="s">
-        <v>70</v>
-      </c>
-      <c r="P11" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>72</v>
+        <v>368</v>
+      </c>
+      <c r="R11" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -2175,37 +2645,31 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
+        <v>370</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>66</v>
+        <v>370</v>
       </c>
       <c r="L12" t="s">
-        <v>67</v>
+        <v>366</v>
       </c>
       <c r="M12" t="s">
-        <v>68</v>
+        <v>367</v>
       </c>
       <c r="N12" t="s">
-        <v>69</v>
-      </c>
-      <c r="O12" t="s">
-        <v>74</v>
-      </c>
-      <c r="P12" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>76</v>
+        <v>368</v>
+      </c>
+      <c r="R12" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -2213,37 +2677,31 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
+        <v>371</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
       </c>
       <c r="E13" t="s">
         <v>20</v>
       </c>
-      <c r="F13" t="s">
-        <v>32</v>
+      <c r="G13" t="b">
+        <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>66</v>
+        <v>372</v>
       </c>
       <c r="L13" t="s">
-        <v>67</v>
+        <v>373</v>
       </c>
       <c r="M13" t="s">
-        <v>68</v>
+        <v>374</v>
       </c>
       <c r="N13" t="s">
-        <v>69</v>
-      </c>
-      <c r="O13" t="s">
-        <v>78</v>
-      </c>
-      <c r="P13" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>80</v>
+        <v>375</v>
+      </c>
+      <c r="R13" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -2251,25 +2709,28 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>377</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" t="s">
-        <v>82</v>
+        <v>20</v>
+      </c>
+      <c r="G14" t="b">
+        <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="L14" t="s">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="M14" t="s">
-        <v>84</v>
+        <v>380</v>
       </c>
       <c r="N14" t="s">
-        <v>85</v>
+        <v>381</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -2277,25 +2738,28 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>382</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" t="s">
-        <v>48</v>
+        <v>20</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>87</v>
+        <v>383</v>
       </c>
       <c r="L15" t="s">
-        <v>88</v>
+        <v>384</v>
       </c>
       <c r="M15" t="s">
-        <v>88</v>
+        <v>385</v>
       </c>
       <c r="N15" t="s">
-        <v>89</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -2303,13 +2767,28 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>277</v>
+        <v>387</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
+        <v>20</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
+        <v>388</v>
+      </c>
+      <c r="L16" t="s">
+        <v>389</v>
+      </c>
+      <c r="M16" t="s">
+        <v>390</v>
+      </c>
+      <c r="N16" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -2317,40 +2796,28 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" t="s">
-        <v>65</v>
+        <v>392</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
       </c>
       <c r="E17" t="s">
         <v>20</v>
       </c>
-      <c r="F17" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" t="s">
-        <v>91</v>
+      <c r="G17" t="b">
+        <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>90</v>
+        <v>393</v>
       </c>
       <c r="L17" t="s">
-        <v>92</v>
+        <v>394</v>
       </c>
       <c r="M17" t="s">
-        <v>93</v>
+        <v>395</v>
       </c>
       <c r="N17" t="s">
-        <v>94</v>
-      </c>
-      <c r="O17" t="s">
-        <v>70</v>
-      </c>
-      <c r="P17" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>72</v>
+        <v>396</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -2358,40 +2825,31 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" t="s">
-        <v>73</v>
+        <v>26</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="J18" t="s">
-        <v>90</v>
+        <v>26</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>92</v>
+        <v>27</v>
       </c>
       <c r="M18" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
       <c r="N18" t="s">
-        <v>94</v>
-      </c>
-      <c r="O18" t="s">
-        <v>74</v>
-      </c>
-      <c r="P18" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -2399,10 +2857,10 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="E19" t="s">
         <v>20</v>
@@ -2411,28 +2869,28 @@
         <v>32</v>
       </c>
       <c r="I19" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="J19" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="L19" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="M19" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="N19" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="O19" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="P19" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="Q19" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -2440,10 +2898,10 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="E20" t="s">
         <v>20</v>
@@ -2452,28 +2910,28 @@
         <v>32</v>
       </c>
       <c r="I20" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="J20" t="s">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c r="L20" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
       <c r="M20" t="s">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="N20" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="O20" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="P20" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="Q20" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -2481,40 +2939,25 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" t="s">
-        <v>101</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="J21" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="L21" t="s">
-        <v>103</v>
+        <v>50</v>
       </c>
       <c r="M21" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="N21" t="s">
-        <v>105</v>
-      </c>
-      <c r="O21" t="s">
-        <v>106</v>
-      </c>
-      <c r="P21" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -2522,40 +2965,25 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
-      </c>
-      <c r="C22" t="s">
-        <v>109</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" t="s">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c r="J22" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="L22" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="M22" t="s">
-        <v>104</v>
+        <v>57</v>
       </c>
       <c r="N22" t="s">
-        <v>105</v>
-      </c>
-      <c r="O22" t="s">
-        <v>110</v>
-      </c>
-      <c r="P22" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -2563,40 +2991,25 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C23" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="J23" t="s">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="L23" t="s">
-        <v>103</v>
+        <v>61</v>
       </c>
       <c r="M23" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
       <c r="N23" t="s">
-        <v>105</v>
-      </c>
-      <c r="O23" t="s">
-        <v>114</v>
-      </c>
-      <c r="P23" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>116</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
@@ -2604,40 +3017,28 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>100</v>
-      </c>
-      <c r="C24" t="s">
-        <v>117</v>
+        <v>311</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" t="s">
-        <v>117</v>
+        <v>47</v>
+      </c>
+      <c r="G24" t="b">
+        <v>0</v>
       </c>
       <c r="J24" t="s">
-        <v>100</v>
+        <v>317</v>
       </c>
       <c r="L24" t="s">
-        <v>103</v>
+        <v>312</v>
       </c>
       <c r="M24" t="s">
-        <v>104</v>
+        <v>312</v>
       </c>
       <c r="N24" t="s">
-        <v>105</v>
-      </c>
-      <c r="O24" t="s">
-        <v>118</v>
-      </c>
-      <c r="P24" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>120</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -2645,40 +3046,28 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" t="s">
-        <v>121</v>
+        <v>314</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" t="s">
-        <v>122</v>
+        <v>47</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
       </c>
       <c r="J25" t="s">
-        <v>100</v>
+        <v>318</v>
       </c>
       <c r="L25" t="s">
-        <v>103</v>
+        <v>315</v>
       </c>
       <c r="M25" t="s">
-        <v>104</v>
+        <v>315</v>
       </c>
       <c r="N25" t="s">
-        <v>105</v>
-      </c>
-      <c r="O25" t="s">
-        <v>123</v>
-      </c>
-      <c r="P25" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>125</v>
+        <v>316</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -2686,7 +3075,7 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="C26" t="s">
         <v>65</v>
@@ -2697,20 +3086,17 @@
       <c r="F26" t="s">
         <v>32</v>
       </c>
-      <c r="I26" t="s">
-        <v>91</v>
-      </c>
       <c r="J26" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="L26" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="M26" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="N26" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="O26" t="s">
         <v>70</v>
@@ -2727,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>126</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
         <v>73</v>
@@ -2738,20 +3124,17 @@
       <c r="F27" t="s">
         <v>32</v>
       </c>
-      <c r="I27" t="s">
-        <v>95</v>
-      </c>
       <c r="J27" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="L27" t="s">
-        <v>127</v>
+        <v>67</v>
       </c>
       <c r="M27" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="N27" t="s">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="O27" t="s">
         <v>74</v>
@@ -2768,10 +3151,10 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -2779,29 +3162,26 @@
       <c r="F28" t="s">
         <v>32</v>
       </c>
-      <c r="I28" t="s">
-        <v>91</v>
-      </c>
       <c r="J28" t="s">
-        <v>130</v>
+        <v>66</v>
       </c>
       <c r="L28" t="s">
-        <v>131</v>
+        <v>67</v>
       </c>
       <c r="M28" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="N28" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="O28" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="P28" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="Q28" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -2809,40 +3189,25 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
-      </c>
-      <c r="I29" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="J29" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="L29" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="M29" t="s">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="N29" t="s">
-        <v>133</v>
-      </c>
-      <c r="O29" t="s">
-        <v>74</v>
-      </c>
-      <c r="P29" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
@@ -2850,40 +3215,25 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" t="s">
-        <v>134</v>
+        <v>86</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="J30" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="L30" t="s">
-        <v>131</v>
+        <v>88</v>
       </c>
       <c r="M30" t="s">
-        <v>132</v>
+        <v>88</v>
       </c>
       <c r="N30" t="s">
-        <v>133</v>
-      </c>
-      <c r="O30" t="s">
-        <v>123</v>
-      </c>
-      <c r="P30" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -2891,40 +3241,28 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>135</v>
-      </c>
-      <c r="C31" t="s">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F31" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I31" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="J31" t="s">
-        <v>138</v>
+        <v>253</v>
       </c>
       <c r="L31" t="s">
-        <v>139</v>
+        <v>255</v>
       </c>
       <c r="M31" t="s">
-        <v>140</v>
+        <v>256</v>
       </c>
       <c r="N31" t="s">
-        <v>141</v>
-      </c>
-      <c r="O31" t="s">
-        <v>142</v>
-      </c>
-      <c r="P31" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>142</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -2932,40 +3270,28 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>135</v>
-      </c>
-      <c r="C32" t="s">
-        <v>143</v>
+        <v>403</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F32" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I32" t="s">
-        <v>143</v>
+        <v>254</v>
       </c>
       <c r="J32" t="s">
-        <v>138</v>
+        <v>403</v>
       </c>
       <c r="L32" t="s">
-        <v>139</v>
+        <v>406</v>
       </c>
       <c r="M32" t="s">
-        <v>140</v>
+        <v>412</v>
       </c>
       <c r="N32" t="s">
-        <v>141</v>
-      </c>
-      <c r="O32" t="s">
-        <v>144</v>
-      </c>
-      <c r="P32" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>144</v>
+        <v>411</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -2973,40 +3299,28 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>135</v>
-      </c>
-      <c r="C33" t="s">
-        <v>145</v>
+        <v>258</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F33" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I33" t="s">
-        <v>145</v>
+        <v>254</v>
       </c>
       <c r="J33" t="s">
-        <v>138</v>
+        <v>258</v>
       </c>
       <c r="L33" t="s">
-        <v>139</v>
+        <v>259</v>
       </c>
       <c r="M33" t="s">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="N33" t="s">
-        <v>141</v>
-      </c>
-      <c r="O33" t="s">
-        <v>146</v>
-      </c>
-      <c r="P33" t="s">
-        <v>146</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>146</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -3014,40 +3328,28 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>135</v>
-      </c>
-      <c r="C34" t="s">
-        <v>147</v>
+        <v>404</v>
       </c>
       <c r="E34" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F34" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I34" t="s">
-        <v>147</v>
+        <v>254</v>
       </c>
       <c r="J34" t="s">
-        <v>138</v>
+        <v>404</v>
       </c>
       <c r="L34" t="s">
-        <v>139</v>
+        <v>407</v>
       </c>
       <c r="M34" t="s">
-        <v>140</v>
+        <v>413</v>
       </c>
       <c r="N34" t="s">
-        <v>141</v>
-      </c>
-      <c r="O34" t="s">
-        <v>148</v>
-      </c>
-      <c r="P34" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>148</v>
+        <v>410</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -3055,40 +3357,28 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>135</v>
-      </c>
-      <c r="C35" t="s">
-        <v>149</v>
+        <v>262</v>
       </c>
       <c r="E35" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F35" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I35" t="s">
-        <v>149</v>
+        <v>254</v>
       </c>
       <c r="J35" t="s">
-        <v>138</v>
+        <v>262</v>
       </c>
       <c r="L35" t="s">
-        <v>139</v>
+        <v>263</v>
       </c>
       <c r="M35" t="s">
-        <v>140</v>
+        <v>260</v>
       </c>
       <c r="N35" t="s">
-        <v>141</v>
-      </c>
-      <c r="O35" t="s">
-        <v>150</v>
-      </c>
-      <c r="P35" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>150</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -3096,40 +3386,28 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>135</v>
-      </c>
-      <c r="C36" t="s">
-        <v>151</v>
+        <v>405</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F36" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I36" t="s">
-        <v>151</v>
+        <v>254</v>
       </c>
       <c r="J36" t="s">
-        <v>138</v>
+        <v>405</v>
       </c>
       <c r="L36" t="s">
-        <v>139</v>
+        <v>408</v>
       </c>
       <c r="M36" t="s">
-        <v>140</v>
+        <v>414</v>
       </c>
       <c r="N36" t="s">
-        <v>141</v>
-      </c>
-      <c r="O36" t="s">
-        <v>152</v>
-      </c>
-      <c r="P36" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>152</v>
+        <v>409</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -3137,40 +3415,25 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>135</v>
-      </c>
-      <c r="C37" t="s">
-        <v>153</v>
+        <v>268</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>137</v>
-      </c>
-      <c r="I37" t="s">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="J37" t="s">
-        <v>138</v>
+        <v>456</v>
       </c>
       <c r="L37" t="s">
-        <v>139</v>
+        <v>433</v>
       </c>
       <c r="M37" t="s">
-        <v>140</v>
+        <v>435</v>
       </c>
       <c r="N37" t="s">
-        <v>141</v>
-      </c>
-      <c r="O37" t="s">
-        <v>154</v>
-      </c>
-      <c r="P37" t="s">
-        <v>154</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>154</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -3178,40 +3441,25 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>135</v>
-      </c>
-      <c r="C38" t="s">
-        <v>155</v>
+        <v>398</v>
       </c>
       <c r="E38" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F38" t="s">
-        <v>137</v>
-      </c>
-      <c r="I38" t="s">
-        <v>155</v>
+        <v>54</v>
       </c>
       <c r="J38" t="s">
-        <v>138</v>
+        <v>457</v>
       </c>
       <c r="L38" t="s">
-        <v>139</v>
+        <v>434</v>
       </c>
       <c r="M38" t="s">
-        <v>140</v>
+        <v>436</v>
       </c>
       <c r="N38" t="s">
-        <v>141</v>
-      </c>
-      <c r="O38" t="s">
-        <v>156</v>
-      </c>
-      <c r="P38" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>156</v>
+        <v>438</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -3219,40 +3467,28 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>135</v>
-      </c>
-      <c r="C39" t="s">
-        <v>157</v>
+        <v>267</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F39" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I39" t="s">
-        <v>157</v>
+        <v>254</v>
       </c>
       <c r="J39" t="s">
-        <v>138</v>
+        <v>267</v>
       </c>
       <c r="L39" t="s">
-        <v>139</v>
+        <v>439</v>
       </c>
       <c r="M39" t="s">
-        <v>140</v>
+        <v>450</v>
       </c>
       <c r="N39" t="s">
-        <v>141</v>
-      </c>
-      <c r="O39" t="s">
-        <v>158</v>
-      </c>
-      <c r="P39" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>158</v>
+        <v>444</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -3260,40 +3496,28 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>135</v>
-      </c>
-      <c r="C40" t="s">
-        <v>159</v>
+        <v>400</v>
       </c>
       <c r="E40" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F40" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I40" t="s">
-        <v>159</v>
+        <v>254</v>
       </c>
       <c r="J40" t="s">
-        <v>138</v>
+        <v>400</v>
       </c>
       <c r="L40" t="s">
-        <v>139</v>
+        <v>443</v>
       </c>
       <c r="M40" t="s">
-        <v>140</v>
+        <v>451</v>
       </c>
       <c r="N40" t="s">
-        <v>141</v>
-      </c>
-      <c r="O40" t="s">
-        <v>160</v>
-      </c>
-      <c r="P40" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>162</v>
+        <v>445</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -3301,40 +3525,28 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>135</v>
-      </c>
-      <c r="C41" t="s">
-        <v>163</v>
+        <v>266</v>
       </c>
       <c r="E41" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F41" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I41" t="s">
-        <v>163</v>
+        <v>254</v>
       </c>
       <c r="J41" t="s">
-        <v>138</v>
+        <v>266</v>
       </c>
       <c r="L41" t="s">
-        <v>139</v>
+        <v>440</v>
       </c>
       <c r="M41" t="s">
-        <v>140</v>
+        <v>452</v>
       </c>
       <c r="N41" t="s">
-        <v>141</v>
-      </c>
-      <c r="O41" t="s">
-        <v>164</v>
-      </c>
-      <c r="P41" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>166</v>
+        <v>446</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -3342,28 +3554,28 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>167</v>
+        <v>401</v>
       </c>
       <c r="E42" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F42" t="s">
-        <v>168</v>
-      </c>
-      <c r="G42" t="b">
-        <v>1</v>
-      </c>
-      <c r="H42" t="s">
-        <v>135</v>
+        <v>54</v>
+      </c>
+      <c r="I42" t="s">
+        <v>254</v>
+      </c>
+      <c r="J42" t="s">
+        <v>401</v>
       </c>
       <c r="L42" t="s">
-        <v>169</v>
+        <v>442</v>
       </c>
       <c r="M42" t="s">
-        <v>170</v>
+        <v>453</v>
       </c>
       <c r="N42" t="s">
-        <v>171</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -3371,40 +3583,28 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>172</v>
-      </c>
-      <c r="C43" t="s">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="E43" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F43" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I43" t="s">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="J43" t="s">
-        <v>175</v>
+        <v>265</v>
       </c>
       <c r="L43" t="s">
-        <v>176</v>
+        <v>415</v>
       </c>
       <c r="M43" t="s">
-        <v>177</v>
+        <v>454</v>
       </c>
       <c r="N43" t="s">
-        <v>178</v>
-      </c>
-      <c r="O43" t="s">
-        <v>179</v>
-      </c>
-      <c r="P43" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>179</v>
+        <v>448</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -3412,40 +3612,28 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>172</v>
-      </c>
-      <c r="C44" t="s">
-        <v>180</v>
+        <v>402</v>
       </c>
       <c r="E44" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F44" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I44" t="s">
-        <v>181</v>
+        <v>254</v>
       </c>
       <c r="J44" t="s">
-        <v>175</v>
+        <v>402</v>
       </c>
       <c r="L44" t="s">
-        <v>176</v>
+        <v>441</v>
       </c>
       <c r="M44" t="s">
-        <v>177</v>
+        <v>455</v>
       </c>
       <c r="N44" t="s">
-        <v>178</v>
-      </c>
-      <c r="O44" t="s">
-        <v>182</v>
-      </c>
-      <c r="P44" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>182</v>
+        <v>449</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -3453,40 +3641,40 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>172</v>
+        <v>397</v>
       </c>
       <c r="C45" t="s">
-        <v>183</v>
+        <v>297</v>
       </c>
       <c r="E45" t="s">
         <v>20</v>
       </c>
       <c r="F45" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I45" t="s">
-        <v>184</v>
+        <v>297</v>
       </c>
       <c r="J45" t="s">
-        <v>175</v>
+        <v>397</v>
       </c>
       <c r="L45" t="s">
-        <v>176</v>
+        <v>427</v>
       </c>
       <c r="M45" t="s">
-        <v>177</v>
+        <v>431</v>
       </c>
       <c r="N45" t="s">
-        <v>178</v>
+        <v>429</v>
       </c>
       <c r="O45" t="s">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="P45" t="s">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="Q45" t="s">
-        <v>185</v>
+        <v>421</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -3494,40 +3682,40 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
+        <v>397</v>
       </c>
       <c r="C46" t="s">
-        <v>186</v>
+        <v>296</v>
       </c>
       <c r="E46" t="s">
         <v>20</v>
       </c>
       <c r="F46" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I46" t="s">
-        <v>187</v>
+        <v>296</v>
       </c>
       <c r="J46" t="s">
-        <v>175</v>
+        <v>397</v>
       </c>
       <c r="L46" t="s">
-        <v>176</v>
+        <v>427</v>
       </c>
       <c r="M46" t="s">
-        <v>177</v>
+        <v>431</v>
       </c>
       <c r="N46" t="s">
-        <v>178</v>
+        <v>429</v>
       </c>
       <c r="O46" t="s">
-        <v>188</v>
+        <v>416</v>
       </c>
       <c r="P46" t="s">
-        <v>188</v>
+        <v>416</v>
       </c>
       <c r="Q46" t="s">
-        <v>188</v>
+        <v>422</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -3535,40 +3723,40 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>172</v>
+        <v>397</v>
       </c>
       <c r="C47" t="s">
-        <v>189</v>
+        <v>295</v>
       </c>
       <c r="E47" t="s">
         <v>20</v>
       </c>
       <c r="F47" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I47" t="s">
-        <v>190</v>
+        <v>295</v>
       </c>
       <c r="J47" t="s">
-        <v>175</v>
+        <v>397</v>
       </c>
       <c r="L47" t="s">
-        <v>176</v>
+        <v>427</v>
       </c>
       <c r="M47" t="s">
-        <v>177</v>
+        <v>431</v>
       </c>
       <c r="N47" t="s">
-        <v>178</v>
+        <v>429</v>
       </c>
       <c r="O47" t="s">
-        <v>191</v>
+        <v>417</v>
       </c>
       <c r="P47" t="s">
-        <v>191</v>
+        <v>417</v>
       </c>
       <c r="Q47" t="s">
-        <v>191</v>
+        <v>423</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -3576,40 +3764,40 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>172</v>
+        <v>399</v>
       </c>
       <c r="C48" t="s">
-        <v>192</v>
+        <v>297</v>
       </c>
       <c r="E48" t="s">
         <v>20</v>
       </c>
       <c r="F48" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I48" t="s">
-        <v>193</v>
+        <v>297</v>
       </c>
       <c r="J48" t="s">
-        <v>175</v>
+        <v>399</v>
       </c>
       <c r="L48" t="s">
-        <v>176</v>
+        <v>428</v>
       </c>
       <c r="M48" t="s">
-        <v>177</v>
+        <v>432</v>
       </c>
       <c r="N48" t="s">
-        <v>178</v>
+        <v>430</v>
       </c>
       <c r="O48" t="s">
-        <v>194</v>
+        <v>418</v>
       </c>
       <c r="P48" t="s">
-        <v>194</v>
+        <v>418</v>
       </c>
       <c r="Q48" t="s">
-        <v>194</v>
+        <v>424</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -3617,40 +3805,40 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>172</v>
+        <v>399</v>
       </c>
       <c r="C49" t="s">
-        <v>195</v>
+        <v>296</v>
       </c>
       <c r="E49" t="s">
         <v>20</v>
       </c>
       <c r="F49" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I49" t="s">
-        <v>195</v>
+        <v>296</v>
       </c>
       <c r="J49" t="s">
-        <v>175</v>
+        <v>399</v>
       </c>
       <c r="L49" t="s">
-        <v>176</v>
+        <v>428</v>
       </c>
       <c r="M49" t="s">
-        <v>177</v>
+        <v>432</v>
       </c>
       <c r="N49" t="s">
-        <v>178</v>
+        <v>430</v>
       </c>
       <c r="O49" t="s">
-        <v>196</v>
+        <v>419</v>
       </c>
       <c r="P49" t="s">
-        <v>196</v>
+        <v>419</v>
       </c>
       <c r="Q49" t="s">
-        <v>196</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -3658,40 +3846,40 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>172</v>
+        <v>399</v>
       </c>
       <c r="C50" t="s">
-        <v>197</v>
+        <v>295</v>
       </c>
       <c r="E50" t="s">
         <v>20</v>
       </c>
       <c r="F50" t="s">
-        <v>137</v>
+        <v>54</v>
       </c>
       <c r="I50" t="s">
-        <v>197</v>
+        <v>295</v>
       </c>
       <c r="J50" t="s">
-        <v>175</v>
+        <v>399</v>
       </c>
       <c r="L50" t="s">
-        <v>176</v>
+        <v>428</v>
       </c>
       <c r="M50" t="s">
-        <v>177</v>
+        <v>432</v>
       </c>
       <c r="N50" t="s">
-        <v>178</v>
+        <v>430</v>
       </c>
       <c r="O50" t="s">
-        <v>198</v>
+        <v>420</v>
       </c>
       <c r="P50" t="s">
-        <v>198</v>
+        <v>420</v>
       </c>
       <c r="Q50" t="s">
-        <v>198</v>
+        <v>426</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -3699,40 +3887,40 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="C51" t="s">
-        <v>134</v>
+        <v>65</v>
       </c>
       <c r="E51" t="s">
         <v>20</v>
       </c>
       <c r="F51" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I51" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J51" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="L51" t="s">
-        <v>176</v>
+        <v>92</v>
       </c>
       <c r="M51" t="s">
-        <v>177</v>
+        <v>93</v>
       </c>
       <c r="N51" t="s">
-        <v>178</v>
+        <v>94</v>
       </c>
       <c r="O51" t="s">
-        <v>123</v>
+        <v>70</v>
       </c>
       <c r="P51" t="s">
-        <v>124</v>
+        <v>71</v>
       </c>
       <c r="Q51" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -3740,40 +3928,40 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>159</v>
+        <v>73</v>
       </c>
       <c r="E52" t="s">
         <v>20</v>
       </c>
       <c r="F52" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I52" t="s">
-        <v>199</v>
+        <v>95</v>
       </c>
       <c r="J52" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="L52" t="s">
-        <v>176</v>
+        <v>92</v>
       </c>
       <c r="M52" t="s">
-        <v>177</v>
+        <v>93</v>
       </c>
       <c r="N52" t="s">
-        <v>178</v>
+        <v>94</v>
       </c>
       <c r="O52" t="s">
-        <v>160</v>
+        <v>74</v>
       </c>
       <c r="P52" t="s">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="Q52" t="s">
-        <v>162</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -3781,31 +3969,40 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>200</v>
+        <v>96</v>
+      </c>
+      <c r="C53" t="s">
+        <v>65</v>
       </c>
       <c r="E53" t="s">
         <v>20</v>
       </c>
       <c r="F53" t="s">
-        <v>168</v>
-      </c>
-      <c r="G53" t="b">
-        <v>1</v>
-      </c>
-      <c r="H53" t="s">
-        <v>172</v>
+        <v>32</v>
+      </c>
+      <c r="I53" t="s">
+        <v>91</v>
       </c>
       <c r="J53" t="s">
-        <v>200</v>
+        <v>96</v>
       </c>
       <c r="L53" t="s">
-        <v>201</v>
+        <v>97</v>
       </c>
       <c r="M53" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="N53" t="s">
-        <v>203</v>
+        <v>99</v>
+      </c>
+      <c r="O53" t="s">
+        <v>70</v>
+      </c>
+      <c r="P53" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -3813,40 +4010,40 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>204</v>
+        <v>96</v>
       </c>
       <c r="C54" t="s">
-        <v>205</v>
+        <v>73</v>
       </c>
       <c r="E54" t="s">
         <v>20</v>
       </c>
       <c r="F54" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I54" t="s">
-        <v>205</v>
+        <v>95</v>
       </c>
       <c r="J54" t="s">
-        <v>204</v>
+        <v>96</v>
       </c>
       <c r="L54" t="s">
-        <v>206</v>
+        <v>97</v>
       </c>
       <c r="M54" t="s">
-        <v>207</v>
+        <v>98</v>
       </c>
       <c r="N54" t="s">
-        <v>208</v>
+        <v>99</v>
       </c>
       <c r="O54" t="s">
-        <v>209</v>
+        <v>74</v>
       </c>
       <c r="P54" t="s">
-        <v>209</v>
+        <v>75</v>
       </c>
       <c r="Q54" t="s">
-        <v>209</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -3854,40 +4051,40 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="C55" t="s">
-        <v>210</v>
+        <v>101</v>
       </c>
       <c r="E55" t="s">
         <v>20</v>
       </c>
       <c r="F55" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I55" t="s">
-        <v>210</v>
+        <v>102</v>
       </c>
       <c r="J55" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="L55" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="M55" t="s">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="N55" t="s">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="O55" t="s">
-        <v>211</v>
+        <v>106</v>
       </c>
       <c r="P55" t="s">
-        <v>211</v>
+        <v>107</v>
       </c>
       <c r="Q55" t="s">
-        <v>211</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -3895,40 +4092,40 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="C56" t="s">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="E56" t="s">
         <v>20</v>
       </c>
       <c r="F56" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I56" t="s">
-        <v>212</v>
+        <v>109</v>
       </c>
       <c r="J56" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="L56" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="M56" t="s">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="N56" t="s">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="O56" t="s">
-        <v>213</v>
+        <v>110</v>
       </c>
       <c r="P56" t="s">
-        <v>213</v>
+        <v>111</v>
       </c>
       <c r="Q56" t="s">
-        <v>213</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -3936,40 +4133,40 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="C57" t="s">
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="E57" t="s">
         <v>20</v>
       </c>
       <c r="F57" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I57" t="s">
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="J57" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="L57" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="M57" t="s">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="N57" t="s">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="O57" t="s">
-        <v>215</v>
+        <v>114</v>
       </c>
       <c r="P57" t="s">
-        <v>215</v>
+        <v>115</v>
       </c>
       <c r="Q57" t="s">
-        <v>215</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -3977,40 +4174,40 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="C58" t="s">
-        <v>216</v>
+        <v>117</v>
       </c>
       <c r="E58" t="s">
         <v>20</v>
       </c>
       <c r="F58" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I58" t="s">
-        <v>216</v>
+        <v>117</v>
       </c>
       <c r="J58" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="L58" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="M58" t="s">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="N58" t="s">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="O58" t="s">
-        <v>217</v>
+        <v>118</v>
       </c>
       <c r="P58" t="s">
-        <v>217</v>
+        <v>119</v>
       </c>
       <c r="Q58" t="s">
-        <v>217</v>
+        <v>120</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -4018,40 +4215,40 @@
         <v>1</v>
       </c>
       <c r="B59" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="C59" t="s">
-        <v>218</v>
+        <v>121</v>
       </c>
       <c r="E59" t="s">
         <v>20</v>
       </c>
       <c r="F59" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I59" t="s">
-        <v>218</v>
+        <v>122</v>
       </c>
       <c r="J59" t="s">
-        <v>204</v>
+        <v>100</v>
       </c>
       <c r="L59" t="s">
-        <v>206</v>
+        <v>103</v>
       </c>
       <c r="M59" t="s">
-        <v>207</v>
+        <v>104</v>
       </c>
       <c r="N59" t="s">
-        <v>208</v>
+        <v>105</v>
       </c>
       <c r="O59" t="s">
-        <v>219</v>
+        <v>123</v>
       </c>
       <c r="P59" t="s">
-        <v>219</v>
+        <v>124</v>
       </c>
       <c r="Q59" t="s">
-        <v>219</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -4059,40 +4256,40 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>204</v>
+        <v>126</v>
       </c>
       <c r="C60" t="s">
-        <v>220</v>
+        <v>65</v>
       </c>
       <c r="E60" t="s">
         <v>20</v>
       </c>
       <c r="F60" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I60" t="s">
-        <v>220</v>
+        <v>91</v>
       </c>
       <c r="J60" t="s">
-        <v>204</v>
+        <v>126</v>
       </c>
       <c r="L60" t="s">
-        <v>206</v>
+        <v>127</v>
       </c>
       <c r="M60" t="s">
-        <v>207</v>
+        <v>128</v>
       </c>
       <c r="N60" t="s">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="O60" t="s">
-        <v>221</v>
+        <v>70</v>
       </c>
       <c r="P60" t="s">
-        <v>221</v>
+        <v>71</v>
       </c>
       <c r="Q60" t="s">
-        <v>221</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -4100,40 +4297,40 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>204</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="E61" t="s">
         <v>20</v>
       </c>
       <c r="F61" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I61" t="s">
-        <v>222</v>
+        <v>95</v>
       </c>
       <c r="J61" t="s">
-        <v>204</v>
+        <v>126</v>
       </c>
       <c r="L61" t="s">
-        <v>206</v>
+        <v>127</v>
       </c>
       <c r="M61" t="s">
-        <v>207</v>
+        <v>128</v>
       </c>
       <c r="N61" t="s">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="O61" t="s">
-        <v>223</v>
+        <v>74</v>
       </c>
       <c r="P61" t="s">
-        <v>223</v>
+        <v>75</v>
       </c>
       <c r="Q61" t="s">
-        <v>223</v>
+        <v>76</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -4141,40 +4338,40 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>159</v>
+        <v>65</v>
       </c>
       <c r="E62" t="s">
         <v>20</v>
       </c>
       <c r="F62" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I62" t="s">
-        <v>199</v>
+        <v>91</v>
       </c>
       <c r="J62" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="L62" t="s">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="M62" t="s">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="N62" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="O62" t="s">
-        <v>160</v>
+        <v>70</v>
       </c>
       <c r="P62" t="s">
-        <v>161</v>
+        <v>71</v>
       </c>
       <c r="Q62" t="s">
-        <v>162</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -4182,40 +4379,40 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="C63" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="E63" t="s">
         <v>20</v>
       </c>
       <c r="F63" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I63" t="s">
-        <v>224</v>
+        <v>95</v>
       </c>
       <c r="J63" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="L63" t="s">
-        <v>206</v>
+        <v>131</v>
       </c>
       <c r="M63" t="s">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="N63" t="s">
-        <v>208</v>
+        <v>133</v>
       </c>
       <c r="O63" t="s">
-        <v>164</v>
+        <v>74</v>
       </c>
       <c r="P63" t="s">
-        <v>165</v>
+        <v>75</v>
       </c>
       <c r="Q63" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -4223,31 +4420,40 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>225</v>
+        <v>130</v>
+      </c>
+      <c r="C64" t="s">
+        <v>134</v>
       </c>
       <c r="E64" t="s">
         <v>20</v>
       </c>
       <c r="F64" t="s">
-        <v>168</v>
-      </c>
-      <c r="G64" t="b">
-        <v>1</v>
-      </c>
-      <c r="H64" t="s">
-        <v>204</v>
+        <v>32</v>
+      </c>
+      <c r="I64" t="s">
+        <v>122</v>
       </c>
       <c r="J64" t="s">
-        <v>225</v>
+        <v>130</v>
       </c>
       <c r="L64" t="s">
-        <v>226</v>
+        <v>131</v>
       </c>
       <c r="M64" t="s">
-        <v>227</v>
+        <v>132</v>
       </c>
       <c r="N64" t="s">
-        <v>228</v>
+        <v>133</v>
+      </c>
+      <c r="O64" t="s">
+        <v>123</v>
+      </c>
+      <c r="P64" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -4255,40 +4461,40 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>229</v>
+        <v>135</v>
       </c>
       <c r="C65" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
       <c r="E65" t="s">
         <v>20</v>
       </c>
       <c r="F65" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I65" t="s">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="J65" t="s">
-        <v>229</v>
+        <v>138</v>
       </c>
       <c r="L65" t="s">
-        <v>230</v>
+        <v>139</v>
       </c>
       <c r="M65" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="N65" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="O65" t="s">
-        <v>70</v>
+        <v>142</v>
       </c>
       <c r="P65" t="s">
-        <v>71</v>
+        <v>142</v>
       </c>
       <c r="Q65" t="s">
-        <v>72</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -4296,40 +4502,40 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>229</v>
+        <v>135</v>
       </c>
       <c r="C66" t="s">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="E66" t="s">
         <v>20</v>
       </c>
       <c r="F66" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I66" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="J66" t="s">
-        <v>229</v>
+        <v>138</v>
       </c>
       <c r="L66" t="s">
-        <v>230</v>
+        <v>139</v>
       </c>
       <c r="M66" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="N66" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="O66" t="s">
-        <v>74</v>
+        <v>144</v>
       </c>
       <c r="P66" t="s">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="Q66" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -4337,40 +4543,40 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>229</v>
+        <v>135</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E67" t="s">
         <v>20</v>
       </c>
       <c r="F67" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I67" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="J67" t="s">
-        <v>229</v>
+        <v>138</v>
       </c>
       <c r="L67" t="s">
-        <v>230</v>
+        <v>139</v>
       </c>
       <c r="M67" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="N67" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="O67" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="P67" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="Q67" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -4378,40 +4584,40 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>229</v>
+        <v>135</v>
       </c>
       <c r="C68" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="E68" t="s">
         <v>20</v>
       </c>
       <c r="F68" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I68" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="J68" t="s">
-        <v>229</v>
+        <v>138</v>
       </c>
       <c r="L68" t="s">
-        <v>230</v>
+        <v>139</v>
       </c>
       <c r="M68" t="s">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="N68" t="s">
-        <v>231</v>
+        <v>141</v>
       </c>
       <c r="O68" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="P68" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="Q68" t="s">
-        <v>166</v>
+        <v>148</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -4419,40 +4625,40 @@
         <v>1</v>
       </c>
       <c r="B69" t="s">
-        <v>232</v>
+        <v>135</v>
       </c>
       <c r="C69" t="s">
-        <v>65</v>
+        <v>149</v>
       </c>
       <c r="E69" t="s">
         <v>20</v>
       </c>
       <c r="F69" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I69" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="J69" t="s">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="L69" t="s">
-        <v>233</v>
+        <v>139</v>
       </c>
       <c r="M69" t="s">
-        <v>233</v>
+        <v>140</v>
       </c>
       <c r="N69" t="s">
-        <v>234</v>
+        <v>141</v>
       </c>
       <c r="O69" t="s">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="P69" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="Q69" t="s">
-        <v>72</v>
+        <v>150</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -4460,40 +4666,40 @@
         <v>1</v>
       </c>
       <c r="B70" t="s">
-        <v>232</v>
+        <v>135</v>
       </c>
       <c r="C70" t="s">
-        <v>73</v>
+        <v>151</v>
       </c>
       <c r="E70" t="s">
         <v>20</v>
       </c>
       <c r="F70" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I70" t="s">
-        <v>95</v>
+        <v>151</v>
       </c>
       <c r="J70" t="s">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="L70" t="s">
-        <v>233</v>
+        <v>139</v>
       </c>
       <c r="M70" t="s">
-        <v>233</v>
+        <v>140</v>
       </c>
       <c r="N70" t="s">
-        <v>234</v>
+        <v>141</v>
       </c>
       <c r="O70" t="s">
-        <v>74</v>
+        <v>152</v>
       </c>
       <c r="P70" t="s">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="Q70" t="s">
-        <v>76</v>
+        <v>152</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -4501,40 +4707,40 @@
         <v>1</v>
       </c>
       <c r="B71" t="s">
-        <v>232</v>
+        <v>135</v>
       </c>
       <c r="C71" t="s">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="E71" t="s">
         <v>20</v>
       </c>
       <c r="F71" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I71" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="J71" t="s">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="L71" t="s">
-        <v>233</v>
+        <v>139</v>
       </c>
       <c r="M71" t="s">
-        <v>233</v>
+        <v>140</v>
       </c>
       <c r="N71" t="s">
-        <v>234</v>
+        <v>141</v>
       </c>
       <c r="O71" t="s">
-        <v>123</v>
+        <v>154</v>
       </c>
       <c r="P71" t="s">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="Q71" t="s">
-        <v>125</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -4542,40 +4748,40 @@
         <v>1</v>
       </c>
       <c r="B72" t="s">
-        <v>232</v>
+        <v>135</v>
       </c>
       <c r="C72" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E72" t="s">
         <v>20</v>
       </c>
       <c r="F72" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I72" t="s">
-        <v>224</v>
+        <v>155</v>
       </c>
       <c r="J72" t="s">
-        <v>232</v>
+        <v>138</v>
       </c>
       <c r="L72" t="s">
-        <v>233</v>
+        <v>139</v>
       </c>
       <c r="M72" t="s">
-        <v>233</v>
+        <v>140</v>
       </c>
       <c r="N72" t="s">
-        <v>234</v>
+        <v>141</v>
       </c>
       <c r="O72" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="P72" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="Q72" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -4583,40 +4789,40 @@
         <v>1</v>
       </c>
       <c r="B73" t="s">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="C73" t="s">
-        <v>65</v>
+        <v>157</v>
       </c>
       <c r="E73" t="s">
         <v>20</v>
       </c>
       <c r="F73" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I73" t="s">
-        <v>91</v>
+        <v>157</v>
       </c>
       <c r="J73" t="s">
-        <v>235</v>
+        <v>138</v>
       </c>
       <c r="L73" t="s">
-        <v>236</v>
+        <v>139</v>
       </c>
       <c r="M73" t="s">
-        <v>236</v>
+        <v>140</v>
       </c>
       <c r="N73" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="O73" t="s">
-        <v>70</v>
+        <v>158</v>
       </c>
       <c r="P73" t="s">
-        <v>71</v>
+        <v>158</v>
       </c>
       <c r="Q73" t="s">
-        <v>72</v>
+        <v>158</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -4624,40 +4830,40 @@
         <v>1</v>
       </c>
       <c r="B74" t="s">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="C74" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="E74" t="s">
         <v>20</v>
       </c>
       <c r="F74" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I74" t="s">
-        <v>95</v>
+        <v>159</v>
       </c>
       <c r="J74" t="s">
-        <v>235</v>
+        <v>138</v>
       </c>
       <c r="L74" t="s">
-        <v>236</v>
+        <v>139</v>
       </c>
       <c r="M74" t="s">
-        <v>236</v>
+        <v>140</v>
       </c>
       <c r="N74" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="O74" t="s">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="P74" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="Q74" t="s">
-        <v>76</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -4665,40 +4871,40 @@
         <v>1</v>
       </c>
       <c r="B75" t="s">
-        <v>235</v>
+        <v>135</v>
       </c>
       <c r="C75" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E75" t="s">
         <v>20</v>
       </c>
       <c r="F75" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I75" t="s">
-        <v>122</v>
+        <v>163</v>
       </c>
       <c r="J75" t="s">
-        <v>235</v>
+        <v>138</v>
       </c>
       <c r="L75" t="s">
-        <v>236</v>
+        <v>139</v>
       </c>
       <c r="M75" t="s">
-        <v>236</v>
+        <v>140</v>
       </c>
       <c r="N75" t="s">
-        <v>237</v>
+        <v>141</v>
       </c>
       <c r="O75" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="P75" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="Q75" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -4706,40 +4912,28 @@
         <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>235</v>
-      </c>
-      <c r="C76" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="E76" t="s">
         <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>32</v>
-      </c>
-      <c r="I76" t="s">
-        <v>224</v>
-      </c>
-      <c r="J76" t="s">
-        <v>235</v>
+        <v>168</v>
+      </c>
+      <c r="G76" t="b">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
+        <v>135</v>
       </c>
       <c r="L76" t="s">
-        <v>236</v>
+        <v>169</v>
       </c>
       <c r="M76" t="s">
-        <v>236</v>
+        <v>170</v>
       </c>
       <c r="N76" t="s">
-        <v>237</v>
-      </c>
-      <c r="O76" t="s">
-        <v>164</v>
-      </c>
-      <c r="P76" t="s">
-        <v>165</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -4747,40 +4941,40 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="C77" t="s">
-        <v>65</v>
+        <v>173</v>
       </c>
       <c r="E77" t="s">
         <v>20</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I77" t="s">
-        <v>91</v>
+        <v>174</v>
       </c>
       <c r="J77" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="L77" t="s">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="M77" t="s">
-        <v>239</v>
+        <v>177</v>
       </c>
       <c r="N77" t="s">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="O77" t="s">
-        <v>70</v>
+        <v>179</v>
       </c>
       <c r="P77" t="s">
-        <v>71</v>
+        <v>179</v>
       </c>
       <c r="Q77" t="s">
-        <v>72</v>
+        <v>179</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -4788,40 +4982,40 @@
         <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="C78" t="s">
-        <v>73</v>
+        <v>180</v>
       </c>
       <c r="E78" t="s">
         <v>20</v>
       </c>
       <c r="F78" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I78" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="J78" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="L78" t="s">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="M78" t="s">
-        <v>239</v>
+        <v>177</v>
       </c>
       <c r="N78" t="s">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="O78" t="s">
-        <v>74</v>
+        <v>182</v>
       </c>
       <c r="P78" t="s">
-        <v>75</v>
+        <v>182</v>
       </c>
       <c r="Q78" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -4829,40 +5023,40 @@
         <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="C79" t="s">
-        <v>134</v>
+        <v>183</v>
       </c>
       <c r="E79" t="s">
         <v>20</v>
       </c>
       <c r="F79" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I79" t="s">
-        <v>122</v>
+        <v>184</v>
       </c>
       <c r="J79" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="L79" t="s">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="M79" t="s">
-        <v>239</v>
+        <v>177</v>
       </c>
       <c r="N79" t="s">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="O79" t="s">
-        <v>123</v>
+        <v>185</v>
       </c>
       <c r="P79" t="s">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="Q79" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -4870,40 +5064,40 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="C80" t="s">
-        <v>163</v>
+        <v>186</v>
       </c>
       <c r="E80" t="s">
         <v>20</v>
       </c>
       <c r="F80" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I80" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="J80" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="L80" t="s">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="M80" t="s">
-        <v>239</v>
+        <v>177</v>
       </c>
       <c r="N80" t="s">
-        <v>240</v>
+        <v>178</v>
       </c>
       <c r="O80" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="P80" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="Q80" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -4911,40 +5105,40 @@
         <v>1</v>
       </c>
       <c r="B81" t="s">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="C81" t="s">
-        <v>65</v>
+        <v>189</v>
       </c>
       <c r="E81" t="s">
         <v>20</v>
       </c>
       <c r="F81" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I81" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="J81" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="L81" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="M81" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="N81" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
       <c r="O81" t="s">
-        <v>70</v>
+        <v>191</v>
       </c>
       <c r="P81" t="s">
-        <v>71</v>
+        <v>191</v>
       </c>
       <c r="Q81" t="s">
-        <v>72</v>
+        <v>191</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -4952,40 +5146,40 @@
         <v>1</v>
       </c>
       <c r="B82" t="s">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="E82" t="s">
         <v>20</v>
       </c>
       <c r="F82" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I82" t="s">
-        <v>95</v>
+        <v>193</v>
       </c>
       <c r="J82" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="L82" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="M82" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="N82" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
       <c r="O82" t="s">
-        <v>74</v>
+        <v>194</v>
       </c>
       <c r="P82" t="s">
-        <v>75</v>
+        <v>194</v>
       </c>
       <c r="Q82" t="s">
-        <v>76</v>
+        <v>194</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -4993,40 +5187,40 @@
         <v>1</v>
       </c>
       <c r="B83" t="s">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>134</v>
+        <v>195</v>
       </c>
       <c r="E83" t="s">
         <v>20</v>
       </c>
       <c r="F83" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I83" t="s">
-        <v>122</v>
+        <v>195</v>
       </c>
       <c r="J83" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="L83" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="M83" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="N83" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
       <c r="O83" t="s">
-        <v>123</v>
+        <v>196</v>
       </c>
       <c r="P83" t="s">
-        <v>124</v>
+        <v>196</v>
       </c>
       <c r="Q83" t="s">
-        <v>125</v>
+        <v>196</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -5034,40 +5228,40 @@
         <v>1</v>
       </c>
       <c r="B84" t="s">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="C84" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="E84" t="s">
         <v>20</v>
       </c>
       <c r="F84" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I84" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="J84" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="L84" t="s">
-        <v>242</v>
+        <v>176</v>
       </c>
       <c r="M84" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="N84" t="s">
-        <v>243</v>
+        <v>178</v>
       </c>
       <c r="O84" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="P84" t="s">
-        <v>165</v>
+        <v>198</v>
       </c>
       <c r="Q84" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -5075,40 +5269,40 @@
         <v>1</v>
       </c>
       <c r="B85" t="s">
-        <v>244</v>
+        <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>65</v>
+        <v>134</v>
       </c>
       <c r="E85" t="s">
         <v>20</v>
       </c>
       <c r="F85" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I85" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J85" t="s">
-        <v>244</v>
+        <v>175</v>
       </c>
       <c r="L85" t="s">
-        <v>245</v>
+        <v>176</v>
       </c>
       <c r="M85" t="s">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="N85" t="s">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="O85" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="P85" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="Q85" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -5116,40 +5310,40 @@
         <v>1</v>
       </c>
       <c r="B86" t="s">
-        <v>244</v>
+        <v>172</v>
       </c>
       <c r="C86" t="s">
-        <v>73</v>
+        <v>159</v>
       </c>
       <c r="E86" t="s">
         <v>20</v>
       </c>
       <c r="F86" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I86" t="s">
-        <v>95</v>
+        <v>199</v>
       </c>
       <c r="J86" t="s">
-        <v>244</v>
+        <v>175</v>
       </c>
       <c r="L86" t="s">
-        <v>245</v>
+        <v>176</v>
       </c>
       <c r="M86" t="s">
-        <v>245</v>
+        <v>177</v>
       </c>
       <c r="N86" t="s">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="O86" t="s">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="P86" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="Q86" t="s">
-        <v>76</v>
+        <v>162</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -5157,40 +5351,31 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>244</v>
-      </c>
-      <c r="C87" t="s">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="E87" t="s">
         <v>20</v>
       </c>
       <c r="F87" t="s">
-        <v>32</v>
-      </c>
-      <c r="I87" t="s">
-        <v>122</v>
+        <v>168</v>
+      </c>
+      <c r="G87" t="b">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
+        <v>172</v>
       </c>
       <c r="J87" t="s">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="L87" t="s">
-        <v>245</v>
+        <v>201</v>
       </c>
       <c r="M87" t="s">
-        <v>245</v>
+        <v>202</v>
       </c>
       <c r="N87" t="s">
-        <v>246</v>
-      </c>
-      <c r="O87" t="s">
-        <v>123</v>
-      </c>
-      <c r="P87" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>125</v>
+        <v>203</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -5198,40 +5383,40 @@
         <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="C88" t="s">
-        <v>163</v>
+        <v>205</v>
       </c>
       <c r="E88" t="s">
         <v>20</v>
       </c>
       <c r="F88" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I88" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="J88" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="L88" t="s">
-        <v>245</v>
+        <v>206</v>
       </c>
       <c r="M88" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
       <c r="N88" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="O88" t="s">
-        <v>164</v>
+        <v>209</v>
       </c>
       <c r="P88" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="Q88" t="s">
-        <v>166</v>
+        <v>209</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -5239,40 +5424,40 @@
         <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="C89" t="s">
-        <v>65</v>
+        <v>210</v>
       </c>
       <c r="E89" t="s">
         <v>20</v>
       </c>
       <c r="F89" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I89" t="s">
-        <v>91</v>
+        <v>210</v>
       </c>
       <c r="J89" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="L89" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="M89" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="N89" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="O89" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="P89" t="s">
-        <v>71</v>
+        <v>211</v>
       </c>
       <c r="Q89" t="s">
-        <v>72</v>
+        <v>211</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -5280,40 +5465,40 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="C90" t="s">
-        <v>73</v>
+        <v>212</v>
       </c>
       <c r="E90" t="s">
         <v>20</v>
       </c>
       <c r="F90" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I90" t="s">
-        <v>95</v>
+        <v>212</v>
       </c>
       <c r="J90" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="L90" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="M90" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="N90" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="O90" t="s">
-        <v>74</v>
+        <v>213</v>
       </c>
       <c r="P90" t="s">
-        <v>75</v>
+        <v>213</v>
       </c>
       <c r="Q90" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -5321,40 +5506,40 @@
         <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="C91" t="s">
-        <v>134</v>
+        <v>214</v>
       </c>
       <c r="E91" t="s">
         <v>20</v>
       </c>
       <c r="F91" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I91" t="s">
-        <v>122</v>
+        <v>214</v>
       </c>
       <c r="J91" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="L91" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="M91" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="N91" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="O91" t="s">
-        <v>123</v>
+        <v>215</v>
       </c>
       <c r="P91" t="s">
-        <v>124</v>
+        <v>215</v>
       </c>
       <c r="Q91" t="s">
-        <v>125</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -5362,40 +5547,40 @@
         <v>1</v>
       </c>
       <c r="B92" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="C92" t="s">
-        <v>163</v>
+        <v>216</v>
       </c>
       <c r="E92" t="s">
         <v>20</v>
       </c>
       <c r="F92" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I92" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="J92" t="s">
-        <v>247</v>
+        <v>204</v>
       </c>
       <c r="L92" t="s">
-        <v>248</v>
+        <v>206</v>
       </c>
       <c r="M92" t="s">
-        <v>248</v>
+        <v>207</v>
       </c>
       <c r="N92" t="s">
-        <v>249</v>
+        <v>208</v>
       </c>
       <c r="O92" t="s">
-        <v>164</v>
+        <v>217</v>
       </c>
       <c r="P92" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="Q92" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -5403,40 +5588,40 @@
         <v>1</v>
       </c>
       <c r="B93" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="C93" t="s">
-        <v>65</v>
+        <v>218</v>
       </c>
       <c r="E93" t="s">
         <v>20</v>
       </c>
       <c r="F93" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I93" t="s">
-        <v>91</v>
+        <v>218</v>
       </c>
       <c r="J93" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="L93" t="s">
-        <v>251</v>
+        <v>206</v>
       </c>
       <c r="M93" t="s">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="N93" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="O93" t="s">
-        <v>70</v>
+        <v>219</v>
       </c>
       <c r="P93" t="s">
-        <v>71</v>
+        <v>219</v>
       </c>
       <c r="Q93" t="s">
-        <v>72</v>
+        <v>219</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -5444,40 +5629,40 @@
         <v>1</v>
       </c>
       <c r="B94" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="C94" t="s">
-        <v>73</v>
+        <v>220</v>
       </c>
       <c r="E94" t="s">
         <v>20</v>
       </c>
       <c r="F94" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I94" t="s">
-        <v>95</v>
+        <v>220</v>
       </c>
       <c r="J94" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="L94" t="s">
-        <v>251</v>
+        <v>206</v>
       </c>
       <c r="M94" t="s">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="N94" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="O94" t="s">
-        <v>74</v>
+        <v>221</v>
       </c>
       <c r="P94" t="s">
-        <v>75</v>
+        <v>221</v>
       </c>
       <c r="Q94" t="s">
-        <v>76</v>
+        <v>221</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -5485,40 +5670,40 @@
         <v>1</v>
       </c>
       <c r="B95" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="C95" t="s">
-        <v>134</v>
+        <v>222</v>
       </c>
       <c r="E95" t="s">
         <v>20</v>
       </c>
       <c r="F95" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I95" t="s">
-        <v>122</v>
+        <v>222</v>
       </c>
       <c r="J95" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="L95" t="s">
-        <v>251</v>
+        <v>206</v>
       </c>
       <c r="M95" t="s">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="N95" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="O95" t="s">
-        <v>123</v>
+        <v>223</v>
       </c>
       <c r="P95" t="s">
-        <v>124</v>
+        <v>223</v>
       </c>
       <c r="Q95" t="s">
-        <v>125</v>
+        <v>223</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -5526,40 +5711,40 @@
         <v>1</v>
       </c>
       <c r="B96" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="C96" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E96" t="s">
         <v>20</v>
       </c>
       <c r="F96" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I96" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="J96" t="s">
-        <v>250</v>
+        <v>204</v>
       </c>
       <c r="L96" t="s">
-        <v>251</v>
+        <v>206</v>
       </c>
       <c r="M96" t="s">
-        <v>251</v>
+        <v>207</v>
       </c>
       <c r="N96" t="s">
-        <v>252</v>
+        <v>208</v>
       </c>
       <c r="O96" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="P96" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="Q96" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -5567,28 +5752,40 @@
         <v>1</v>
       </c>
       <c r="B97" t="s">
-        <v>253</v>
+        <v>204</v>
+      </c>
+      <c r="C97" t="s">
+        <v>163</v>
       </c>
       <c r="E97" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F97" t="s">
-        <v>54</v>
+        <v>137</v>
       </c>
       <c r="I97" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="J97" t="s">
-        <v>253</v>
+        <v>204</v>
       </c>
       <c r="L97" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="M97" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="N97" t="s">
-        <v>257</v>
+        <v>208</v>
+      </c>
+      <c r="O97" t="s">
+        <v>164</v>
+      </c>
+      <c r="P97" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -5596,28 +5793,31 @@
         <v>1</v>
       </c>
       <c r="B98" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="E98" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F98" t="s">
-        <v>54</v>
-      </c>
-      <c r="I98" t="s">
-        <v>254</v>
+        <v>168</v>
+      </c>
+      <c r="G98" t="b">
+        <v>1</v>
+      </c>
+      <c r="H98" t="s">
+        <v>204</v>
       </c>
       <c r="J98" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="L98" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="M98" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="N98" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -5625,28 +5825,40 @@
         <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>262</v>
+        <v>229</v>
+      </c>
+      <c r="C99" t="s">
+        <v>65</v>
       </c>
       <c r="E99" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F99" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I99" t="s">
-        <v>254</v>
+        <v>91</v>
       </c>
       <c r="J99" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="L99" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="M99" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="N99" t="s">
-        <v>264</v>
+        <v>231</v>
+      </c>
+      <c r="O99" t="s">
+        <v>70</v>
+      </c>
+      <c r="P99" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -5654,28 +5866,40 @@
         <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>265</v>
+        <v>229</v>
+      </c>
+      <c r="C100" t="s">
+        <v>73</v>
       </c>
       <c r="E100" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F100" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I100" t="s">
-        <v>254</v>
+        <v>95</v>
       </c>
       <c r="J100" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="L100" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="M100" t="s">
-        <v>267</v>
+        <v>230</v>
       </c>
       <c r="N100" t="s">
-        <v>268</v>
+        <v>231</v>
+      </c>
+      <c r="O100" t="s">
+        <v>74</v>
+      </c>
+      <c r="P100" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -5683,28 +5907,40 @@
         <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>269</v>
+        <v>229</v>
+      </c>
+      <c r="C101" t="s">
+        <v>134</v>
       </c>
       <c r="E101" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F101" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I101" t="s">
-        <v>254</v>
+        <v>122</v>
       </c>
       <c r="J101" t="s">
-        <v>269</v>
+        <v>229</v>
       </c>
       <c r="L101" t="s">
-        <v>270</v>
+        <v>230</v>
       </c>
       <c r="M101" t="s">
-        <v>271</v>
+        <v>230</v>
       </c>
       <c r="N101" t="s">
-        <v>272</v>
+        <v>231</v>
+      </c>
+      <c r="O101" t="s">
+        <v>123</v>
+      </c>
+      <c r="P101" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -5712,28 +5948,40 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>273</v>
+        <v>229</v>
+      </c>
+      <c r="C102" t="s">
+        <v>163</v>
       </c>
       <c r="E102" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F102" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I102" t="s">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="J102" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="L102" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
       <c r="M102" t="s">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="N102" t="s">
-        <v>276</v>
+        <v>231</v>
+      </c>
+      <c r="O102" t="s">
+        <v>164</v>
+      </c>
+      <c r="P102" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -5741,40 +5989,40 @@
         <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="C103" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="E103" t="s">
         <v>20</v>
       </c>
       <c r="F103" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I103" t="s">
-        <v>283</v>
+        <v>91</v>
       </c>
       <c r="J103" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="L103" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="M103" t="s">
-        <v>288</v>
+        <v>233</v>
       </c>
       <c r="N103" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="O103" t="s">
-        <v>290</v>
+        <v>70</v>
       </c>
       <c r="P103" t="s">
-        <v>298</v>
+        <v>71</v>
       </c>
       <c r="Q103" t="s">
-        <v>294</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -5782,40 +6030,40 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="C104" t="s">
-        <v>280</v>
+        <v>73</v>
       </c>
       <c r="E104" t="s">
         <v>20</v>
       </c>
       <c r="F104" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I104" t="s">
-        <v>284</v>
+        <v>95</v>
       </c>
       <c r="J104" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="L104" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="M104" t="s">
-        <v>288</v>
+        <v>233</v>
       </c>
       <c r="N104" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="O104" t="s">
-        <v>291</v>
+        <v>74</v>
       </c>
       <c r="P104" t="s">
-        <v>299</v>
+        <v>75</v>
       </c>
       <c r="Q104" t="s">
-        <v>295</v>
+        <v>76</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -5823,40 +6071,40 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="C105" t="s">
-        <v>281</v>
+        <v>134</v>
       </c>
       <c r="E105" t="s">
         <v>20</v>
       </c>
       <c r="F105" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I105" t="s">
-        <v>285</v>
+        <v>122</v>
       </c>
       <c r="J105" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="L105" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="M105" t="s">
-        <v>288</v>
+        <v>233</v>
       </c>
       <c r="N105" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="O105" t="s">
-        <v>292</v>
+        <v>123</v>
       </c>
       <c r="P105" t="s">
-        <v>300</v>
+        <v>124</v>
       </c>
       <c r="Q105" t="s">
-        <v>296</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -5864,40 +6112,40 @@
         <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="C106" t="s">
-        <v>282</v>
+        <v>163</v>
       </c>
       <c r="E106" t="s">
         <v>20</v>
       </c>
       <c r="F106" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I106" t="s">
-        <v>286</v>
+        <v>224</v>
       </c>
       <c r="J106" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="L106" t="s">
-        <v>287</v>
+        <v>233</v>
       </c>
       <c r="M106" t="s">
-        <v>288</v>
+        <v>233</v>
       </c>
       <c r="N106" t="s">
-        <v>289</v>
+        <v>234</v>
       </c>
       <c r="O106" t="s">
-        <v>293</v>
+        <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>301</v>
+        <v>165</v>
       </c>
       <c r="Q106" t="s">
-        <v>297</v>
+        <v>166</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -5905,25 +6153,40 @@
         <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>279</v>
+        <v>235</v>
+      </c>
+      <c r="C107" t="s">
+        <v>65</v>
       </c>
       <c r="E107" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F107" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I107" t="s">
-        <v>254</v>
+        <v>91</v>
+      </c>
+      <c r="J107" t="s">
+        <v>235</v>
       </c>
       <c r="L107" t="s">
-        <v>287</v>
+        <v>236</v>
       </c>
       <c r="M107" t="s">
-        <v>288</v>
+        <v>236</v>
       </c>
       <c r="N107" t="s">
-        <v>289</v>
+        <v>237</v>
+      </c>
+      <c r="O107" t="s">
+        <v>70</v>
+      </c>
+      <c r="P107" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -5931,40 +6194,40 @@
         <v>1</v>
       </c>
       <c r="B108" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="C108" t="s">
-        <v>306</v>
+        <v>73</v>
       </c>
       <c r="E108" t="s">
         <v>20</v>
       </c>
       <c r="F108" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I108" t="s">
-        <v>307</v>
+        <v>95</v>
       </c>
       <c r="J108" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="L108" t="s">
-        <v>310</v>
+        <v>236</v>
       </c>
       <c r="M108" t="s">
-        <v>311</v>
+        <v>236</v>
       </c>
       <c r="N108" t="s">
-        <v>312</v>
+        <v>237</v>
       </c>
       <c r="O108" t="s">
-        <v>303</v>
+        <v>74</v>
       </c>
       <c r="P108" t="s">
-        <v>303</v>
+        <v>75</v>
       </c>
       <c r="Q108" t="s">
-        <v>315</v>
+        <v>76</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -5972,40 +6235,40 @@
         <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="C109" t="s">
-        <v>305</v>
+        <v>134</v>
       </c>
       <c r="E109" t="s">
         <v>20</v>
       </c>
       <c r="F109" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I109" t="s">
-        <v>308</v>
+        <v>122</v>
       </c>
       <c r="J109" t="s">
-        <v>302</v>
+        <v>235</v>
       </c>
       <c r="L109" t="s">
-        <v>310</v>
+        <v>236</v>
       </c>
       <c r="M109" t="s">
-        <v>311</v>
+        <v>236</v>
       </c>
       <c r="N109" t="s">
-        <v>312</v>
+        <v>237</v>
       </c>
       <c r="O109" t="s">
-        <v>313</v>
+        <v>123</v>
       </c>
       <c r="P109" t="s">
-        <v>318</v>
+        <v>124</v>
       </c>
       <c r="Q109" t="s">
-        <v>316</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -6013,174 +6276,1331 @@
         <v>1</v>
       </c>
       <c r="B110" t="s">
+        <v>235</v>
+      </c>
+      <c r="C110" t="s">
+        <v>163</v>
+      </c>
+      <c r="E110" t="s">
+        <v>20</v>
+      </c>
+      <c r="F110" t="s">
+        <v>32</v>
+      </c>
+      <c r="I110" t="s">
+        <v>224</v>
+      </c>
+      <c r="J110" t="s">
+        <v>235</v>
+      </c>
+      <c r="L110" t="s">
+        <v>236</v>
+      </c>
+      <c r="M110" t="s">
+        <v>236</v>
+      </c>
+      <c r="N110" t="s">
+        <v>237</v>
+      </c>
+      <c r="O110" t="s">
+        <v>164</v>
+      </c>
+      <c r="P110" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1</v>
+      </c>
+      <c r="B111" t="s">
+        <v>238</v>
+      </c>
+      <c r="C111" t="s">
+        <v>65</v>
+      </c>
+      <c r="E111" t="s">
+        <v>20</v>
+      </c>
+      <c r="F111" t="s">
+        <v>32</v>
+      </c>
+      <c r="I111" t="s">
+        <v>91</v>
+      </c>
+      <c r="J111" t="s">
+        <v>238</v>
+      </c>
+      <c r="L111" t="s">
+        <v>239</v>
+      </c>
+      <c r="M111" t="s">
+        <v>239</v>
+      </c>
+      <c r="N111" t="s">
+        <v>240</v>
+      </c>
+      <c r="O111" t="s">
+        <v>70</v>
+      </c>
+      <c r="P111" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1</v>
+      </c>
+      <c r="B112" t="s">
+        <v>238</v>
+      </c>
+      <c r="C112" t="s">
+        <v>73</v>
+      </c>
+      <c r="E112" t="s">
+        <v>20</v>
+      </c>
+      <c r="F112" t="s">
+        <v>32</v>
+      </c>
+      <c r="I112" t="s">
+        <v>95</v>
+      </c>
+      <c r="J112" t="s">
+        <v>238</v>
+      </c>
+      <c r="L112" t="s">
+        <v>239</v>
+      </c>
+      <c r="M112" t="s">
+        <v>239</v>
+      </c>
+      <c r="N112" t="s">
+        <v>240</v>
+      </c>
+      <c r="O112" t="s">
+        <v>74</v>
+      </c>
+      <c r="P112" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1</v>
+      </c>
+      <c r="B113" t="s">
+        <v>238</v>
+      </c>
+      <c r="C113" t="s">
+        <v>134</v>
+      </c>
+      <c r="E113" t="s">
+        <v>20</v>
+      </c>
+      <c r="F113" t="s">
+        <v>32</v>
+      </c>
+      <c r="I113" t="s">
+        <v>122</v>
+      </c>
+      <c r="J113" t="s">
+        <v>238</v>
+      </c>
+      <c r="L113" t="s">
+        <v>239</v>
+      </c>
+      <c r="M113" t="s">
+        <v>239</v>
+      </c>
+      <c r="N113" t="s">
+        <v>240</v>
+      </c>
+      <c r="O113" t="s">
+        <v>123</v>
+      </c>
+      <c r="P113" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1</v>
+      </c>
+      <c r="B114" t="s">
+        <v>238</v>
+      </c>
+      <c r="C114" t="s">
+        <v>163</v>
+      </c>
+      <c r="E114" t="s">
+        <v>20</v>
+      </c>
+      <c r="F114" t="s">
+        <v>32</v>
+      </c>
+      <c r="I114" t="s">
+        <v>224</v>
+      </c>
+      <c r="J114" t="s">
+        <v>238</v>
+      </c>
+      <c r="L114" t="s">
+        <v>239</v>
+      </c>
+      <c r="M114" t="s">
+        <v>239</v>
+      </c>
+      <c r="N114" t="s">
+        <v>240</v>
+      </c>
+      <c r="O114" t="s">
+        <v>164</v>
+      </c>
+      <c r="P114" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1</v>
+      </c>
+      <c r="B115" t="s">
+        <v>241</v>
+      </c>
+      <c r="C115" t="s">
+        <v>65</v>
+      </c>
+      <c r="E115" t="s">
+        <v>20</v>
+      </c>
+      <c r="F115" t="s">
+        <v>32</v>
+      </c>
+      <c r="I115" t="s">
+        <v>91</v>
+      </c>
+      <c r="J115" t="s">
+        <v>241</v>
+      </c>
+      <c r="L115" t="s">
+        <v>242</v>
+      </c>
+      <c r="M115" t="s">
+        <v>242</v>
+      </c>
+      <c r="N115" t="s">
+        <v>243</v>
+      </c>
+      <c r="O115" t="s">
+        <v>70</v>
+      </c>
+      <c r="P115" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1</v>
+      </c>
+      <c r="B116" t="s">
+        <v>241</v>
+      </c>
+      <c r="C116" t="s">
+        <v>73</v>
+      </c>
+      <c r="E116" t="s">
+        <v>20</v>
+      </c>
+      <c r="F116" t="s">
+        <v>32</v>
+      </c>
+      <c r="I116" t="s">
+        <v>95</v>
+      </c>
+      <c r="J116" t="s">
+        <v>241</v>
+      </c>
+      <c r="L116" t="s">
+        <v>242</v>
+      </c>
+      <c r="M116" t="s">
+        <v>242</v>
+      </c>
+      <c r="N116" t="s">
+        <v>243</v>
+      </c>
+      <c r="O116" t="s">
+        <v>74</v>
+      </c>
+      <c r="P116" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1</v>
+      </c>
+      <c r="B117" t="s">
+        <v>241</v>
+      </c>
+      <c r="C117" t="s">
+        <v>134</v>
+      </c>
+      <c r="E117" t="s">
+        <v>20</v>
+      </c>
+      <c r="F117" t="s">
+        <v>32</v>
+      </c>
+      <c r="I117" t="s">
+        <v>122</v>
+      </c>
+      <c r="J117" t="s">
+        <v>241</v>
+      </c>
+      <c r="L117" t="s">
+        <v>242</v>
+      </c>
+      <c r="M117" t="s">
+        <v>242</v>
+      </c>
+      <c r="N117" t="s">
+        <v>243</v>
+      </c>
+      <c r="O117" t="s">
+        <v>123</v>
+      </c>
+      <c r="P117" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1</v>
+      </c>
+      <c r="B118" t="s">
+        <v>241</v>
+      </c>
+      <c r="C118" t="s">
+        <v>163</v>
+      </c>
+      <c r="E118" t="s">
+        <v>20</v>
+      </c>
+      <c r="F118" t="s">
+        <v>32</v>
+      </c>
+      <c r="I118" t="s">
+        <v>224</v>
+      </c>
+      <c r="J118" t="s">
+        <v>241</v>
+      </c>
+      <c r="L118" t="s">
+        <v>242</v>
+      </c>
+      <c r="M118" t="s">
+        <v>242</v>
+      </c>
+      <c r="N118" t="s">
+        <v>243</v>
+      </c>
+      <c r="O118" t="s">
+        <v>164</v>
+      </c>
+      <c r="P118" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1</v>
+      </c>
+      <c r="B119" t="s">
+        <v>244</v>
+      </c>
+      <c r="C119" t="s">
+        <v>65</v>
+      </c>
+      <c r="E119" t="s">
+        <v>20</v>
+      </c>
+      <c r="F119" t="s">
+        <v>32</v>
+      </c>
+      <c r="I119" t="s">
+        <v>91</v>
+      </c>
+      <c r="J119" t="s">
+        <v>244</v>
+      </c>
+      <c r="L119" t="s">
+        <v>245</v>
+      </c>
+      <c r="M119" t="s">
+        <v>245</v>
+      </c>
+      <c r="N119" t="s">
+        <v>246</v>
+      </c>
+      <c r="O119" t="s">
+        <v>70</v>
+      </c>
+      <c r="P119" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1</v>
+      </c>
+      <c r="B120" t="s">
+        <v>244</v>
+      </c>
+      <c r="C120" t="s">
+        <v>73</v>
+      </c>
+      <c r="E120" t="s">
+        <v>20</v>
+      </c>
+      <c r="F120" t="s">
+        <v>32</v>
+      </c>
+      <c r="I120" t="s">
+        <v>95</v>
+      </c>
+      <c r="J120" t="s">
+        <v>244</v>
+      </c>
+      <c r="L120" t="s">
+        <v>245</v>
+      </c>
+      <c r="M120" t="s">
+        <v>245</v>
+      </c>
+      <c r="N120" t="s">
+        <v>246</v>
+      </c>
+      <c r="O120" t="s">
+        <v>74</v>
+      </c>
+      <c r="P120" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1</v>
+      </c>
+      <c r="B121" t="s">
+        <v>244</v>
+      </c>
+      <c r="C121" t="s">
+        <v>134</v>
+      </c>
+      <c r="E121" t="s">
+        <v>20</v>
+      </c>
+      <c r="F121" t="s">
+        <v>32</v>
+      </c>
+      <c r="I121" t="s">
+        <v>122</v>
+      </c>
+      <c r="J121" t="s">
+        <v>244</v>
+      </c>
+      <c r="L121" t="s">
+        <v>245</v>
+      </c>
+      <c r="M121" t="s">
+        <v>245</v>
+      </c>
+      <c r="N121" t="s">
+        <v>246</v>
+      </c>
+      <c r="O121" t="s">
+        <v>123</v>
+      </c>
+      <c r="P121" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1</v>
+      </c>
+      <c r="B122" t="s">
+        <v>244</v>
+      </c>
+      <c r="C122" t="s">
+        <v>163</v>
+      </c>
+      <c r="E122" t="s">
+        <v>20</v>
+      </c>
+      <c r="F122" t="s">
+        <v>32</v>
+      </c>
+      <c r="I122" t="s">
+        <v>224</v>
+      </c>
+      <c r="J122" t="s">
+        <v>244</v>
+      </c>
+      <c r="L122" t="s">
+        <v>245</v>
+      </c>
+      <c r="M122" t="s">
+        <v>245</v>
+      </c>
+      <c r="N122" t="s">
+        <v>246</v>
+      </c>
+      <c r="O122" t="s">
+        <v>164</v>
+      </c>
+      <c r="P122" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1</v>
+      </c>
+      <c r="B123" t="s">
+        <v>247</v>
+      </c>
+      <c r="C123" t="s">
+        <v>65</v>
+      </c>
+      <c r="E123" t="s">
+        <v>20</v>
+      </c>
+      <c r="F123" t="s">
+        <v>32</v>
+      </c>
+      <c r="I123" t="s">
+        <v>91</v>
+      </c>
+      <c r="J123" t="s">
+        <v>247</v>
+      </c>
+      <c r="L123" t="s">
+        <v>248</v>
+      </c>
+      <c r="M123" t="s">
+        <v>248</v>
+      </c>
+      <c r="N123" t="s">
+        <v>249</v>
+      </c>
+      <c r="O123" t="s">
+        <v>70</v>
+      </c>
+      <c r="P123" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1</v>
+      </c>
+      <c r="B124" t="s">
+        <v>247</v>
+      </c>
+      <c r="C124" t="s">
+        <v>73</v>
+      </c>
+      <c r="E124" t="s">
+        <v>20</v>
+      </c>
+      <c r="F124" t="s">
+        <v>32</v>
+      </c>
+      <c r="I124" t="s">
+        <v>95</v>
+      </c>
+      <c r="J124" t="s">
+        <v>247</v>
+      </c>
+      <c r="L124" t="s">
+        <v>248</v>
+      </c>
+      <c r="M124" t="s">
+        <v>248</v>
+      </c>
+      <c r="N124" t="s">
+        <v>249</v>
+      </c>
+      <c r="O124" t="s">
+        <v>74</v>
+      </c>
+      <c r="P124" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1</v>
+      </c>
+      <c r="B125" t="s">
+        <v>247</v>
+      </c>
+      <c r="C125" t="s">
+        <v>134</v>
+      </c>
+      <c r="E125" t="s">
+        <v>20</v>
+      </c>
+      <c r="F125" t="s">
+        <v>32</v>
+      </c>
+      <c r="I125" t="s">
+        <v>122</v>
+      </c>
+      <c r="J125" t="s">
+        <v>247</v>
+      </c>
+      <c r="L125" t="s">
+        <v>248</v>
+      </c>
+      <c r="M125" t="s">
+        <v>248</v>
+      </c>
+      <c r="N125" t="s">
+        <v>249</v>
+      </c>
+      <c r="O125" t="s">
+        <v>123</v>
+      </c>
+      <c r="P125" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1</v>
+      </c>
+      <c r="B126" t="s">
+        <v>247</v>
+      </c>
+      <c r="C126" t="s">
+        <v>163</v>
+      </c>
+      <c r="E126" t="s">
+        <v>20</v>
+      </c>
+      <c r="F126" t="s">
+        <v>32</v>
+      </c>
+      <c r="I126" t="s">
+        <v>224</v>
+      </c>
+      <c r="J126" t="s">
+        <v>247</v>
+      </c>
+      <c r="L126" t="s">
+        <v>248</v>
+      </c>
+      <c r="M126" t="s">
+        <v>248</v>
+      </c>
+      <c r="N126" t="s">
+        <v>249</v>
+      </c>
+      <c r="O126" t="s">
+        <v>164</v>
+      </c>
+      <c r="P126" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1</v>
+      </c>
+      <c r="B127" t="s">
+        <v>250</v>
+      </c>
+      <c r="C127" t="s">
+        <v>65</v>
+      </c>
+      <c r="E127" t="s">
+        <v>20</v>
+      </c>
+      <c r="F127" t="s">
+        <v>32</v>
+      </c>
+      <c r="I127" t="s">
+        <v>91</v>
+      </c>
+      <c r="J127" t="s">
+        <v>250</v>
+      </c>
+      <c r="L127" t="s">
+        <v>251</v>
+      </c>
+      <c r="M127" t="s">
+        <v>251</v>
+      </c>
+      <c r="N127" t="s">
+        <v>252</v>
+      </c>
+      <c r="O127" t="s">
+        <v>70</v>
+      </c>
+      <c r="P127" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>1</v>
+      </c>
+      <c r="B128" t="s">
+        <v>250</v>
+      </c>
+      <c r="C128" t="s">
+        <v>73</v>
+      </c>
+      <c r="E128" t="s">
+        <v>20</v>
+      </c>
+      <c r="F128" t="s">
+        <v>32</v>
+      </c>
+      <c r="I128" t="s">
+        <v>95</v>
+      </c>
+      <c r="J128" t="s">
+        <v>250</v>
+      </c>
+      <c r="L128" t="s">
+        <v>251</v>
+      </c>
+      <c r="M128" t="s">
+        <v>251</v>
+      </c>
+      <c r="N128" t="s">
+        <v>252</v>
+      </c>
+      <c r="O128" t="s">
+        <v>74</v>
+      </c>
+      <c r="P128" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>1</v>
+      </c>
+      <c r="B129" t="s">
+        <v>250</v>
+      </c>
+      <c r="C129" t="s">
+        <v>134</v>
+      </c>
+      <c r="E129" t="s">
+        <v>20</v>
+      </c>
+      <c r="F129" t="s">
+        <v>32</v>
+      </c>
+      <c r="I129" t="s">
+        <v>122</v>
+      </c>
+      <c r="J129" t="s">
+        <v>250</v>
+      </c>
+      <c r="L129" t="s">
+        <v>251</v>
+      </c>
+      <c r="M129" t="s">
+        <v>251</v>
+      </c>
+      <c r="N129" t="s">
+        <v>252</v>
+      </c>
+      <c r="O129" t="s">
+        <v>123</v>
+      </c>
+      <c r="P129" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>1</v>
+      </c>
+      <c r="B130" t="s">
+        <v>250</v>
+      </c>
+      <c r="C130" t="s">
+        <v>163</v>
+      </c>
+      <c r="E130" t="s">
+        <v>20</v>
+      </c>
+      <c r="F130" t="s">
+        <v>32</v>
+      </c>
+      <c r="I130" t="s">
+        <v>224</v>
+      </c>
+      <c r="J130" t="s">
+        <v>250</v>
+      </c>
+      <c r="L130" t="s">
+        <v>251</v>
+      </c>
+      <c r="M130" t="s">
+        <v>251</v>
+      </c>
+      <c r="N130" t="s">
+        <v>252</v>
+      </c>
+      <c r="O130" t="s">
+        <v>164</v>
+      </c>
+      <c r="P130" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>1</v>
+      </c>
+      <c r="B131" t="s">
+        <v>269</v>
+      </c>
+      <c r="C131" t="s">
+        <v>101</v>
+      </c>
+      <c r="E131" t="s">
+        <v>20</v>
+      </c>
+      <c r="F131" t="s">
+        <v>54</v>
+      </c>
+      <c r="I131" t="s">
+        <v>274</v>
+      </c>
+      <c r="J131" t="s">
+        <v>269</v>
+      </c>
+      <c r="L131" t="s">
+        <v>278</v>
+      </c>
+      <c r="M131" t="s">
+        <v>279</v>
+      </c>
+      <c r="N131" t="s">
+        <v>280</v>
+      </c>
+      <c r="O131" t="s">
+        <v>281</v>
+      </c>
+      <c r="P131" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>1</v>
+      </c>
+      <c r="B132" t="s">
+        <v>269</v>
+      </c>
+      <c r="C132" t="s">
+        <v>271</v>
+      </c>
+      <c r="E132" t="s">
+        <v>20</v>
+      </c>
+      <c r="F132" t="s">
+        <v>54</v>
+      </c>
+      <c r="I132" t="s">
+        <v>275</v>
+      </c>
+      <c r="J132" t="s">
+        <v>269</v>
+      </c>
+      <c r="L132" t="s">
+        <v>278</v>
+      </c>
+      <c r="M132" t="s">
+        <v>279</v>
+      </c>
+      <c r="N132" t="s">
+        <v>280</v>
+      </c>
+      <c r="O132" t="s">
+        <v>282</v>
+      </c>
+      <c r="P132" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>1</v>
+      </c>
+      <c r="B133" t="s">
+        <v>269</v>
+      </c>
+      <c r="C133" t="s">
+        <v>272</v>
+      </c>
+      <c r="E133" t="s">
+        <v>20</v>
+      </c>
+      <c r="F133" t="s">
+        <v>54</v>
+      </c>
+      <c r="I133" t="s">
+        <v>276</v>
+      </c>
+      <c r="J133" t="s">
+        <v>269</v>
+      </c>
+      <c r="L133" t="s">
+        <v>278</v>
+      </c>
+      <c r="M133" t="s">
+        <v>279</v>
+      </c>
+      <c r="N133" t="s">
+        <v>280</v>
+      </c>
+      <c r="O133" t="s">
+        <v>283</v>
+      </c>
+      <c r="P133" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>1</v>
+      </c>
+      <c r="B134" t="s">
+        <v>269</v>
+      </c>
+      <c r="C134" t="s">
+        <v>273</v>
+      </c>
+      <c r="E134" t="s">
+        <v>20</v>
+      </c>
+      <c r="F134" t="s">
+        <v>54</v>
+      </c>
+      <c r="I134" t="s">
+        <v>277</v>
+      </c>
+      <c r="J134" t="s">
+        <v>269</v>
+      </c>
+      <c r="L134" t="s">
+        <v>278</v>
+      </c>
+      <c r="M134" t="s">
+        <v>279</v>
+      </c>
+      <c r="N134" t="s">
+        <v>280</v>
+      </c>
+      <c r="O134" t="s">
+        <v>284</v>
+      </c>
+      <c r="P134" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>1</v>
+      </c>
+      <c r="B135" t="s">
+        <v>270</v>
+      </c>
+      <c r="E135" t="s">
+        <v>47</v>
+      </c>
+      <c r="F135" t="s">
+        <v>54</v>
+      </c>
+      <c r="I135" t="s">
+        <v>254</v>
+      </c>
+      <c r="L135" t="s">
+        <v>278</v>
+      </c>
+      <c r="M135" t="s">
+        <v>279</v>
+      </c>
+      <c r="N135" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>1</v>
+      </c>
+      <c r="B136" t="s">
+        <v>293</v>
+      </c>
+      <c r="C136" t="s">
+        <v>297</v>
+      </c>
+      <c r="E136" t="s">
+        <v>20</v>
+      </c>
+      <c r="F136" t="s">
+        <v>54</v>
+      </c>
+      <c r="I136" t="s">
+        <v>298</v>
+      </c>
+      <c r="J136" t="s">
+        <v>293</v>
+      </c>
+      <c r="L136" t="s">
+        <v>301</v>
+      </c>
+      <c r="M136" t="s">
         <v>302</v>
       </c>
-      <c r="C110" t="s">
+      <c r="N136" t="s">
+        <v>303</v>
+      </c>
+      <c r="O136" t="s">
+        <v>294</v>
+      </c>
+      <c r="P136" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>1</v>
+      </c>
+      <c r="B137" t="s">
+        <v>293</v>
+      </c>
+      <c r="C137" t="s">
+        <v>296</v>
+      </c>
+      <c r="E137" t="s">
+        <v>20</v>
+      </c>
+      <c r="F137" t="s">
+        <v>54</v>
+      </c>
+      <c r="I137" t="s">
+        <v>299</v>
+      </c>
+      <c r="J137" t="s">
+        <v>293</v>
+      </c>
+      <c r="L137" t="s">
+        <v>301</v>
+      </c>
+      <c r="M137" t="s">
+        <v>302</v>
+      </c>
+      <c r="N137" t="s">
+        <v>303</v>
+      </c>
+      <c r="O137" t="s">
         <v>304</v>
       </c>
-      <c r="E110" t="s">
-        <v>20</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="P137" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>1</v>
+      </c>
+      <c r="B138" t="s">
+        <v>293</v>
+      </c>
+      <c r="C138" t="s">
+        <v>295</v>
+      </c>
+      <c r="E138" t="s">
+        <v>20</v>
+      </c>
+      <c r="F138" t="s">
         <v>54</v>
       </c>
-      <c r="I110" t="s">
-        <v>309</v>
-      </c>
-      <c r="J110" t="s">
+      <c r="I138" t="s">
+        <v>300</v>
+      </c>
+      <c r="J138" t="s">
+        <v>293</v>
+      </c>
+      <c r="L138" t="s">
+        <v>301</v>
+      </c>
+      <c r="M138" t="s">
         <v>302</v>
       </c>
-      <c r="L110" t="s">
+      <c r="N138" t="s">
+        <v>303</v>
+      </c>
+      <c r="O138" t="s">
+        <v>305</v>
+      </c>
+      <c r="P138" t="s">
         <v>310</v>
       </c>
-      <c r="M110" t="s">
-        <v>311</v>
-      </c>
-      <c r="N110" t="s">
-        <v>312</v>
-      </c>
-      <c r="O110" t="s">
-        <v>314</v>
-      </c>
-      <c r="P110" t="s">
-        <v>319</v>
-      </c>
-      <c r="Q110" t="s">
-        <v>317</v>
+      <c r="Q138" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B11:B13 B16">
-    <cfRule type="duplicateValues" dxfId="43" priority="45"/>
+  <conditionalFormatting sqref="B29">
+    <cfRule type="duplicateValues" dxfId="51" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14">
-    <cfRule type="duplicateValues" dxfId="42" priority="43"/>
+  <conditionalFormatting sqref="B37:B50 B26:B28">
+    <cfRule type="duplicateValues" dxfId="50" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28">
-    <cfRule type="duplicateValues" dxfId="41" priority="41"/>
+  <conditionalFormatting sqref="B62">
+    <cfRule type="duplicateValues" dxfId="49" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B29">
-    <cfRule type="duplicateValues" dxfId="40" priority="40"/>
+  <conditionalFormatting sqref="B63">
+    <cfRule type="duplicateValues" dxfId="48" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B30">
-    <cfRule type="duplicateValues" dxfId="39" priority="39"/>
+  <conditionalFormatting sqref="B64">
+    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B41">
-    <cfRule type="duplicateValues" dxfId="38" priority="38"/>
+  <conditionalFormatting sqref="B65:B75">
+    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B42">
+  <conditionalFormatting sqref="B76">
+    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B77:B87 B129:B174 B31:B36">
+    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B88:B97">
+    <cfRule type="duplicateValues" dxfId="43" priority="31"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B98">
+    <cfRule type="duplicateValues" dxfId="42" priority="30"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B99:B130">
+    <cfRule type="duplicateValues" dxfId="41" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C26:C28">
+    <cfRule type="duplicateValues" dxfId="40" priority="53"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C55:C59">
+    <cfRule type="duplicateValues" dxfId="39" priority="51"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C65:C75">
+    <cfRule type="duplicateValues" dxfId="38" priority="46"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C85:C86">
     <cfRule type="duplicateValues" dxfId="37" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43:B53 B95:B146">
-    <cfRule type="duplicateValues" dxfId="36" priority="28"/>
+  <conditionalFormatting sqref="C88:C97">
+    <cfRule type="duplicateValues" dxfId="36" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B54:B63">
-    <cfRule type="duplicateValues" dxfId="35" priority="22"/>
+  <conditionalFormatting sqref="H39">
+    <cfRule type="duplicateValues" dxfId="35" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
-    <cfRule type="duplicateValues" dxfId="34" priority="21"/>
+  <conditionalFormatting sqref="H40">
+    <cfRule type="duplicateValues" dxfId="34" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B65:B96">
-    <cfRule type="duplicateValues" dxfId="33" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11:C13">
-    <cfRule type="duplicateValues" dxfId="32" priority="44"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C21:C25">
-    <cfRule type="duplicateValues" dxfId="31" priority="42"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C31:C41">
-    <cfRule type="duplicateValues" dxfId="30" priority="37"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C51:C52">
-    <cfRule type="duplicateValues" dxfId="29" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C54:C63">
-    <cfRule type="duplicateValues" dxfId="28" priority="20"/>
+  <conditionalFormatting sqref="H41">
+    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="27" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H53:H63 H65:H146">
-    <cfRule type="duplicateValues" dxfId="26" priority="25"/>
+  <conditionalFormatting sqref="H43">
+    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H64">
-    <cfRule type="duplicateValues" dxfId="25" priority="19"/>
+  <conditionalFormatting sqref="H44">
+    <cfRule type="duplicateValues" dxfId="30" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I24">
-    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
+  <conditionalFormatting sqref="H76">
+    <cfRule type="duplicateValues" dxfId="29" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I31:I41">
-    <cfRule type="duplicateValues" dxfId="23" priority="34"/>
+  <conditionalFormatting sqref="H87:H97 H99:H174 H31:H36">
+    <cfRule type="duplicateValues" dxfId="28" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I52">
-    <cfRule type="duplicateValues" dxfId="22" priority="26"/>
+  <conditionalFormatting sqref="H98">
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I54:I61 I63">
-    <cfRule type="duplicateValues" dxfId="21" priority="17"/>
+  <conditionalFormatting sqref="I56:I58">
+    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I62">
-    <cfRule type="duplicateValues" dxfId="20" priority="15"/>
+  <conditionalFormatting sqref="I65:I75">
+    <cfRule type="duplicateValues" dxfId="25" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I68">
-    <cfRule type="duplicateValues" dxfId="19" priority="13"/>
+  <conditionalFormatting sqref="I86">
+    <cfRule type="duplicateValues" dxfId="24" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I72">
-    <cfRule type="duplicateValues" dxfId="18" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I76">
-    <cfRule type="duplicateValues" dxfId="17" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I80">
-    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I84">
-    <cfRule type="duplicateValues" dxfId="15" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I88">
-    <cfRule type="duplicateValues" dxfId="14" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I92">
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+  <conditionalFormatting sqref="I88:I95 I97">
+    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I96">
-    <cfRule type="duplicateValues" dxfId="12" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J28">
-    <cfRule type="duplicateValues" dxfId="11" priority="32"/>
+  <conditionalFormatting sqref="I102">
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J29">
-    <cfRule type="duplicateValues" dxfId="10" priority="31"/>
+  <conditionalFormatting sqref="I106">
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J30">
-    <cfRule type="duplicateValues" dxfId="9" priority="30"/>
+  <conditionalFormatting sqref="I110">
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J41">
-    <cfRule type="duplicateValues" dxfId="8" priority="33"/>
+  <conditionalFormatting sqref="I114">
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J43:J52">
-    <cfRule type="duplicateValues" dxfId="7" priority="23"/>
+  <conditionalFormatting sqref="I118">
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J53 J107 J111:J146">
-    <cfRule type="duplicateValues" dxfId="6" priority="24"/>
+  <conditionalFormatting sqref="I122">
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J54:J63">
-    <cfRule type="duplicateValues" dxfId="5" priority="16"/>
+  <conditionalFormatting sqref="I126">
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I130">
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J31:J36">
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J37:J50">
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J62">
+    <cfRule type="duplicateValues" dxfId="11" priority="41"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J63">
+    <cfRule type="duplicateValues" dxfId="10" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J64">
-    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J65:J96">
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
+  <conditionalFormatting sqref="J65:J75">
+    <cfRule type="duplicateValues" dxfId="8" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J95:J96">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+  <conditionalFormatting sqref="J77:J86">
+    <cfRule type="duplicateValues" dxfId="7" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J97:J106">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  <conditionalFormatting sqref="J88:J97">
+    <cfRule type="duplicateValues" dxfId="6" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J108:J110">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="J98">
+    <cfRule type="duplicateValues" dxfId="5" priority="27"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J99:J130">
+    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J129:J130">
+    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J131:J134">
+    <cfRule type="duplicateValues" dxfId="2" priority="66"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J135 J87 J139:J174">
+    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J136:J138">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/resources/variable_schema_data_individual_nutrition_template.xlsx
+++ b/resources/variable_schema_data_individual_nutrition_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1531BD-6D67-45C0-82FB-848277E0221E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D4B081-779F-4947-B9C3-1A7DD3647C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2730" yWindow="2730" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2357,28 +2357,31 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>319</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
+        <v>26</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
       </c>
       <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="b">
-        <v>0</v>
+      <c r="F3" t="s">
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>320</v>
+        <v>26</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>321</v>
+        <v>27</v>
       </c>
       <c r="M3" t="s">
-        <v>322</v>
+        <v>28</v>
       </c>
       <c r="N3" t="s">
-        <v>323</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -2386,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -2398,16 +2401,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="L4" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="M4" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="N4" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -2415,31 +2418,28 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5" t="s">
-        <v>330</v>
-      </c>
-      <c r="F5" t="s">
-        <v>330</v>
+        <v>20</v>
       </c>
       <c r="G5" t="b">
         <v>0</v>
       </c>
       <c r="J5" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="L5" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="M5" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="N5" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -2447,31 +2447,31 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>330</v>
       </c>
       <c r="F6" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="G6" t="b">
         <v>0</v>
       </c>
       <c r="J6" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="L6" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="M6" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="N6" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -2479,7 +2479,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -2494,16 +2494,16 @@
         <v>0</v>
       </c>
       <c r="J7" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="L7" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="M7" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="N7" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -2511,7 +2511,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2526,19 +2526,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="L8" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="M8" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="N8" t="s">
-        <v>350</v>
-      </c>
-      <c r="R8" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -2546,7 +2543,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -2555,25 +2552,25 @@
         <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>336</v>
       </c>
       <c r="G9" t="b">
         <v>0</v>
       </c>
       <c r="J9" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="L9" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="M9" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="N9" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="R9" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -2581,31 +2578,34 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>54</v>
       </c>
       <c r="G10" t="b">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="L10" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="M10" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="N10" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="R10" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -2613,7 +2613,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -2625,19 +2625,19 @@
         <v>0</v>
       </c>
       <c r="J11" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="L11" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="M11" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="N11" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="R11" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -2645,19 +2645,19 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="G12" t="b">
         <v>0</v>
       </c>
       <c r="J12" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="L12" t="s">
         <v>366</v>
@@ -2677,31 +2677,31 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="G13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="L13" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="M13" t="s">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="N13" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="R13" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -2709,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -2721,16 +2721,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="L14" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="M14" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="N14" t="s">
-        <v>381</v>
+        <v>375</v>
+      </c>
+      <c r="R14" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -2738,7 +2741,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -2750,16 +2753,16 @@
         <v>0</v>
       </c>
       <c r="J15" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="L15" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="M15" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="N15" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -2767,7 +2770,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -2779,16 +2782,16 @@
         <v>0</v>
       </c>
       <c r="J16" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="L16" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="M16" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="N16" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -2796,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -2808,16 +2811,16 @@
         <v>0</v>
       </c>
       <c r="J17" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="L17" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="M17" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="N17" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -2825,31 +2828,28 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" t="b">
-        <v>1</v>
+        <v>392</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
       </c>
       <c r="E18" t="s">
         <v>20</v>
       </c>
-      <c r="F18" t="s">
-        <v>21</v>
+      <c r="G18" t="b">
+        <v>0</v>
       </c>
       <c r="J18" t="s">
-        <v>26</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
+        <v>393</v>
       </c>
       <c r="L18" t="s">
-        <v>27</v>
+        <v>394</v>
       </c>
       <c r="M18" t="s">
-        <v>28</v>
+        <v>395</v>
       </c>
       <c r="N18" t="s">
-        <v>29</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -3415,25 +3415,40 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>268</v>
+        <v>293</v>
+      </c>
+      <c r="C37" t="s">
+        <v>297</v>
       </c>
       <c r="E37" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F37" t="s">
         <v>54</v>
       </c>
+      <c r="I37" t="s">
+        <v>298</v>
+      </c>
       <c r="J37" t="s">
-        <v>456</v>
+        <v>293</v>
       </c>
       <c r="L37" t="s">
-        <v>433</v>
+        <v>301</v>
       </c>
       <c r="M37" t="s">
-        <v>435</v>
+        <v>302</v>
       </c>
       <c r="N37" t="s">
-        <v>437</v>
+        <v>303</v>
+      </c>
+      <c r="O37" t="s">
+        <v>294</v>
+      </c>
+      <c r="P37" t="s">
+        <v>294</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -3441,25 +3456,40 @@
         <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>398</v>
+        <v>293</v>
+      </c>
+      <c r="C38" t="s">
+        <v>296</v>
       </c>
       <c r="E38" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F38" t="s">
         <v>54</v>
       </c>
+      <c r="I38" t="s">
+        <v>299</v>
+      </c>
       <c r="J38" t="s">
-        <v>457</v>
+        <v>293</v>
       </c>
       <c r="L38" t="s">
-        <v>434</v>
+        <v>301</v>
       </c>
       <c r="M38" t="s">
-        <v>436</v>
+        <v>302</v>
       </c>
       <c r="N38" t="s">
-        <v>438</v>
+        <v>303</v>
+      </c>
+      <c r="O38" t="s">
+        <v>304</v>
+      </c>
+      <c r="P38" t="s">
+        <v>309</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -3467,28 +3497,40 @@
         <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>267</v>
+        <v>293</v>
+      </c>
+      <c r="C39" t="s">
+        <v>295</v>
       </c>
       <c r="E39" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F39" t="s">
         <v>54</v>
       </c>
       <c r="I39" t="s">
-        <v>254</v>
+        <v>300</v>
       </c>
       <c r="J39" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="L39" t="s">
-        <v>439</v>
+        <v>301</v>
       </c>
       <c r="M39" t="s">
-        <v>450</v>
+        <v>302</v>
       </c>
       <c r="N39" t="s">
-        <v>444</v>
+        <v>303</v>
+      </c>
+      <c r="O39" t="s">
+        <v>305</v>
+      </c>
+      <c r="P39" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -3496,7 +3538,7 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>400</v>
+        <v>268</v>
       </c>
       <c r="E40" t="s">
         <v>47</v>
@@ -3504,20 +3546,17 @@
       <c r="F40" t="s">
         <v>54</v>
       </c>
-      <c r="I40" t="s">
-        <v>254</v>
-      </c>
       <c r="J40" t="s">
-        <v>400</v>
+        <v>456</v>
       </c>
       <c r="L40" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="M40" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="N40" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -3525,7 +3564,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>266</v>
+        <v>398</v>
       </c>
       <c r="E41" t="s">
         <v>47</v>
@@ -3533,20 +3572,17 @@
       <c r="F41" t="s">
         <v>54</v>
       </c>
-      <c r="I41" t="s">
-        <v>254</v>
-      </c>
       <c r="J41" t="s">
-        <v>266</v>
+        <v>457</v>
       </c>
       <c r="L41" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="M41" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="N41" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -3554,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>401</v>
+        <v>267</v>
       </c>
       <c r="E42" t="s">
         <v>47</v>
@@ -3566,16 +3602,16 @@
         <v>254</v>
       </c>
       <c r="J42" t="s">
-        <v>401</v>
+        <v>267</v>
       </c>
       <c r="L42" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="M42" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="N42" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -3583,7 +3619,7 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>265</v>
+        <v>400</v>
       </c>
       <c r="E43" t="s">
         <v>47</v>
@@ -3595,16 +3631,16 @@
         <v>254</v>
       </c>
       <c r="J43" t="s">
-        <v>265</v>
+        <v>400</v>
       </c>
       <c r="L43" t="s">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="M43" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="N43" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -3612,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>402</v>
+        <v>266</v>
       </c>
       <c r="E44" t="s">
         <v>47</v>
@@ -3624,16 +3660,16 @@
         <v>254</v>
       </c>
       <c r="J44" t="s">
-        <v>402</v>
+        <v>266</v>
       </c>
       <c r="L44" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="M44" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="N44" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -3641,40 +3677,28 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>397</v>
-      </c>
-      <c r="C45" t="s">
-        <v>297</v>
+        <v>401</v>
       </c>
       <c r="E45" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F45" t="s">
         <v>54</v>
       </c>
       <c r="I45" t="s">
-        <v>297</v>
+        <v>254</v>
       </c>
       <c r="J45" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="L45" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="M45" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
       <c r="N45" t="s">
-        <v>429</v>
-      </c>
-      <c r="O45" t="s">
-        <v>294</v>
-      </c>
-      <c r="P45" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -3682,40 +3706,28 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>397</v>
-      </c>
-      <c r="C46" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="E46" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F46" t="s">
         <v>54</v>
       </c>
       <c r="I46" t="s">
-        <v>296</v>
+        <v>254</v>
       </c>
       <c r="J46" t="s">
-        <v>397</v>
+        <v>265</v>
       </c>
       <c r="L46" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="M46" t="s">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="N46" t="s">
-        <v>429</v>
-      </c>
-      <c r="O46" t="s">
-        <v>416</v>
-      </c>
-      <c r="P46" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -3723,40 +3735,28 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>397</v>
-      </c>
-      <c r="C47" t="s">
-        <v>295</v>
+        <v>402</v>
       </c>
       <c r="E47" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F47" t="s">
         <v>54</v>
       </c>
       <c r="I47" t="s">
-        <v>295</v>
+        <v>254</v>
       </c>
       <c r="J47" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="L47" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="M47" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="N47" t="s">
-        <v>429</v>
-      </c>
-      <c r="O47" t="s">
-        <v>417</v>
-      </c>
-      <c r="P47" t="s">
-        <v>417</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -3764,7 +3764,7 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C48" t="s">
         <v>297</v>
@@ -3779,25 +3779,25 @@
         <v>297</v>
       </c>
       <c r="J48" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L48" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M48" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N48" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O48" t="s">
-        <v>418</v>
+        <v>294</v>
       </c>
       <c r="P48" t="s">
-        <v>418</v>
+        <v>294</v>
       </c>
       <c r="Q48" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -3805,7 +3805,7 @@
         <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C49" t="s">
         <v>296</v>
@@ -3820,25 +3820,25 @@
         <v>296</v>
       </c>
       <c r="J49" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L49" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M49" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N49" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O49" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="P49" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="Q49" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -3846,7 +3846,7 @@
         <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C50" t="s">
         <v>295</v>
@@ -3861,25 +3861,25 @@
         <v>295</v>
       </c>
       <c r="J50" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L50" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M50" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N50" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O50" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="P50" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Q50" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -3887,40 +3887,40 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>90</v>
+        <v>399</v>
       </c>
       <c r="C51" t="s">
-        <v>65</v>
+        <v>297</v>
       </c>
       <c r="E51" t="s">
         <v>20</v>
       </c>
       <c r="F51" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="I51" t="s">
-        <v>91</v>
+        <v>297</v>
       </c>
       <c r="J51" t="s">
-        <v>90</v>
+        <v>399</v>
       </c>
       <c r="L51" t="s">
-        <v>92</v>
+        <v>428</v>
       </c>
       <c r="M51" t="s">
-        <v>93</v>
+        <v>432</v>
       </c>
       <c r="N51" t="s">
-        <v>94</v>
+        <v>430</v>
       </c>
       <c r="O51" t="s">
-        <v>70</v>
+        <v>418</v>
       </c>
       <c r="P51" t="s">
-        <v>71</v>
+        <v>418</v>
       </c>
       <c r="Q51" t="s">
-        <v>72</v>
+        <v>424</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -3928,40 +3928,40 @@
         <v>1</v>
       </c>
       <c r="B52" t="s">
-        <v>90</v>
+        <v>399</v>
       </c>
       <c r="C52" t="s">
-        <v>73</v>
+        <v>296</v>
       </c>
       <c r="E52" t="s">
         <v>20</v>
       </c>
       <c r="F52" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="I52" t="s">
-        <v>95</v>
+        <v>296</v>
       </c>
       <c r="J52" t="s">
-        <v>90</v>
+        <v>399</v>
       </c>
       <c r="L52" t="s">
-        <v>92</v>
+        <v>428</v>
       </c>
       <c r="M52" t="s">
-        <v>93</v>
+        <v>432</v>
       </c>
       <c r="N52" t="s">
-        <v>94</v>
+        <v>430</v>
       </c>
       <c r="O52" t="s">
-        <v>74</v>
+        <v>419</v>
       </c>
       <c r="P52" t="s">
-        <v>75</v>
+        <v>419</v>
       </c>
       <c r="Q52" t="s">
-        <v>76</v>
+        <v>425</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -3969,40 +3969,40 @@
         <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>399</v>
       </c>
       <c r="C53" t="s">
-        <v>65</v>
+        <v>295</v>
       </c>
       <c r="E53" t="s">
         <v>20</v>
       </c>
       <c r="F53" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="I53" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="J53" t="s">
-        <v>96</v>
+        <v>399</v>
       </c>
       <c r="L53" t="s">
-        <v>97</v>
+        <v>428</v>
       </c>
       <c r="M53" t="s">
-        <v>98</v>
+        <v>432</v>
       </c>
       <c r="N53" t="s">
-        <v>99</v>
+        <v>430</v>
       </c>
       <c r="O53" t="s">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="P53" t="s">
-        <v>71</v>
+        <v>420</v>
       </c>
       <c r="Q53" t="s">
-        <v>72</v>
+        <v>426</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -4010,10 +4010,10 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E54" t="s">
         <v>20</v>
@@ -4022,28 +4022,28 @@
         <v>32</v>
       </c>
       <c r="I54" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J54" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="L54" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="M54" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="N54" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="O54" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P54" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q54" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -4051,10 +4051,10 @@
         <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C55" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E55" t="s">
         <v>20</v>
@@ -4063,28 +4063,28 @@
         <v>32</v>
       </c>
       <c r="I55" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J55" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L55" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="M55" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="N55" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="O55" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="P55" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="Q55" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -4092,10 +4092,10 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C56" t="s">
-        <v>109</v>
+        <v>65</v>
       </c>
       <c r="E56" t="s">
         <v>20</v>
@@ -4104,28 +4104,28 @@
         <v>32</v>
       </c>
       <c r="I56" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="J56" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L56" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="M56" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="N56" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O56" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="P56" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="Q56" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -4133,10 +4133,10 @@
         <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C57" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="E57" t="s">
         <v>20</v>
@@ -4145,28 +4145,28 @@
         <v>32</v>
       </c>
       <c r="I57" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="J57" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L57" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="M57" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="N57" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O57" t="s">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="P57" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="Q57" t="s">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -4177,7 +4177,7 @@
         <v>100</v>
       </c>
       <c r="C58" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="E58" t="s">
         <v>20</v>
@@ -4186,7 +4186,7 @@
         <v>32</v>
       </c>
       <c r="I58" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="J58" t="s">
         <v>100</v>
@@ -4201,13 +4201,13 @@
         <v>105</v>
       </c>
       <c r="O58" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="P58" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="Q58" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -4218,7 +4218,7 @@
         <v>100</v>
       </c>
       <c r="C59" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E59" t="s">
         <v>20</v>
@@ -4227,7 +4227,7 @@
         <v>32</v>
       </c>
       <c r="I59" t="s">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="J59" t="s">
         <v>100</v>
@@ -4242,13 +4242,13 @@
         <v>105</v>
       </c>
       <c r="O59" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="P59" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="Q59" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -4256,10 +4256,10 @@
         <v>1</v>
       </c>
       <c r="B60" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C60" t="s">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="E60" t="s">
         <v>20</v>
@@ -4268,28 +4268,28 @@
         <v>32</v>
       </c>
       <c r="I60" t="s">
-        <v>91</v>
+        <v>113</v>
       </c>
       <c r="J60" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="L60" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="M60" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="N60" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="O60" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="P60" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="Q60" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -4297,10 +4297,10 @@
         <v>1</v>
       </c>
       <c r="B61" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C61" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="E61" t="s">
         <v>20</v>
@@ -4309,28 +4309,28 @@
         <v>32</v>
       </c>
       <c r="I61" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="J61" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="L61" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="M61" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="N61" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="O61" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="P61" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
       <c r="Q61" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -4338,10 +4338,10 @@
         <v>1</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C62" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="E62" t="s">
         <v>20</v>
@@ -4350,28 +4350,28 @@
         <v>32</v>
       </c>
       <c r="I62" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J62" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="L62" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="M62" t="s">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="N62" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="O62" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="P62" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="Q62" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -4379,10 +4379,10 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E63" t="s">
         <v>20</v>
@@ -4391,28 +4391,28 @@
         <v>32</v>
       </c>
       <c r="I63" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J63" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L63" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M63" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N63" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O63" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P63" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q63" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -4420,10 +4420,10 @@
         <v>1</v>
       </c>
       <c r="B64" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="E64" t="s">
         <v>20</v>
@@ -4432,28 +4432,28 @@
         <v>32</v>
       </c>
       <c r="I64" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J64" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L64" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M64" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N64" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O64" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="P64" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Q64" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -4461,40 +4461,40 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C65" t="s">
-        <v>136</v>
+        <v>65</v>
       </c>
       <c r="E65" t="s">
         <v>20</v>
       </c>
       <c r="F65" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I65" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="J65" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L65" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M65" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N65" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O65" t="s">
-        <v>142</v>
+        <v>70</v>
       </c>
       <c r="P65" t="s">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="Q65" t="s">
-        <v>142</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -4502,40 +4502,40 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C66" t="s">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="E66" t="s">
         <v>20</v>
       </c>
       <c r="F66" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I66" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="J66" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L66" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M66" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N66" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O66" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="P66" t="s">
-        <v>144</v>
+        <v>75</v>
       </c>
       <c r="Q66" t="s">
-        <v>144</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -4543,40 +4543,40 @@
         <v>1</v>
       </c>
       <c r="B67" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C67" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="E67" t="s">
         <v>20</v>
       </c>
       <c r="F67" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I67" t="s">
-        <v>145</v>
+        <v>122</v>
       </c>
       <c r="J67" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L67" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M67" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N67" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O67" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="P67" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="Q67" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -4587,7 +4587,7 @@
         <v>135</v>
       </c>
       <c r="C68" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E68" t="s">
         <v>20</v>
@@ -4596,7 +4596,7 @@
         <v>137</v>
       </c>
       <c r="I68" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="J68" t="s">
         <v>138</v>
@@ -4611,13 +4611,13 @@
         <v>141</v>
       </c>
       <c r="O68" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="P68" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Q68" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -4628,7 +4628,7 @@
         <v>135</v>
       </c>
       <c r="C69" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E69" t="s">
         <v>20</v>
@@ -4637,7 +4637,7 @@
         <v>137</v>
       </c>
       <c r="I69" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="J69" t="s">
         <v>138</v>
@@ -4652,13 +4652,13 @@
         <v>141</v>
       </c>
       <c r="O69" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="P69" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="Q69" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -4669,7 +4669,7 @@
         <v>135</v>
       </c>
       <c r="C70" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E70" t="s">
         <v>20</v>
@@ -4678,7 +4678,7 @@
         <v>137</v>
       </c>
       <c r="I70" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="J70" t="s">
         <v>138</v>
@@ -4693,13 +4693,13 @@
         <v>141</v>
       </c>
       <c r="O70" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="P70" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="Q70" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -4710,7 +4710,7 @@
         <v>135</v>
       </c>
       <c r="C71" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="E71" t="s">
         <v>20</v>
@@ -4719,7 +4719,7 @@
         <v>137</v>
       </c>
       <c r="I71" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="J71" t="s">
         <v>138</v>
@@ -4734,13 +4734,13 @@
         <v>141</v>
       </c>
       <c r="O71" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="P71" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="Q71" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -4751,7 +4751,7 @@
         <v>135</v>
       </c>
       <c r="C72" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E72" t="s">
         <v>20</v>
@@ -4760,7 +4760,7 @@
         <v>137</v>
       </c>
       <c r="I72" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="J72" t="s">
         <v>138</v>
@@ -4775,13 +4775,13 @@
         <v>141</v>
       </c>
       <c r="O72" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="P72" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="Q72" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -4792,7 +4792,7 @@
         <v>135</v>
       </c>
       <c r="C73" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="E73" t="s">
         <v>20</v>
@@ -4801,7 +4801,7 @@
         <v>137</v>
       </c>
       <c r="I73" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="J73" t="s">
         <v>138</v>
@@ -4816,13 +4816,13 @@
         <v>141</v>
       </c>
       <c r="O73" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="P73" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="Q73" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -4833,7 +4833,7 @@
         <v>135</v>
       </c>
       <c r="C74" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="E74" t="s">
         <v>20</v>
@@ -4842,7 +4842,7 @@
         <v>137</v>
       </c>
       <c r="I74" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="J74" t="s">
         <v>138</v>
@@ -4857,13 +4857,13 @@
         <v>141</v>
       </c>
       <c r="O74" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="P74" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="Q74" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -4874,7 +4874,7 @@
         <v>135</v>
       </c>
       <c r="C75" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="E75" t="s">
         <v>20</v>
@@ -4883,7 +4883,7 @@
         <v>137</v>
       </c>
       <c r="I75" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="J75" t="s">
         <v>138</v>
@@ -4898,13 +4898,13 @@
         <v>141</v>
       </c>
       <c r="O75" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="P75" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="Q75" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -4912,28 +4912,40 @@
         <v>1</v>
       </c>
       <c r="B76" t="s">
-        <v>167</v>
+        <v>135</v>
+      </c>
+      <c r="C76" t="s">
+        <v>157</v>
       </c>
       <c r="E76" t="s">
         <v>20</v>
       </c>
       <c r="F76" t="s">
-        <v>168</v>
-      </c>
-      <c r="G76" t="b">
-        <v>1</v>
-      </c>
-      <c r="H76" t="s">
-        <v>135</v>
+        <v>137</v>
+      </c>
+      <c r="I76" t="s">
+        <v>157</v>
+      </c>
+      <c r="J76" t="s">
+        <v>138</v>
       </c>
       <c r="L76" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M76" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="N76" t="s">
-        <v>171</v>
+        <v>141</v>
+      </c>
+      <c r="O76" t="s">
+        <v>158</v>
+      </c>
+      <c r="P76" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -4941,10 +4953,10 @@
         <v>1</v>
       </c>
       <c r="B77" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="C77" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
       <c r="E77" t="s">
         <v>20</v>
@@ -4953,28 +4965,28 @@
         <v>137</v>
       </c>
       <c r="I77" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J77" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="L77" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="M77" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="N77" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="O77" t="s">
-        <v>179</v>
+        <v>160</v>
       </c>
       <c r="P77" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="Q77" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -4982,10 +4994,10 @@
         <v>1</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="C78" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="E78" t="s">
         <v>20</v>
@@ -4994,28 +5006,28 @@
         <v>137</v>
       </c>
       <c r="I78" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="J78" t="s">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="L78" t="s">
-        <v>176</v>
+        <v>139</v>
       </c>
       <c r="M78" t="s">
-        <v>177</v>
+        <v>140</v>
       </c>
       <c r="N78" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="O78" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="P78" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="Q78" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -5023,40 +5035,28 @@
         <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>172</v>
-      </c>
-      <c r="C79" t="s">
-        <v>183</v>
+        <v>167</v>
       </c>
       <c r="E79" t="s">
         <v>20</v>
       </c>
       <c r="F79" t="s">
-        <v>137</v>
-      </c>
-      <c r="I79" t="s">
-        <v>184</v>
-      </c>
-      <c r="J79" t="s">
-        <v>175</v>
+        <v>168</v>
+      </c>
+      <c r="G79" t="b">
+        <v>1</v>
+      </c>
+      <c r="H79" t="s">
+        <v>135</v>
       </c>
       <c r="L79" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="M79" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N79" t="s">
-        <v>178</v>
-      </c>
-      <c r="O79" t="s">
-        <v>185</v>
-      </c>
-      <c r="P79" t="s">
-        <v>185</v>
-      </c>
-      <c r="Q79" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -5067,7 +5067,7 @@
         <v>172</v>
       </c>
       <c r="C80" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="E80" t="s">
         <v>20</v>
@@ -5076,7 +5076,7 @@
         <v>137</v>
       </c>
       <c r="I80" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="J80" t="s">
         <v>175</v>
@@ -5091,13 +5091,13 @@
         <v>178</v>
       </c>
       <c r="O80" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="P80" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="Q80" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -5108,7 +5108,7 @@
         <v>172</v>
       </c>
       <c r="C81" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="E81" t="s">
         <v>20</v>
@@ -5117,7 +5117,7 @@
         <v>137</v>
       </c>
       <c r="I81" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="J81" t="s">
         <v>175</v>
@@ -5132,13 +5132,13 @@
         <v>178</v>
       </c>
       <c r="O81" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="P81" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="Q81" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -5149,7 +5149,7 @@
         <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="E82" t="s">
         <v>20</v>
@@ -5158,7 +5158,7 @@
         <v>137</v>
       </c>
       <c r="I82" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="J82" t="s">
         <v>175</v>
@@ -5173,13 +5173,13 @@
         <v>178</v>
       </c>
       <c r="O82" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="P82" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="Q82" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -5190,7 +5190,7 @@
         <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E83" t="s">
         <v>20</v>
@@ -5199,7 +5199,7 @@
         <v>137</v>
       </c>
       <c r="I83" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="J83" t="s">
         <v>175</v>
@@ -5214,13 +5214,13 @@
         <v>178</v>
       </c>
       <c r="O83" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="P83" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="Q83" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -5231,7 +5231,7 @@
         <v>172</v>
       </c>
       <c r="C84" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E84" t="s">
         <v>20</v>
@@ -5240,7 +5240,7 @@
         <v>137</v>
       </c>
       <c r="I84" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="J84" t="s">
         <v>175</v>
@@ -5255,13 +5255,13 @@
         <v>178</v>
       </c>
       <c r="O84" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="P84" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="Q84" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -5272,7 +5272,7 @@
         <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>134</v>
+        <v>192</v>
       </c>
       <c r="E85" t="s">
         <v>20</v>
@@ -5281,7 +5281,7 @@
         <v>137</v>
       </c>
       <c r="I85" t="s">
-        <v>122</v>
+        <v>193</v>
       </c>
       <c r="J85" t="s">
         <v>175</v>
@@ -5296,13 +5296,13 @@
         <v>178</v>
       </c>
       <c r="O85" t="s">
-        <v>123</v>
+        <v>194</v>
       </c>
       <c r="P85" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="Q85" t="s">
-        <v>125</v>
+        <v>194</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -5313,7 +5313,7 @@
         <v>172</v>
       </c>
       <c r="C86" t="s">
-        <v>159</v>
+        <v>195</v>
       </c>
       <c r="E86" t="s">
         <v>20</v>
@@ -5322,7 +5322,7 @@
         <v>137</v>
       </c>
       <c r="I86" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="J86" t="s">
         <v>175</v>
@@ -5337,13 +5337,13 @@
         <v>178</v>
       </c>
       <c r="O86" t="s">
-        <v>160</v>
+        <v>196</v>
       </c>
       <c r="P86" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="Q86" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -5351,31 +5351,40 @@
         <v>1</v>
       </c>
       <c r="B87" t="s">
-        <v>200</v>
+        <v>172</v>
+      </c>
+      <c r="C87" t="s">
+        <v>197</v>
       </c>
       <c r="E87" t="s">
         <v>20</v>
       </c>
       <c r="F87" t="s">
-        <v>168</v>
-      </c>
-      <c r="G87" t="b">
-        <v>1</v>
-      </c>
-      <c r="H87" t="s">
-        <v>172</v>
+        <v>137</v>
+      </c>
+      <c r="I87" t="s">
+        <v>197</v>
       </c>
       <c r="J87" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="L87" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="M87" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="N87" t="s">
-        <v>203</v>
+        <v>178</v>
+      </c>
+      <c r="O87" t="s">
+        <v>198</v>
+      </c>
+      <c r="P87" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -5383,10 +5392,10 @@
         <v>1</v>
       </c>
       <c r="B88" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="C88" t="s">
-        <v>205</v>
+        <v>134</v>
       </c>
       <c r="E88" t="s">
         <v>20</v>
@@ -5395,28 +5404,28 @@
         <v>137</v>
       </c>
       <c r="I88" t="s">
-        <v>205</v>
+        <v>122</v>
       </c>
       <c r="J88" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="L88" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="M88" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="N88" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="O88" t="s">
-        <v>209</v>
+        <v>123</v>
       </c>
       <c r="P88" t="s">
-        <v>209</v>
+        <v>124</v>
       </c>
       <c r="Q88" t="s">
-        <v>209</v>
+        <v>125</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -5424,10 +5433,10 @@
         <v>1</v>
       </c>
       <c r="B89" t="s">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="C89" t="s">
-        <v>210</v>
+        <v>159</v>
       </c>
       <c r="E89" t="s">
         <v>20</v>
@@ -5436,28 +5445,28 @@
         <v>137</v>
       </c>
       <c r="I89" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="J89" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="L89" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="M89" t="s">
-        <v>207</v>
+        <v>177</v>
       </c>
       <c r="N89" t="s">
-        <v>208</v>
+        <v>178</v>
       </c>
       <c r="O89" t="s">
-        <v>211</v>
+        <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>211</v>
+        <v>161</v>
       </c>
       <c r="Q89" t="s">
-        <v>211</v>
+        <v>162</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -5465,40 +5474,31 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>204</v>
-      </c>
-      <c r="C90" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="E90" t="s">
         <v>20</v>
       </c>
       <c r="F90" t="s">
-        <v>137</v>
-      </c>
-      <c r="I90" t="s">
-        <v>212</v>
+        <v>168</v>
+      </c>
+      <c r="G90" t="b">
+        <v>1</v>
+      </c>
+      <c r="H90" t="s">
+        <v>172</v>
       </c>
       <c r="J90" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L90" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="M90" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N90" t="s">
-        <v>208</v>
-      </c>
-      <c r="O90" t="s">
-        <v>213</v>
-      </c>
-      <c r="P90" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -5509,7 +5509,7 @@
         <v>204</v>
       </c>
       <c r="C91" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="E91" t="s">
         <v>20</v>
@@ -5518,7 +5518,7 @@
         <v>137</v>
       </c>
       <c r="I91" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="J91" t="s">
         <v>204</v>
@@ -5533,13 +5533,13 @@
         <v>208</v>
       </c>
       <c r="O91" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="P91" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="Q91" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -5550,7 +5550,7 @@
         <v>204</v>
       </c>
       <c r="C92" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="E92" t="s">
         <v>20</v>
@@ -5559,7 +5559,7 @@
         <v>137</v>
       </c>
       <c r="I92" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="J92" t="s">
         <v>204</v>
@@ -5574,13 +5574,13 @@
         <v>208</v>
       </c>
       <c r="O92" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="P92" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="Q92" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -5591,7 +5591,7 @@
         <v>204</v>
       </c>
       <c r="C93" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E93" t="s">
         <v>20</v>
@@ -5600,7 +5600,7 @@
         <v>137</v>
       </c>
       <c r="I93" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="J93" t="s">
         <v>204</v>
@@ -5615,13 +5615,13 @@
         <v>208</v>
       </c>
       <c r="O93" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="P93" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="Q93" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -5632,7 +5632,7 @@
         <v>204</v>
       </c>
       <c r="C94" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="E94" t="s">
         <v>20</v>
@@ -5641,7 +5641,7 @@
         <v>137</v>
       </c>
       <c r="I94" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="J94" t="s">
         <v>204</v>
@@ -5656,13 +5656,13 @@
         <v>208</v>
       </c>
       <c r="O94" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="P94" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="Q94" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -5673,7 +5673,7 @@
         <v>204</v>
       </c>
       <c r="C95" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="E95" t="s">
         <v>20</v>
@@ -5682,7 +5682,7 @@
         <v>137</v>
       </c>
       <c r="I95" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="J95" t="s">
         <v>204</v>
@@ -5697,13 +5697,13 @@
         <v>208</v>
       </c>
       <c r="O95" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="P95" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="Q95" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -5714,7 +5714,7 @@
         <v>204</v>
       </c>
       <c r="C96" t="s">
-        <v>159</v>
+        <v>218</v>
       </c>
       <c r="E96" t="s">
         <v>20</v>
@@ -5723,7 +5723,7 @@
         <v>137</v>
       </c>
       <c r="I96" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="J96" t="s">
         <v>204</v>
@@ -5738,13 +5738,13 @@
         <v>208</v>
       </c>
       <c r="O96" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="P96" t="s">
-        <v>161</v>
+        <v>219</v>
       </c>
       <c r="Q96" t="s">
-        <v>162</v>
+        <v>219</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -5755,7 +5755,7 @@
         <v>204</v>
       </c>
       <c r="C97" t="s">
-        <v>163</v>
+        <v>220</v>
       </c>
       <c r="E97" t="s">
         <v>20</v>
@@ -5764,7 +5764,7 @@
         <v>137</v>
       </c>
       <c r="I97" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J97" t="s">
         <v>204</v>
@@ -5779,13 +5779,13 @@
         <v>208</v>
       </c>
       <c r="O97" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="P97" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="Q97" t="s">
-        <v>166</v>
+        <v>221</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -5793,31 +5793,40 @@
         <v>1</v>
       </c>
       <c r="B98" t="s">
-        <v>225</v>
+        <v>204</v>
+      </c>
+      <c r="C98" t="s">
+        <v>222</v>
       </c>
       <c r="E98" t="s">
         <v>20</v>
       </c>
       <c r="F98" t="s">
-        <v>168</v>
-      </c>
-      <c r="G98" t="b">
-        <v>1</v>
-      </c>
-      <c r="H98" t="s">
+        <v>137</v>
+      </c>
+      <c r="I98" t="s">
+        <v>222</v>
+      </c>
+      <c r="J98" t="s">
         <v>204</v>
       </c>
-      <c r="J98" t="s">
-        <v>225</v>
-      </c>
       <c r="L98" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="M98" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="N98" t="s">
-        <v>228</v>
+        <v>208</v>
+      </c>
+      <c r="O98" t="s">
+        <v>223</v>
+      </c>
+      <c r="P98" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -5825,40 +5834,40 @@
         <v>1</v>
       </c>
       <c r="B99" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="C99" t="s">
-        <v>65</v>
+        <v>159</v>
       </c>
       <c r="E99" t="s">
         <v>20</v>
       </c>
       <c r="F99" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I99" t="s">
-        <v>91</v>
+        <v>199</v>
       </c>
       <c r="J99" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="L99" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="M99" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="N99" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="O99" t="s">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="P99" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="Q99" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -5866,40 +5875,40 @@
         <v>1</v>
       </c>
       <c r="B100" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="C100" t="s">
-        <v>73</v>
+        <v>163</v>
       </c>
       <c r="E100" t="s">
         <v>20</v>
       </c>
       <c r="F100" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="I100" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="J100" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="L100" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="M100" t="s">
-        <v>230</v>
+        <v>207</v>
       </c>
       <c r="N100" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="O100" t="s">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="P100" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="Q100" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -5907,40 +5916,31 @@
         <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>229</v>
-      </c>
-      <c r="C101" t="s">
-        <v>134</v>
+        <v>225</v>
       </c>
       <c r="E101" t="s">
         <v>20</v>
       </c>
       <c r="F101" t="s">
-        <v>32</v>
-      </c>
-      <c r="I101" t="s">
-        <v>122</v>
+        <v>168</v>
+      </c>
+      <c r="G101" t="b">
+        <v>1</v>
+      </c>
+      <c r="H101" t="s">
+        <v>204</v>
       </c>
       <c r="J101" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L101" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M101" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N101" t="s">
-        <v>231</v>
-      </c>
-      <c r="O101" t="s">
-        <v>123</v>
-      </c>
-      <c r="P101" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q101" t="s">
-        <v>125</v>
+        <v>228</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -5951,7 +5951,7 @@
         <v>229</v>
       </c>
       <c r="C102" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="E102" t="s">
         <v>20</v>
@@ -5960,7 +5960,7 @@
         <v>32</v>
       </c>
       <c r="I102" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="J102" t="s">
         <v>229</v>
@@ -5975,13 +5975,13 @@
         <v>231</v>
       </c>
       <c r="O102" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="P102" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="Q102" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -5989,10 +5989,10 @@
         <v>1</v>
       </c>
       <c r="B103" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C103" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E103" t="s">
         <v>20</v>
@@ -6001,28 +6001,28 @@
         <v>32</v>
       </c>
       <c r="I103" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J103" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L103" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M103" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N103" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O103" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P103" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q103" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -6030,10 +6030,10 @@
         <v>1</v>
       </c>
       <c r="B104" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C104" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="E104" t="s">
         <v>20</v>
@@ -6042,28 +6042,28 @@
         <v>32</v>
       </c>
       <c r="I104" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="J104" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L104" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M104" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N104" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O104" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="P104" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="Q104" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -6071,10 +6071,10 @@
         <v>1</v>
       </c>
       <c r="B105" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C105" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E105" t="s">
         <v>20</v>
@@ -6083,28 +6083,28 @@
         <v>32</v>
       </c>
       <c r="I105" t="s">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="J105" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L105" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M105" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N105" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O105" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="P105" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="Q105" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -6115,7 +6115,7 @@
         <v>232</v>
       </c>
       <c r="C106" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="E106" t="s">
         <v>20</v>
@@ -6124,7 +6124,7 @@
         <v>32</v>
       </c>
       <c r="I106" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="J106" t="s">
         <v>232</v>
@@ -6139,13 +6139,13 @@
         <v>234</v>
       </c>
       <c r="O106" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="P106" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="Q106" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -6153,10 +6153,10 @@
         <v>1</v>
       </c>
       <c r="B107" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C107" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E107" t="s">
         <v>20</v>
@@ -6165,28 +6165,28 @@
         <v>32</v>
       </c>
       <c r="I107" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J107" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="L107" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="M107" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N107" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O107" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P107" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q107" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -6194,10 +6194,10 @@
         <v>1</v>
       </c>
       <c r="B108" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C108" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="E108" t="s">
         <v>20</v>
@@ -6206,28 +6206,28 @@
         <v>32</v>
       </c>
       <c r="I108" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="J108" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="L108" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="M108" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N108" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O108" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="P108" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="Q108" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -6235,10 +6235,10 @@
         <v>1</v>
       </c>
       <c r="B109" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C109" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E109" t="s">
         <v>20</v>
@@ -6247,28 +6247,28 @@
         <v>32</v>
       </c>
       <c r="I109" t="s">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="J109" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="L109" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="M109" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N109" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O109" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="P109" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="Q109" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -6279,7 +6279,7 @@
         <v>235</v>
       </c>
       <c r="C110" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="E110" t="s">
         <v>20</v>
@@ -6288,7 +6288,7 @@
         <v>32</v>
       </c>
       <c r="I110" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="J110" t="s">
         <v>235</v>
@@ -6303,13 +6303,13 @@
         <v>237</v>
       </c>
       <c r="O110" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="P110" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="Q110" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -6317,10 +6317,10 @@
         <v>1</v>
       </c>
       <c r="B111" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C111" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E111" t="s">
         <v>20</v>
@@ -6329,28 +6329,28 @@
         <v>32</v>
       </c>
       <c r="I111" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J111" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L111" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M111" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N111" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O111" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P111" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q111" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -6358,10 +6358,10 @@
         <v>1</v>
       </c>
       <c r="B112" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C112" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="E112" t="s">
         <v>20</v>
@@ -6370,28 +6370,28 @@
         <v>32</v>
       </c>
       <c r="I112" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="J112" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L112" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M112" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N112" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O112" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="P112" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="Q112" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -6399,10 +6399,10 @@
         <v>1</v>
       </c>
       <c r="B113" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C113" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E113" t="s">
         <v>20</v>
@@ -6411,28 +6411,28 @@
         <v>32</v>
       </c>
       <c r="I113" t="s">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="J113" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L113" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M113" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N113" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O113" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="P113" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="Q113" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -6443,7 +6443,7 @@
         <v>238</v>
       </c>
       <c r="C114" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="E114" t="s">
         <v>20</v>
@@ -6452,7 +6452,7 @@
         <v>32</v>
       </c>
       <c r="I114" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="J114" t="s">
         <v>238</v>
@@ -6467,13 +6467,13 @@
         <v>240</v>
       </c>
       <c r="O114" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="P114" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="Q114" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -6481,10 +6481,10 @@
         <v>1</v>
       </c>
       <c r="B115" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C115" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E115" t="s">
         <v>20</v>
@@ -6493,28 +6493,28 @@
         <v>32</v>
       </c>
       <c r="I115" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J115" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L115" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M115" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N115" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O115" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P115" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q115" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -6522,10 +6522,10 @@
         <v>1</v>
       </c>
       <c r="B116" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C116" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="E116" t="s">
         <v>20</v>
@@ -6534,28 +6534,28 @@
         <v>32</v>
       </c>
       <c r="I116" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="J116" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L116" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M116" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N116" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O116" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="P116" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="Q116" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -6563,10 +6563,10 @@
         <v>1</v>
       </c>
       <c r="B117" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C117" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E117" t="s">
         <v>20</v>
@@ -6575,28 +6575,28 @@
         <v>32</v>
       </c>
       <c r="I117" t="s">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="J117" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L117" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M117" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N117" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O117" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="P117" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="Q117" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -6607,7 +6607,7 @@
         <v>241</v>
       </c>
       <c r="C118" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="E118" t="s">
         <v>20</v>
@@ -6616,7 +6616,7 @@
         <v>32</v>
       </c>
       <c r="I118" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="J118" t="s">
         <v>241</v>
@@ -6631,13 +6631,13 @@
         <v>243</v>
       </c>
       <c r="O118" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="P118" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="Q118" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -6645,10 +6645,10 @@
         <v>1</v>
       </c>
       <c r="B119" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C119" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E119" t="s">
         <v>20</v>
@@ -6657,28 +6657,28 @@
         <v>32</v>
       </c>
       <c r="I119" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J119" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L119" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M119" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N119" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O119" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P119" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q119" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -6686,10 +6686,10 @@
         <v>1</v>
       </c>
       <c r="B120" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C120" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="E120" t="s">
         <v>20</v>
@@ -6698,28 +6698,28 @@
         <v>32</v>
       </c>
       <c r="I120" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="J120" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L120" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M120" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N120" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O120" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="P120" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="Q120" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -6727,10 +6727,10 @@
         <v>1</v>
       </c>
       <c r="B121" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C121" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E121" t="s">
         <v>20</v>
@@ -6739,28 +6739,28 @@
         <v>32</v>
       </c>
       <c r="I121" t="s">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="J121" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L121" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M121" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N121" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O121" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="P121" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="Q121" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
@@ -6771,7 +6771,7 @@
         <v>244</v>
       </c>
       <c r="C122" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="E122" t="s">
         <v>20</v>
@@ -6780,7 +6780,7 @@
         <v>32</v>
       </c>
       <c r="I122" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="J122" t="s">
         <v>244</v>
@@ -6795,13 +6795,13 @@
         <v>246</v>
       </c>
       <c r="O122" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="P122" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="Q122" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -6809,10 +6809,10 @@
         <v>1</v>
       </c>
       <c r="B123" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C123" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E123" t="s">
         <v>20</v>
@@ -6821,28 +6821,28 @@
         <v>32</v>
       </c>
       <c r="I123" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J123" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L123" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M123" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N123" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O123" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P123" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q123" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -6850,10 +6850,10 @@
         <v>1</v>
       </c>
       <c r="B124" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C124" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="E124" t="s">
         <v>20</v>
@@ -6862,28 +6862,28 @@
         <v>32</v>
       </c>
       <c r="I124" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="J124" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L124" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M124" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N124" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O124" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="P124" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="Q124" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
@@ -6891,10 +6891,10 @@
         <v>1</v>
       </c>
       <c r="B125" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C125" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E125" t="s">
         <v>20</v>
@@ -6903,28 +6903,28 @@
         <v>32</v>
       </c>
       <c r="I125" t="s">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="J125" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L125" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M125" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N125" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O125" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="P125" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="Q125" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -6935,7 +6935,7 @@
         <v>247</v>
       </c>
       <c r="C126" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="E126" t="s">
         <v>20</v>
@@ -6944,7 +6944,7 @@
         <v>32</v>
       </c>
       <c r="I126" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="J126" t="s">
         <v>247</v>
@@ -6959,13 +6959,13 @@
         <v>249</v>
       </c>
       <c r="O126" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="P126" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="Q126" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -6973,10 +6973,10 @@
         <v>1</v>
       </c>
       <c r="B127" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C127" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E127" t="s">
         <v>20</v>
@@ -6985,28 +6985,28 @@
         <v>32</v>
       </c>
       <c r="I127" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J127" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L127" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M127" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N127" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O127" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P127" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q127" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -7014,10 +7014,10 @@
         <v>1</v>
       </c>
       <c r="B128" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C128" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="E128" t="s">
         <v>20</v>
@@ -7026,28 +7026,28 @@
         <v>32</v>
       </c>
       <c r="I128" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
       <c r="J128" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L128" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M128" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N128" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O128" t="s">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="P128" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="Q128" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -7055,10 +7055,10 @@
         <v>1</v>
       </c>
       <c r="B129" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C129" t="s">
-        <v>134</v>
+        <v>163</v>
       </c>
       <c r="E129" t="s">
         <v>20</v>
@@ -7067,28 +7067,28 @@
         <v>32</v>
       </c>
       <c r="I129" t="s">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="J129" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L129" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M129" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N129" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O129" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="P129" t="s">
-        <v>124</v>
+        <v>165</v>
       </c>
       <c r="Q129" t="s">
-        <v>125</v>
+        <v>166</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -7099,7 +7099,7 @@
         <v>250</v>
       </c>
       <c r="C130" t="s">
-        <v>163</v>
+        <v>65</v>
       </c>
       <c r="E130" t="s">
         <v>20</v>
@@ -7108,7 +7108,7 @@
         <v>32</v>
       </c>
       <c r="I130" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="J130" t="s">
         <v>250</v>
@@ -7123,13 +7123,13 @@
         <v>252</v>
       </c>
       <c r="O130" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="P130" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="Q130" t="s">
-        <v>166</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
@@ -7137,40 +7137,40 @@
         <v>1</v>
       </c>
       <c r="B131" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="C131" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E131" t="s">
         <v>20</v>
       </c>
       <c r="F131" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I131" t="s">
-        <v>274</v>
+        <v>95</v>
       </c>
       <c r="J131" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="L131" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="M131" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="N131" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="O131" t="s">
-        <v>281</v>
+        <v>74</v>
       </c>
       <c r="P131" t="s">
-        <v>289</v>
+        <v>75</v>
       </c>
       <c r="Q131" t="s">
-        <v>285</v>
+        <v>76</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -7178,40 +7178,40 @@
         <v>1</v>
       </c>
       <c r="B132" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="C132" t="s">
-        <v>271</v>
+        <v>134</v>
       </c>
       <c r="E132" t="s">
         <v>20</v>
       </c>
       <c r="F132" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I132" t="s">
-        <v>275</v>
+        <v>122</v>
       </c>
       <c r="J132" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="L132" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="M132" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="N132" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="O132" t="s">
-        <v>282</v>
+        <v>123</v>
       </c>
       <c r="P132" t="s">
-        <v>290</v>
+        <v>124</v>
       </c>
       <c r="Q132" t="s">
-        <v>286</v>
+        <v>125</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
@@ -7219,40 +7219,40 @@
         <v>1</v>
       </c>
       <c r="B133" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="C133" t="s">
-        <v>272</v>
+        <v>163</v>
       </c>
       <c r="E133" t="s">
         <v>20</v>
       </c>
       <c r="F133" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I133" t="s">
-        <v>276</v>
+        <v>224</v>
       </c>
       <c r="J133" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="L133" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="M133" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="N133" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="O133" t="s">
-        <v>283</v>
+        <v>164</v>
       </c>
       <c r="P133" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
       <c r="Q133" t="s">
-        <v>287</v>
+        <v>166</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -7263,7 +7263,7 @@
         <v>269</v>
       </c>
       <c r="C134" t="s">
-        <v>273</v>
+        <v>101</v>
       </c>
       <c r="E134" t="s">
         <v>20</v>
@@ -7272,7 +7272,7 @@
         <v>54</v>
       </c>
       <c r="I134" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="J134" t="s">
         <v>269</v>
@@ -7287,13 +7287,13 @@
         <v>280</v>
       </c>
       <c r="O134" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="P134" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="Q134" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -7301,16 +7301,22 @@
         <v>1</v>
       </c>
       <c r="B135" t="s">
-        <v>270</v>
+        <v>269</v>
+      </c>
+      <c r="C135" t="s">
+        <v>271</v>
       </c>
       <c r="E135" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F135" t="s">
         <v>54</v>
       </c>
       <c r="I135" t="s">
-        <v>254</v>
+        <v>275</v>
+      </c>
+      <c r="J135" t="s">
+        <v>269</v>
       </c>
       <c r="L135" t="s">
         <v>278</v>
@@ -7321,16 +7327,25 @@
       <c r="N135" t="s">
         <v>280</v>
       </c>
+      <c r="O135" t="s">
+        <v>282</v>
+      </c>
+      <c r="P135" t="s">
+        <v>290</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>1</v>
       </c>
       <c r="B136" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C136" t="s">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="E136" t="s">
         <v>20</v>
@@ -7339,28 +7354,28 @@
         <v>54</v>
       </c>
       <c r="I136" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="J136" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="L136" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="M136" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="N136" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="O136" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="P136" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Q136" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -7368,10 +7383,10 @@
         <v>1</v>
       </c>
       <c r="B137" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="C137" t="s">
-        <v>296</v>
+        <v>273</v>
       </c>
       <c r="E137" t="s">
         <v>20</v>
@@ -7380,28 +7395,28 @@
         <v>54</v>
       </c>
       <c r="I137" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="J137" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="L137" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="M137" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="N137" t="s">
-        <v>303</v>
+        <v>280</v>
       </c>
       <c r="O137" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
       <c r="P137" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="Q137" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -7409,197 +7424,182 @@
         <v>1</v>
       </c>
       <c r="B138" t="s">
-        <v>293</v>
-      </c>
-      <c r="C138" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="E138" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F138" t="s">
         <v>54</v>
       </c>
       <c r="I138" t="s">
-        <v>300</v>
-      </c>
-      <c r="J138" t="s">
-        <v>293</v>
+        <v>254</v>
       </c>
       <c r="L138" t="s">
-        <v>301</v>
+        <v>278</v>
       </c>
       <c r="M138" t="s">
-        <v>302</v>
+        <v>279</v>
       </c>
       <c r="N138" t="s">
-        <v>303</v>
-      </c>
-      <c r="O138" t="s">
-        <v>305</v>
-      </c>
-      <c r="P138" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q138" t="s">
-        <v>308</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B29">
     <cfRule type="duplicateValues" dxfId="51" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B37:B50 B26:B28">
+  <conditionalFormatting sqref="B40:B53 B26:B28">
     <cfRule type="duplicateValues" dxfId="50" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B62">
+  <conditionalFormatting sqref="B65">
     <cfRule type="duplicateValues" dxfId="49" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B63">
+  <conditionalFormatting sqref="B66">
     <cfRule type="duplicateValues" dxfId="48" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B64">
+  <conditionalFormatting sqref="B67">
     <cfRule type="duplicateValues" dxfId="47" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B65:B75">
+  <conditionalFormatting sqref="B68:B78">
     <cfRule type="duplicateValues" dxfId="46" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B76">
+  <conditionalFormatting sqref="B79">
     <cfRule type="duplicateValues" dxfId="45" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B77:B87 B129:B174 B31:B36">
+  <conditionalFormatting sqref="B80:B90 B132:B174 B31:B39">
     <cfRule type="duplicateValues" dxfId="44" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B88:B97">
+  <conditionalFormatting sqref="B91:B100">
     <cfRule type="duplicateValues" dxfId="43" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B98">
+  <conditionalFormatting sqref="B101">
     <cfRule type="duplicateValues" dxfId="42" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B99:B130">
+  <conditionalFormatting sqref="B102:B133">
     <cfRule type="duplicateValues" dxfId="41" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:C28">
     <cfRule type="duplicateValues" dxfId="40" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C55:C59">
+  <conditionalFormatting sqref="C58:C62">
     <cfRule type="duplicateValues" dxfId="39" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C65:C75">
+  <conditionalFormatting sqref="C68:C78">
     <cfRule type="duplicateValues" dxfId="38" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C85:C86">
+  <conditionalFormatting sqref="C88:C89">
     <cfRule type="duplicateValues" dxfId="37" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C88:C97">
+  <conditionalFormatting sqref="C91:C100">
     <cfRule type="duplicateValues" dxfId="36" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H39">
+  <conditionalFormatting sqref="H42">
     <cfRule type="duplicateValues" dxfId="35" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H40">
+  <conditionalFormatting sqref="H43">
     <cfRule type="duplicateValues" dxfId="34" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H41">
+  <conditionalFormatting sqref="H44">
     <cfRule type="duplicateValues" dxfId="33" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H42">
+  <conditionalFormatting sqref="H45">
     <cfRule type="duplicateValues" dxfId="32" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H43">
+  <conditionalFormatting sqref="H46">
     <cfRule type="duplicateValues" dxfId="31" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H44">
+  <conditionalFormatting sqref="H47">
     <cfRule type="duplicateValues" dxfId="30" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H76">
+  <conditionalFormatting sqref="H79">
     <cfRule type="duplicateValues" dxfId="29" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H87:H97 H99:H174 H31:H36">
+  <conditionalFormatting sqref="H90:H100 H102:H174 H31:H39">
     <cfRule type="duplicateValues" dxfId="28" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H98">
+  <conditionalFormatting sqref="H101">
     <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I56:I58">
+  <conditionalFormatting sqref="I59:I61">
     <cfRule type="duplicateValues" dxfId="26" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I65:I75">
+  <conditionalFormatting sqref="I68:I78">
     <cfRule type="duplicateValues" dxfId="25" priority="43"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I86">
+  <conditionalFormatting sqref="I89">
     <cfRule type="duplicateValues" dxfId="24" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I88:I95 I97">
+  <conditionalFormatting sqref="I91:I98 I100">
     <cfRule type="duplicateValues" dxfId="23" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I96">
+  <conditionalFormatting sqref="I99">
     <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I102">
+  <conditionalFormatting sqref="I105">
     <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I106">
+  <conditionalFormatting sqref="I109">
     <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I110">
+  <conditionalFormatting sqref="I113">
     <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I114">
+  <conditionalFormatting sqref="I117">
     <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I118">
+  <conditionalFormatting sqref="I121">
     <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I122">
+  <conditionalFormatting sqref="I125">
     <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I126">
+  <conditionalFormatting sqref="I129">
     <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I130">
+  <conditionalFormatting sqref="I133">
     <cfRule type="duplicateValues" dxfId="14" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:J36">
     <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J37:J50">
+  <conditionalFormatting sqref="J40:J53">
     <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J62">
+  <conditionalFormatting sqref="J65">
     <cfRule type="duplicateValues" dxfId="11" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J63">
+  <conditionalFormatting sqref="J66">
     <cfRule type="duplicateValues" dxfId="10" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J64">
+  <conditionalFormatting sqref="J67">
     <cfRule type="duplicateValues" dxfId="9" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J65:J75">
+  <conditionalFormatting sqref="J68:J78">
     <cfRule type="duplicateValues" dxfId="8" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J77:J86">
+  <conditionalFormatting sqref="J80:J89">
     <cfRule type="duplicateValues" dxfId="7" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J88:J97">
+  <conditionalFormatting sqref="J91:J100">
     <cfRule type="duplicateValues" dxfId="6" priority="25"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J98">
+  <conditionalFormatting sqref="J101">
     <cfRule type="duplicateValues" dxfId="5" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J99:J130">
+  <conditionalFormatting sqref="J102:J133">
     <cfRule type="duplicateValues" dxfId="4" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J129:J130">
+  <conditionalFormatting sqref="J132:J133">
     <cfRule type="duplicateValues" dxfId="3" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J131:J134">
+  <conditionalFormatting sqref="J134:J137">
     <cfRule type="duplicateValues" dxfId="2" priority="66"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J135 J87 J139:J174">
+  <conditionalFormatting sqref="J138:J174 J90">
     <cfRule type="duplicateValues" dxfId="1" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J136:J138">
+  <conditionalFormatting sqref="J37:J39">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/variable_schema_data_individual_nutrition_template.xlsx
+++ b/resources/variable_schema_data_individual_nutrition_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D4B081-779F-4947-B9C3-1A7DD3647C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2E13B0-CBB2-472C-A0F4-8E91FD1547DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1595" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="537">
   <si>
     <t>rule_type</t>
   </si>
@@ -1394,6 +1394,243 @@
   </si>
   <si>
     <t>nut_mfaz_noflag,mfaz_noflag</t>
+  </si>
+  <si>
+    <t>age_cat</t>
+  </si>
+  <si>
+    <t>0-4y</t>
+  </si>
+  <si>
+    <t>factor</t>
+  </si>
+  <si>
+    <t>0-4y,0-4</t>
+  </si>
+  <si>
+    <t>Age Category</t>
+  </si>
+  <si>
+    <t>Catégorie d'âge</t>
+  </si>
+  <si>
+    <t>فئة العمر</t>
+  </si>
+  <si>
+    <t>5-9y</t>
+  </si>
+  <si>
+    <t>5-9y,5-9</t>
+  </si>
+  <si>
+    <t>10-14y</t>
+  </si>
+  <si>
+    <t>10-14y,10-14</t>
+  </si>
+  <si>
+    <t>15-19y</t>
+  </si>
+  <si>
+    <t>15-19y,15-19</t>
+  </si>
+  <si>
+    <t>20-24y</t>
+  </si>
+  <si>
+    <t>20-24y,20-24</t>
+  </si>
+  <si>
+    <t>25-29y</t>
+  </si>
+  <si>
+    <t>25-29y,25-29</t>
+  </si>
+  <si>
+    <t>30-34y</t>
+  </si>
+  <si>
+    <t>30-34y,30-34</t>
+  </si>
+  <si>
+    <t>35-39y</t>
+  </si>
+  <si>
+    <t>35-39y,35-39</t>
+  </si>
+  <si>
+    <t>40-44y</t>
+  </si>
+  <si>
+    <t>40-44y,40-44</t>
+  </si>
+  <si>
+    <t>45-49y</t>
+  </si>
+  <si>
+    <t>45-49y,45-49</t>
+  </si>
+  <si>
+    <t>50-54y</t>
+  </si>
+  <si>
+    <t>50-54y,50-54</t>
+  </si>
+  <si>
+    <t>55-59y</t>
+  </si>
+  <si>
+    <t>55-59y,55-59</t>
+  </si>
+  <si>
+    <t>60-64y</t>
+  </si>
+  <si>
+    <t>60-64y,60-64</t>
+  </si>
+  <si>
+    <t>65-69y</t>
+  </si>
+  <si>
+    <t>65-69y,65-69</t>
+  </si>
+  <si>
+    <t>70-74y</t>
+  </si>
+  <si>
+    <t>70-74y,70-74</t>
+  </si>
+  <si>
+    <t>75-79y</t>
+  </si>
+  <si>
+    <t>75-79y,75-79</t>
+  </si>
+  <si>
+    <t>80-84y</t>
+  </si>
+  <si>
+    <t>80-84y,80-84</t>
+  </si>
+  <si>
+    <t>85-89y</t>
+  </si>
+  <si>
+    <t>85-89y,85-89</t>
+  </si>
+  <si>
+    <t>90-94y</t>
+  </si>
+  <si>
+    <t>90-94y,90-94</t>
+  </si>
+  <si>
+    <t>95-99y</t>
+  </si>
+  <si>
+    <t>95-99y,95-99</t>
+  </si>
+  <si>
+    <t>100-104y</t>
+  </si>
+  <si>
+    <t>100-104y,100-104</t>
+  </si>
+  <si>
+    <t>105-109y</t>
+  </si>
+  <si>
+    <t>105-109y,105-109</t>
+  </si>
+  <si>
+    <t>110-114y</t>
+  </si>
+  <si>
+    <t>110-114y,110-114</t>
+  </si>
+  <si>
+    <t>115-119y</t>
+  </si>
+  <si>
+    <t>115-119y,115-119</t>
+  </si>
+  <si>
+    <t>120-124y</t>
+  </si>
+  <si>
+    <t>120-124y,120-124</t>
+  </si>
+  <si>
+    <t>age_months_cat</t>
+  </si>
+  <si>
+    <t>0-5m</t>
+  </si>
+  <si>
+    <t>0-5m,0-5</t>
+  </si>
+  <si>
+    <t>Age Category (Months)</t>
+  </si>
+  <si>
+    <t>Catégorie d'âge (mois)</t>
+  </si>
+  <si>
+    <t>فئة العمر (بالأشهر)</t>
+  </si>
+  <si>
+    <t>6-11m</t>
+  </si>
+  <si>
+    <t>6-11m,6-11</t>
+  </si>
+  <si>
+    <t>12-17m</t>
+  </si>
+  <si>
+    <t>12-17m,12-17</t>
+  </si>
+  <si>
+    <t>18-23m</t>
+  </si>
+  <si>
+    <t>18-23m,18-23</t>
+  </si>
+  <si>
+    <t>24-29m</t>
+  </si>
+  <si>
+    <t>24-29m,24-29</t>
+  </si>
+  <si>
+    <t>30-35m</t>
+  </si>
+  <si>
+    <t>30-35m,30-35</t>
+  </si>
+  <si>
+    <t>36-41m</t>
+  </si>
+  <si>
+    <t>36-41m,36-41</t>
+  </si>
+  <si>
+    <t>42-47m</t>
+  </si>
+  <si>
+    <t>42-47m,42-47</t>
+  </si>
+  <si>
+    <t>48-53m</t>
+  </si>
+  <si>
+    <t>48-53m,48-53</t>
+  </si>
+  <si>
+    <t>54-59m</t>
+  </si>
+  <si>
+    <t>54-59m,54-59</t>
   </si>
 </sst>
 </file>
@@ -1435,7 +1672,27 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="52">
+  <dxfs count="54">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2254,7 +2511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S138"/>
+  <dimension ref="A1:S173"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
@@ -7445,162 +7702,1603 @@
         <v>280</v>
       </c>
     </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>1</v>
+      </c>
+      <c r="B139" t="s">
+        <v>458</v>
+      </c>
+      <c r="C139" t="s">
+        <v>459</v>
+      </c>
+      <c r="E139" t="s">
+        <v>460</v>
+      </c>
+      <c r="F139" t="s">
+        <v>54</v>
+      </c>
+      <c r="I139" t="s">
+        <v>461</v>
+      </c>
+      <c r="J139" t="s">
+        <v>458</v>
+      </c>
+      <c r="L139" t="s">
+        <v>462</v>
+      </c>
+      <c r="M139" t="s">
+        <v>463</v>
+      </c>
+      <c r="N139" t="s">
+        <v>464</v>
+      </c>
+      <c r="O139" t="s">
+        <v>459</v>
+      </c>
+      <c r="P139" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>1</v>
+      </c>
+      <c r="B140" t="s">
+        <v>458</v>
+      </c>
+      <c r="C140" t="s">
+        <v>465</v>
+      </c>
+      <c r="E140" t="s">
+        <v>460</v>
+      </c>
+      <c r="F140" t="s">
+        <v>54</v>
+      </c>
+      <c r="I140" t="s">
+        <v>466</v>
+      </c>
+      <c r="J140" t="s">
+        <v>458</v>
+      </c>
+      <c r="L140" t="s">
+        <v>462</v>
+      </c>
+      <c r="M140" t="s">
+        <v>463</v>
+      </c>
+      <c r="N140" t="s">
+        <v>464</v>
+      </c>
+      <c r="O140" t="s">
+        <v>465</v>
+      </c>
+      <c r="P140" t="s">
+        <v>465</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>1</v>
+      </c>
+      <c r="B141" t="s">
+        <v>458</v>
+      </c>
+      <c r="C141" t="s">
+        <v>467</v>
+      </c>
+      <c r="E141" t="s">
+        <v>460</v>
+      </c>
+      <c r="F141" t="s">
+        <v>54</v>
+      </c>
+      <c r="I141" t="s">
+        <v>468</v>
+      </c>
+      <c r="J141" t="s">
+        <v>458</v>
+      </c>
+      <c r="L141" t="s">
+        <v>462</v>
+      </c>
+      <c r="M141" t="s">
+        <v>463</v>
+      </c>
+      <c r="N141" t="s">
+        <v>464</v>
+      </c>
+      <c r="O141" t="s">
+        <v>467</v>
+      </c>
+      <c r="P141" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>1</v>
+      </c>
+      <c r="B142" t="s">
+        <v>458</v>
+      </c>
+      <c r="C142" t="s">
+        <v>469</v>
+      </c>
+      <c r="E142" t="s">
+        <v>460</v>
+      </c>
+      <c r="F142" t="s">
+        <v>54</v>
+      </c>
+      <c r="I142" t="s">
+        <v>470</v>
+      </c>
+      <c r="J142" t="s">
+        <v>458</v>
+      </c>
+      <c r="L142" t="s">
+        <v>462</v>
+      </c>
+      <c r="M142" t="s">
+        <v>463</v>
+      </c>
+      <c r="N142" t="s">
+        <v>464</v>
+      </c>
+      <c r="O142" t="s">
+        <v>469</v>
+      </c>
+      <c r="P142" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>1</v>
+      </c>
+      <c r="B143" t="s">
+        <v>458</v>
+      </c>
+      <c r="C143" t="s">
+        <v>471</v>
+      </c>
+      <c r="E143" t="s">
+        <v>460</v>
+      </c>
+      <c r="F143" t="s">
+        <v>54</v>
+      </c>
+      <c r="I143" t="s">
+        <v>472</v>
+      </c>
+      <c r="J143" t="s">
+        <v>458</v>
+      </c>
+      <c r="L143" t="s">
+        <v>462</v>
+      </c>
+      <c r="M143" t="s">
+        <v>463</v>
+      </c>
+      <c r="N143" t="s">
+        <v>464</v>
+      </c>
+      <c r="O143" t="s">
+        <v>471</v>
+      </c>
+      <c r="P143" t="s">
+        <v>471</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>1</v>
+      </c>
+      <c r="B144" t="s">
+        <v>458</v>
+      </c>
+      <c r="C144" t="s">
+        <v>473</v>
+      </c>
+      <c r="E144" t="s">
+        <v>460</v>
+      </c>
+      <c r="F144" t="s">
+        <v>54</v>
+      </c>
+      <c r="I144" t="s">
+        <v>474</v>
+      </c>
+      <c r="J144" t="s">
+        <v>458</v>
+      </c>
+      <c r="L144" t="s">
+        <v>462</v>
+      </c>
+      <c r="M144" t="s">
+        <v>463</v>
+      </c>
+      <c r="N144" t="s">
+        <v>464</v>
+      </c>
+      <c r="O144" t="s">
+        <v>473</v>
+      </c>
+      <c r="P144" t="s">
+        <v>473</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>1</v>
+      </c>
+      <c r="B145" t="s">
+        <v>458</v>
+      </c>
+      <c r="C145" t="s">
+        <v>475</v>
+      </c>
+      <c r="E145" t="s">
+        <v>460</v>
+      </c>
+      <c r="F145" t="s">
+        <v>54</v>
+      </c>
+      <c r="I145" t="s">
+        <v>476</v>
+      </c>
+      <c r="J145" t="s">
+        <v>458</v>
+      </c>
+      <c r="L145" t="s">
+        <v>462</v>
+      </c>
+      <c r="M145" t="s">
+        <v>463</v>
+      </c>
+      <c r="N145" t="s">
+        <v>464</v>
+      </c>
+      <c r="O145" t="s">
+        <v>475</v>
+      </c>
+      <c r="P145" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>1</v>
+      </c>
+      <c r="B146" t="s">
+        <v>458</v>
+      </c>
+      <c r="C146" t="s">
+        <v>477</v>
+      </c>
+      <c r="E146" t="s">
+        <v>460</v>
+      </c>
+      <c r="F146" t="s">
+        <v>54</v>
+      </c>
+      <c r="I146" t="s">
+        <v>478</v>
+      </c>
+      <c r="J146" t="s">
+        <v>458</v>
+      </c>
+      <c r="L146" t="s">
+        <v>462</v>
+      </c>
+      <c r="M146" t="s">
+        <v>463</v>
+      </c>
+      <c r="N146" t="s">
+        <v>464</v>
+      </c>
+      <c r="O146" t="s">
+        <v>477</v>
+      </c>
+      <c r="P146" t="s">
+        <v>477</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>1</v>
+      </c>
+      <c r="B147" t="s">
+        <v>458</v>
+      </c>
+      <c r="C147" t="s">
+        <v>479</v>
+      </c>
+      <c r="E147" t="s">
+        <v>460</v>
+      </c>
+      <c r="F147" t="s">
+        <v>54</v>
+      </c>
+      <c r="I147" t="s">
+        <v>480</v>
+      </c>
+      <c r="J147" t="s">
+        <v>458</v>
+      </c>
+      <c r="L147" t="s">
+        <v>462</v>
+      </c>
+      <c r="M147" t="s">
+        <v>463</v>
+      </c>
+      <c r="N147" t="s">
+        <v>464</v>
+      </c>
+      <c r="O147" t="s">
+        <v>479</v>
+      </c>
+      <c r="P147" t="s">
+        <v>479</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>1</v>
+      </c>
+      <c r="B148" t="s">
+        <v>458</v>
+      </c>
+      <c r="C148" t="s">
+        <v>481</v>
+      </c>
+      <c r="E148" t="s">
+        <v>460</v>
+      </c>
+      <c r="F148" t="s">
+        <v>54</v>
+      </c>
+      <c r="I148" t="s">
+        <v>482</v>
+      </c>
+      <c r="J148" t="s">
+        <v>458</v>
+      </c>
+      <c r="L148" t="s">
+        <v>462</v>
+      </c>
+      <c r="M148" t="s">
+        <v>463</v>
+      </c>
+      <c r="N148" t="s">
+        <v>464</v>
+      </c>
+      <c r="O148" t="s">
+        <v>481</v>
+      </c>
+      <c r="P148" t="s">
+        <v>481</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>1</v>
+      </c>
+      <c r="B149" t="s">
+        <v>458</v>
+      </c>
+      <c r="C149" t="s">
+        <v>483</v>
+      </c>
+      <c r="E149" t="s">
+        <v>460</v>
+      </c>
+      <c r="F149" t="s">
+        <v>54</v>
+      </c>
+      <c r="I149" t="s">
+        <v>484</v>
+      </c>
+      <c r="J149" t="s">
+        <v>458</v>
+      </c>
+      <c r="L149" t="s">
+        <v>462</v>
+      </c>
+      <c r="M149" t="s">
+        <v>463</v>
+      </c>
+      <c r="N149" t="s">
+        <v>464</v>
+      </c>
+      <c r="O149" t="s">
+        <v>483</v>
+      </c>
+      <c r="P149" t="s">
+        <v>483</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>1</v>
+      </c>
+      <c r="B150" t="s">
+        <v>458</v>
+      </c>
+      <c r="C150" t="s">
+        <v>485</v>
+      </c>
+      <c r="E150" t="s">
+        <v>460</v>
+      </c>
+      <c r="F150" t="s">
+        <v>54</v>
+      </c>
+      <c r="I150" t="s">
+        <v>486</v>
+      </c>
+      <c r="J150" t="s">
+        <v>458</v>
+      </c>
+      <c r="L150" t="s">
+        <v>462</v>
+      </c>
+      <c r="M150" t="s">
+        <v>463</v>
+      </c>
+      <c r="N150" t="s">
+        <v>464</v>
+      </c>
+      <c r="O150" t="s">
+        <v>485</v>
+      </c>
+      <c r="P150" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>1</v>
+      </c>
+      <c r="B151" t="s">
+        <v>458</v>
+      </c>
+      <c r="C151" t="s">
+        <v>487</v>
+      </c>
+      <c r="E151" t="s">
+        <v>460</v>
+      </c>
+      <c r="F151" t="s">
+        <v>54</v>
+      </c>
+      <c r="I151" t="s">
+        <v>488</v>
+      </c>
+      <c r="J151" t="s">
+        <v>458</v>
+      </c>
+      <c r="L151" t="s">
+        <v>462</v>
+      </c>
+      <c r="M151" t="s">
+        <v>463</v>
+      </c>
+      <c r="N151" t="s">
+        <v>464</v>
+      </c>
+      <c r="O151" t="s">
+        <v>487</v>
+      </c>
+      <c r="P151" t="s">
+        <v>487</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>1</v>
+      </c>
+      <c r="B152" t="s">
+        <v>458</v>
+      </c>
+      <c r="C152" t="s">
+        <v>489</v>
+      </c>
+      <c r="E152" t="s">
+        <v>460</v>
+      </c>
+      <c r="F152" t="s">
+        <v>54</v>
+      </c>
+      <c r="I152" t="s">
+        <v>490</v>
+      </c>
+      <c r="J152" t="s">
+        <v>458</v>
+      </c>
+      <c r="L152" t="s">
+        <v>462</v>
+      </c>
+      <c r="M152" t="s">
+        <v>463</v>
+      </c>
+      <c r="N152" t="s">
+        <v>464</v>
+      </c>
+      <c r="O152" t="s">
+        <v>489</v>
+      </c>
+      <c r="P152" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>1</v>
+      </c>
+      <c r="B153" t="s">
+        <v>458</v>
+      </c>
+      <c r="C153" t="s">
+        <v>491</v>
+      </c>
+      <c r="E153" t="s">
+        <v>460</v>
+      </c>
+      <c r="F153" t="s">
+        <v>54</v>
+      </c>
+      <c r="I153" t="s">
+        <v>492</v>
+      </c>
+      <c r="J153" t="s">
+        <v>458</v>
+      </c>
+      <c r="L153" t="s">
+        <v>462</v>
+      </c>
+      <c r="M153" t="s">
+        <v>463</v>
+      </c>
+      <c r="N153" t="s">
+        <v>464</v>
+      </c>
+      <c r="O153" t="s">
+        <v>491</v>
+      </c>
+      <c r="P153" t="s">
+        <v>491</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>1</v>
+      </c>
+      <c r="B154" t="s">
+        <v>458</v>
+      </c>
+      <c r="C154" t="s">
+        <v>493</v>
+      </c>
+      <c r="E154" t="s">
+        <v>460</v>
+      </c>
+      <c r="F154" t="s">
+        <v>54</v>
+      </c>
+      <c r="I154" t="s">
+        <v>494</v>
+      </c>
+      <c r="J154" t="s">
+        <v>458</v>
+      </c>
+      <c r="L154" t="s">
+        <v>462</v>
+      </c>
+      <c r="M154" t="s">
+        <v>463</v>
+      </c>
+      <c r="N154" t="s">
+        <v>464</v>
+      </c>
+      <c r="O154" t="s">
+        <v>493</v>
+      </c>
+      <c r="P154" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>1</v>
+      </c>
+      <c r="B155" t="s">
+        <v>458</v>
+      </c>
+      <c r="C155" t="s">
+        <v>495</v>
+      </c>
+      <c r="E155" t="s">
+        <v>460</v>
+      </c>
+      <c r="F155" t="s">
+        <v>54</v>
+      </c>
+      <c r="I155" t="s">
+        <v>496</v>
+      </c>
+      <c r="J155" t="s">
+        <v>458</v>
+      </c>
+      <c r="L155" t="s">
+        <v>462</v>
+      </c>
+      <c r="M155" t="s">
+        <v>463</v>
+      </c>
+      <c r="N155" t="s">
+        <v>464</v>
+      </c>
+      <c r="O155" t="s">
+        <v>495</v>
+      </c>
+      <c r="P155" t="s">
+        <v>495</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>1</v>
+      </c>
+      <c r="B156" t="s">
+        <v>458</v>
+      </c>
+      <c r="C156" t="s">
+        <v>497</v>
+      </c>
+      <c r="E156" t="s">
+        <v>460</v>
+      </c>
+      <c r="F156" t="s">
+        <v>54</v>
+      </c>
+      <c r="I156" t="s">
+        <v>498</v>
+      </c>
+      <c r="J156" t="s">
+        <v>458</v>
+      </c>
+      <c r="L156" t="s">
+        <v>462</v>
+      </c>
+      <c r="M156" t="s">
+        <v>463</v>
+      </c>
+      <c r="N156" t="s">
+        <v>464</v>
+      </c>
+      <c r="O156" t="s">
+        <v>497</v>
+      </c>
+      <c r="P156" t="s">
+        <v>497</v>
+      </c>
+      <c r="Q156" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>1</v>
+      </c>
+      <c r="B157" t="s">
+        <v>458</v>
+      </c>
+      <c r="C157" t="s">
+        <v>499</v>
+      </c>
+      <c r="E157" t="s">
+        <v>460</v>
+      </c>
+      <c r="F157" t="s">
+        <v>54</v>
+      </c>
+      <c r="I157" t="s">
+        <v>500</v>
+      </c>
+      <c r="J157" t="s">
+        <v>458</v>
+      </c>
+      <c r="L157" t="s">
+        <v>462</v>
+      </c>
+      <c r="M157" t="s">
+        <v>463</v>
+      </c>
+      <c r="N157" t="s">
+        <v>464</v>
+      </c>
+      <c r="O157" t="s">
+        <v>499</v>
+      </c>
+      <c r="P157" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>1</v>
+      </c>
+      <c r="B158" t="s">
+        <v>458</v>
+      </c>
+      <c r="C158" t="s">
+        <v>501</v>
+      </c>
+      <c r="E158" t="s">
+        <v>460</v>
+      </c>
+      <c r="F158" t="s">
+        <v>54</v>
+      </c>
+      <c r="I158" t="s">
+        <v>502</v>
+      </c>
+      <c r="J158" t="s">
+        <v>458</v>
+      </c>
+      <c r="L158" t="s">
+        <v>462</v>
+      </c>
+      <c r="M158" t="s">
+        <v>463</v>
+      </c>
+      <c r="N158" t="s">
+        <v>464</v>
+      </c>
+      <c r="O158" t="s">
+        <v>501</v>
+      </c>
+      <c r="P158" t="s">
+        <v>501</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>1</v>
+      </c>
+      <c r="B159" t="s">
+        <v>458</v>
+      </c>
+      <c r="C159" t="s">
+        <v>503</v>
+      </c>
+      <c r="E159" t="s">
+        <v>460</v>
+      </c>
+      <c r="F159" t="s">
+        <v>54</v>
+      </c>
+      <c r="I159" t="s">
+        <v>504</v>
+      </c>
+      <c r="J159" t="s">
+        <v>458</v>
+      </c>
+      <c r="L159" t="s">
+        <v>462</v>
+      </c>
+      <c r="M159" t="s">
+        <v>463</v>
+      </c>
+      <c r="N159" t="s">
+        <v>464</v>
+      </c>
+      <c r="O159" t="s">
+        <v>503</v>
+      </c>
+      <c r="P159" t="s">
+        <v>503</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>1</v>
+      </c>
+      <c r="B160" t="s">
+        <v>458</v>
+      </c>
+      <c r="C160" t="s">
+        <v>505</v>
+      </c>
+      <c r="E160" t="s">
+        <v>460</v>
+      </c>
+      <c r="F160" t="s">
+        <v>54</v>
+      </c>
+      <c r="I160" t="s">
+        <v>506</v>
+      </c>
+      <c r="J160" t="s">
+        <v>458</v>
+      </c>
+      <c r="L160" t="s">
+        <v>462</v>
+      </c>
+      <c r="M160" t="s">
+        <v>463</v>
+      </c>
+      <c r="N160" t="s">
+        <v>464</v>
+      </c>
+      <c r="O160" t="s">
+        <v>505</v>
+      </c>
+      <c r="P160" t="s">
+        <v>505</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>1</v>
+      </c>
+      <c r="B161" t="s">
+        <v>458</v>
+      </c>
+      <c r="C161" t="s">
+        <v>507</v>
+      </c>
+      <c r="E161" t="s">
+        <v>460</v>
+      </c>
+      <c r="F161" t="s">
+        <v>54</v>
+      </c>
+      <c r="I161" t="s">
+        <v>508</v>
+      </c>
+      <c r="J161" t="s">
+        <v>458</v>
+      </c>
+      <c r="L161" t="s">
+        <v>462</v>
+      </c>
+      <c r="M161" t="s">
+        <v>463</v>
+      </c>
+      <c r="N161" t="s">
+        <v>464</v>
+      </c>
+      <c r="O161" t="s">
+        <v>507</v>
+      </c>
+      <c r="P161" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>1</v>
+      </c>
+      <c r="B162" t="s">
+        <v>458</v>
+      </c>
+      <c r="C162" t="s">
+        <v>509</v>
+      </c>
+      <c r="E162" t="s">
+        <v>460</v>
+      </c>
+      <c r="F162" t="s">
+        <v>54</v>
+      </c>
+      <c r="I162" t="s">
+        <v>510</v>
+      </c>
+      <c r="J162" t="s">
+        <v>458</v>
+      </c>
+      <c r="L162" t="s">
+        <v>462</v>
+      </c>
+      <c r="M162" t="s">
+        <v>463</v>
+      </c>
+      <c r="N162" t="s">
+        <v>464</v>
+      </c>
+      <c r="O162" t="s">
+        <v>509</v>
+      </c>
+      <c r="P162" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>1</v>
+      </c>
+      <c r="B163" t="s">
+        <v>458</v>
+      </c>
+      <c r="C163" t="s">
+        <v>511</v>
+      </c>
+      <c r="E163" t="s">
+        <v>460</v>
+      </c>
+      <c r="F163" t="s">
+        <v>54</v>
+      </c>
+      <c r="I163" t="s">
+        <v>512</v>
+      </c>
+      <c r="J163" t="s">
+        <v>458</v>
+      </c>
+      <c r="L163" t="s">
+        <v>462</v>
+      </c>
+      <c r="M163" t="s">
+        <v>463</v>
+      </c>
+      <c r="N163" t="s">
+        <v>464</v>
+      </c>
+      <c r="O163" t="s">
+        <v>511</v>
+      </c>
+      <c r="P163" t="s">
+        <v>511</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>1</v>
+      </c>
+      <c r="B164" t="s">
+        <v>513</v>
+      </c>
+      <c r="C164" t="s">
+        <v>514</v>
+      </c>
+      <c r="E164" t="s">
+        <v>460</v>
+      </c>
+      <c r="F164" t="s">
+        <v>54</v>
+      </c>
+      <c r="I164" t="s">
+        <v>515</v>
+      </c>
+      <c r="J164" t="s">
+        <v>513</v>
+      </c>
+      <c r="L164" t="s">
+        <v>516</v>
+      </c>
+      <c r="M164" t="s">
+        <v>517</v>
+      </c>
+      <c r="N164" t="s">
+        <v>518</v>
+      </c>
+      <c r="O164" t="s">
+        <v>514</v>
+      </c>
+      <c r="P164" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>1</v>
+      </c>
+      <c r="B165" t="s">
+        <v>513</v>
+      </c>
+      <c r="C165" t="s">
+        <v>519</v>
+      </c>
+      <c r="E165" t="s">
+        <v>460</v>
+      </c>
+      <c r="F165" t="s">
+        <v>54</v>
+      </c>
+      <c r="I165" t="s">
+        <v>520</v>
+      </c>
+      <c r="J165" t="s">
+        <v>513</v>
+      </c>
+      <c r="L165" t="s">
+        <v>516</v>
+      </c>
+      <c r="M165" t="s">
+        <v>517</v>
+      </c>
+      <c r="N165" t="s">
+        <v>518</v>
+      </c>
+      <c r="O165" t="s">
+        <v>519</v>
+      </c>
+      <c r="P165" t="s">
+        <v>519</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>1</v>
+      </c>
+      <c r="B166" t="s">
+        <v>513</v>
+      </c>
+      <c r="C166" t="s">
+        <v>521</v>
+      </c>
+      <c r="E166" t="s">
+        <v>460</v>
+      </c>
+      <c r="F166" t="s">
+        <v>54</v>
+      </c>
+      <c r="I166" t="s">
+        <v>522</v>
+      </c>
+      <c r="J166" t="s">
+        <v>513</v>
+      </c>
+      <c r="L166" t="s">
+        <v>516</v>
+      </c>
+      <c r="M166" t="s">
+        <v>517</v>
+      </c>
+      <c r="N166" t="s">
+        <v>518</v>
+      </c>
+      <c r="O166" t="s">
+        <v>521</v>
+      </c>
+      <c r="P166" t="s">
+        <v>521</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>1</v>
+      </c>
+      <c r="B167" t="s">
+        <v>513</v>
+      </c>
+      <c r="C167" t="s">
+        <v>523</v>
+      </c>
+      <c r="E167" t="s">
+        <v>460</v>
+      </c>
+      <c r="F167" t="s">
+        <v>54</v>
+      </c>
+      <c r="I167" t="s">
+        <v>524</v>
+      </c>
+      <c r="J167" t="s">
+        <v>513</v>
+      </c>
+      <c r="L167" t="s">
+        <v>516</v>
+      </c>
+      <c r="M167" t="s">
+        <v>517</v>
+      </c>
+      <c r="N167" t="s">
+        <v>518</v>
+      </c>
+      <c r="O167" t="s">
+        <v>523</v>
+      </c>
+      <c r="P167" t="s">
+        <v>523</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>1</v>
+      </c>
+      <c r="B168" t="s">
+        <v>513</v>
+      </c>
+      <c r="C168" t="s">
+        <v>525</v>
+      </c>
+      <c r="E168" t="s">
+        <v>460</v>
+      </c>
+      <c r="F168" t="s">
+        <v>54</v>
+      </c>
+      <c r="I168" t="s">
+        <v>526</v>
+      </c>
+      <c r="J168" t="s">
+        <v>513</v>
+      </c>
+      <c r="L168" t="s">
+        <v>516</v>
+      </c>
+      <c r="M168" t="s">
+        <v>517</v>
+      </c>
+      <c r="N168" t="s">
+        <v>518</v>
+      </c>
+      <c r="O168" t="s">
+        <v>525</v>
+      </c>
+      <c r="P168" t="s">
+        <v>525</v>
+      </c>
+      <c r="Q168" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>1</v>
+      </c>
+      <c r="B169" t="s">
+        <v>513</v>
+      </c>
+      <c r="C169" t="s">
+        <v>527</v>
+      </c>
+      <c r="E169" t="s">
+        <v>460</v>
+      </c>
+      <c r="F169" t="s">
+        <v>54</v>
+      </c>
+      <c r="I169" t="s">
+        <v>528</v>
+      </c>
+      <c r="J169" t="s">
+        <v>513</v>
+      </c>
+      <c r="L169" t="s">
+        <v>516</v>
+      </c>
+      <c r="M169" t="s">
+        <v>517</v>
+      </c>
+      <c r="N169" t="s">
+        <v>518</v>
+      </c>
+      <c r="O169" t="s">
+        <v>527</v>
+      </c>
+      <c r="P169" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q169" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>1</v>
+      </c>
+      <c r="B170" t="s">
+        <v>513</v>
+      </c>
+      <c r="C170" t="s">
+        <v>529</v>
+      </c>
+      <c r="E170" t="s">
+        <v>460</v>
+      </c>
+      <c r="F170" t="s">
+        <v>54</v>
+      </c>
+      <c r="I170" t="s">
+        <v>530</v>
+      </c>
+      <c r="J170" t="s">
+        <v>513</v>
+      </c>
+      <c r="L170" t="s">
+        <v>516</v>
+      </c>
+      <c r="M170" t="s">
+        <v>517</v>
+      </c>
+      <c r="N170" t="s">
+        <v>518</v>
+      </c>
+      <c r="O170" t="s">
+        <v>529</v>
+      </c>
+      <c r="P170" t="s">
+        <v>529</v>
+      </c>
+      <c r="Q170" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>1</v>
+      </c>
+      <c r="B171" t="s">
+        <v>513</v>
+      </c>
+      <c r="C171" t="s">
+        <v>531</v>
+      </c>
+      <c r="E171" t="s">
+        <v>460</v>
+      </c>
+      <c r="F171" t="s">
+        <v>54</v>
+      </c>
+      <c r="I171" t="s">
+        <v>532</v>
+      </c>
+      <c r="J171" t="s">
+        <v>513</v>
+      </c>
+      <c r="L171" t="s">
+        <v>516</v>
+      </c>
+      <c r="M171" t="s">
+        <v>517</v>
+      </c>
+      <c r="N171" t="s">
+        <v>518</v>
+      </c>
+      <c r="O171" t="s">
+        <v>531</v>
+      </c>
+      <c r="P171" t="s">
+        <v>531</v>
+      </c>
+      <c r="Q171" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>1</v>
+      </c>
+      <c r="B172" t="s">
+        <v>513</v>
+      </c>
+      <c r="C172" t="s">
+        <v>533</v>
+      </c>
+      <c r="E172" t="s">
+        <v>460</v>
+      </c>
+      <c r="F172" t="s">
+        <v>54</v>
+      </c>
+      <c r="I172" t="s">
+        <v>534</v>
+      </c>
+      <c r="J172" t="s">
+        <v>513</v>
+      </c>
+      <c r="L172" t="s">
+        <v>516</v>
+      </c>
+      <c r="M172" t="s">
+        <v>517</v>
+      </c>
+      <c r="N172" t="s">
+        <v>518</v>
+      </c>
+      <c r="O172" t="s">
+        <v>533</v>
+      </c>
+      <c r="P172" t="s">
+        <v>533</v>
+      </c>
+      <c r="Q172" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>1</v>
+      </c>
+      <c r="B173" t="s">
+        <v>513</v>
+      </c>
+      <c r="C173" t="s">
+        <v>535</v>
+      </c>
+      <c r="E173" t="s">
+        <v>460</v>
+      </c>
+      <c r="F173" t="s">
+        <v>54</v>
+      </c>
+      <c r="I173" t="s">
+        <v>536</v>
+      </c>
+      <c r="J173" t="s">
+        <v>513</v>
+      </c>
+      <c r="L173" t="s">
+        <v>516</v>
+      </c>
+      <c r="M173" t="s">
+        <v>517</v>
+      </c>
+      <c r="N173" t="s">
+        <v>518</v>
+      </c>
+      <c r="O173" t="s">
+        <v>535</v>
+      </c>
+      <c r="P173" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>535</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B29">
+    <cfRule type="duplicateValues" dxfId="53" priority="54"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B40:B53 B26:B28">
+    <cfRule type="duplicateValues" dxfId="52" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B65">
     <cfRule type="duplicateValues" dxfId="51" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B40:B53 B26:B28">
-    <cfRule type="duplicateValues" dxfId="50" priority="54"/>
+  <conditionalFormatting sqref="B66">
+    <cfRule type="duplicateValues" dxfId="50" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B65">
+  <conditionalFormatting sqref="B67">
     <cfRule type="duplicateValues" dxfId="49" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
+  <conditionalFormatting sqref="B68:B78">
     <cfRule type="duplicateValues" dxfId="48" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
-    <cfRule type="duplicateValues" dxfId="47" priority="48"/>
+  <conditionalFormatting sqref="B79">
+    <cfRule type="duplicateValues" dxfId="47" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B68:B78">
-    <cfRule type="duplicateValues" dxfId="46" priority="47"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B79">
-    <cfRule type="duplicateValues" dxfId="45" priority="45"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B80:B90 B132:B174 B31:B39">
-    <cfRule type="duplicateValues" dxfId="44" priority="37"/>
+  <conditionalFormatting sqref="B80:B90 B132:B138 B31:B39 B174">
+    <cfRule type="duplicateValues" dxfId="46" priority="39"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B91:B100">
-    <cfRule type="duplicateValues" dxfId="43" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B101">
-    <cfRule type="duplicateValues" dxfId="42" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B102:B133">
-    <cfRule type="duplicateValues" dxfId="41" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:C28">
-    <cfRule type="duplicateValues" dxfId="40" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="55"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C58:C62">
-    <cfRule type="duplicateValues" dxfId="39" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C68:C78">
-    <cfRule type="duplicateValues" dxfId="38" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C88:C89">
-    <cfRule type="duplicateValues" dxfId="37" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C91:C100">
-    <cfRule type="duplicateValues" dxfId="36" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H42">
+    <cfRule type="duplicateValues" dxfId="37" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H43">
+    <cfRule type="duplicateValues" dxfId="36" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H44">
     <cfRule type="duplicateValues" dxfId="35" priority="9"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H43">
+  <conditionalFormatting sqref="H45">
     <cfRule type="duplicateValues" dxfId="34" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H44">
+  <conditionalFormatting sqref="H46">
     <cfRule type="duplicateValues" dxfId="33" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H45">
-    <cfRule type="duplicateValues" dxfId="32" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H46">
-    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="H47">
-    <cfRule type="duplicateValues" dxfId="30" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H79">
-    <cfRule type="duplicateValues" dxfId="29" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H90:H100 H102:H174 H31:H39">
-    <cfRule type="duplicateValues" dxfId="28" priority="34"/>
+  <conditionalFormatting sqref="H90:H100 H102:H138 H31:H39 H174">
+    <cfRule type="duplicateValues" dxfId="30" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H101">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I59:I61">
-    <cfRule type="duplicateValues" dxfId="26" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I68:I78">
-    <cfRule type="duplicateValues" dxfId="25" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I89">
-    <cfRule type="duplicateValues" dxfId="24" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I91:I98 I100">
-    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I99">
-    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I105">
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I109">
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I113">
     <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I109">
+  <conditionalFormatting sqref="I117">
     <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I113">
+  <conditionalFormatting sqref="I121">
     <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I117">
+  <conditionalFormatting sqref="I125">
     <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I121">
+  <conditionalFormatting sqref="I129">
     <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I125">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I129">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="I133">
-    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:J36">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J37:J39">
+    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J40:J53">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J65">
-    <cfRule type="duplicateValues" dxfId="11" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J66">
-    <cfRule type="duplicateValues" dxfId="10" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67">
-    <cfRule type="duplicateValues" dxfId="9" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J68:J78">
-    <cfRule type="duplicateValues" dxfId="8" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J80:J89">
-    <cfRule type="duplicateValues" dxfId="7" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J91:J100">
-    <cfRule type="duplicateValues" dxfId="6" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J101">
-    <cfRule type="duplicateValues" dxfId="5" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J102:J133">
-    <cfRule type="duplicateValues" dxfId="4" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J132:J133">
-    <cfRule type="duplicateValues" dxfId="3" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J134:J137">
-    <cfRule type="duplicateValues" dxfId="2" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="68"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J138:J174 J90">
-    <cfRule type="duplicateValues" dxfId="1" priority="33"/>
+  <conditionalFormatting sqref="J138 J90 J174">
+    <cfRule type="duplicateValues" dxfId="2" priority="35"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J37:J39">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  <conditionalFormatting sqref="C139 C141">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I139 I141">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/resources/variable_schema_data_individual_nutrition_template.xlsx
+++ b/resources/variable_schema_data_individual_nutrition_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R Projects\SaeedR1987\public_health_resources\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saeed.rahman\Desktop\public_health_resources\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C2E13B0-CBB2-472C-A0F4-8E91FD1547DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C35C4ED-293A-44CB-B337-5EAF00278A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="345" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2058" uniqueCount="538">
   <si>
     <t>rule_type</t>
   </si>
@@ -1631,6 +1631,9 @@
   </si>
   <si>
     <t>54-59m,54-59</t>
+  </si>
+  <si>
+    <t>nut_muac_cm_noflag</t>
   </si>
 </sst>
 </file>
@@ -2511,7 +2514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S173"/>
+  <dimension ref="A1:S174"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26.140625" customWidth="1"/>
@@ -3472,25 +3475,25 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>537</v>
       </c>
       <c r="E30" t="s">
         <v>47</v>
       </c>
       <c r="F30" t="s">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="J30" t="s">
-        <v>87</v>
+        <v>537</v>
       </c>
       <c r="L30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="N30" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
@@ -3498,28 +3501,25 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>253</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
         <v>47</v>
       </c>
       <c r="F31" t="s">
-        <v>54</v>
-      </c>
-      <c r="I31" t="s">
-        <v>254</v>
+        <v>48</v>
       </c>
       <c r="J31" t="s">
-        <v>253</v>
+        <v>87</v>
       </c>
       <c r="L31" t="s">
-        <v>255</v>
+        <v>88</v>
       </c>
       <c r="M31" t="s">
-        <v>256</v>
+        <v>88</v>
       </c>
       <c r="N31" t="s">
-        <v>257</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
@@ -3527,7 +3527,7 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>403</v>
+        <v>253</v>
       </c>
       <c r="E32" t="s">
         <v>47</v>
@@ -3539,16 +3539,16 @@
         <v>254</v>
       </c>
       <c r="J32" t="s">
-        <v>403</v>
+        <v>253</v>
       </c>
       <c r="L32" t="s">
-        <v>406</v>
+        <v>255</v>
       </c>
       <c r="M32" t="s">
-        <v>412</v>
+        <v>256</v>
       </c>
       <c r="N32" t="s">
-        <v>411</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
@@ -3556,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>258</v>
+        <v>403</v>
       </c>
       <c r="E33" t="s">
         <v>47</v>
@@ -3568,16 +3568,16 @@
         <v>254</v>
       </c>
       <c r="J33" t="s">
-        <v>258</v>
+        <v>403</v>
       </c>
       <c r="L33" t="s">
-        <v>259</v>
+        <v>406</v>
       </c>
       <c r="M33" t="s">
-        <v>260</v>
+        <v>412</v>
       </c>
       <c r="N33" t="s">
-        <v>261</v>
+        <v>411</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
@@ -3585,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>404</v>
+        <v>258</v>
       </c>
       <c r="E34" t="s">
         <v>47</v>
@@ -3597,16 +3597,16 @@
         <v>254</v>
       </c>
       <c r="J34" t="s">
-        <v>404</v>
+        <v>258</v>
       </c>
       <c r="L34" t="s">
-        <v>407</v>
+        <v>259</v>
       </c>
       <c r="M34" t="s">
-        <v>413</v>
+        <v>260</v>
       </c>
       <c r="N34" t="s">
-        <v>410</v>
+        <v>261</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
@@ -3614,7 +3614,7 @@
         <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>262</v>
+        <v>404</v>
       </c>
       <c r="E35" t="s">
         <v>47</v>
@@ -3626,16 +3626,16 @@
         <v>254</v>
       </c>
       <c r="J35" t="s">
-        <v>262</v>
+        <v>404</v>
       </c>
       <c r="L35" t="s">
-        <v>263</v>
+        <v>407</v>
       </c>
       <c r="M35" t="s">
-        <v>260</v>
+        <v>413</v>
       </c>
       <c r="N35" t="s">
-        <v>264</v>
+        <v>410</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
@@ -3643,7 +3643,7 @@
         <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>405</v>
+        <v>262</v>
       </c>
       <c r="E36" t="s">
         <v>47</v>
@@ -3655,16 +3655,16 @@
         <v>254</v>
       </c>
       <c r="J36" t="s">
-        <v>405</v>
+        <v>262</v>
       </c>
       <c r="L36" t="s">
-        <v>408</v>
+        <v>263</v>
       </c>
       <c r="M36" t="s">
-        <v>414</v>
+        <v>260</v>
       </c>
       <c r="N36" t="s">
-        <v>409</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
@@ -3672,40 +3672,28 @@
         <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>293</v>
-      </c>
-      <c r="C37" t="s">
-        <v>297</v>
+        <v>405</v>
       </c>
       <c r="E37" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F37" t="s">
         <v>54</v>
       </c>
       <c r="I37" t="s">
-        <v>298</v>
+        <v>254</v>
       </c>
       <c r="J37" t="s">
-        <v>293</v>
+        <v>405</v>
       </c>
       <c r="L37" t="s">
-        <v>301</v>
+        <v>408</v>
       </c>
       <c r="M37" t="s">
-        <v>302</v>
+        <v>414</v>
       </c>
       <c r="N37" t="s">
-        <v>303</v>
-      </c>
-      <c r="O37" t="s">
-        <v>294</v>
-      </c>
-      <c r="P37" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>306</v>
+        <v>409</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.25">
@@ -3716,7 +3704,7 @@
         <v>293</v>
       </c>
       <c r="C38" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E38" t="s">
         <v>20</v>
@@ -3725,7 +3713,7 @@
         <v>54</v>
       </c>
       <c r="I38" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J38" t="s">
         <v>293</v>
@@ -3740,13 +3728,13 @@
         <v>303</v>
       </c>
       <c r="O38" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="P38" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="Q38" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
@@ -3757,7 +3745,7 @@
         <v>293</v>
       </c>
       <c r="C39" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E39" t="s">
         <v>20</v>
@@ -3766,7 +3754,7 @@
         <v>54</v>
       </c>
       <c r="I39" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J39" t="s">
         <v>293</v>
@@ -3781,13 +3769,13 @@
         <v>303</v>
       </c>
       <c r="O39" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="P39" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
@@ -3795,25 +3783,40 @@
         <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>268</v>
+        <v>293</v>
+      </c>
+      <c r="C40" t="s">
+        <v>295</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F40" t="s">
         <v>54</v>
       </c>
+      <c r="I40" t="s">
+        <v>300</v>
+      </c>
       <c r="J40" t="s">
-        <v>456</v>
+        <v>293</v>
       </c>
       <c r="L40" t="s">
-        <v>433</v>
+        <v>301</v>
       </c>
       <c r="M40" t="s">
-        <v>435</v>
+        <v>302</v>
       </c>
       <c r="N40" t="s">
-        <v>437</v>
+        <v>303</v>
+      </c>
+      <c r="O40" t="s">
+        <v>305</v>
+      </c>
+      <c r="P40" t="s">
+        <v>310</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
@@ -3821,7 +3824,7 @@
         <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>398</v>
+        <v>268</v>
       </c>
       <c r="E41" t="s">
         <v>47</v>
@@ -3830,16 +3833,16 @@
         <v>54</v>
       </c>
       <c r="J41" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="L41" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="M41" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N41" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
@@ -3847,7 +3850,7 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>267</v>
+        <v>398</v>
       </c>
       <c r="E42" t="s">
         <v>47</v>
@@ -3855,20 +3858,17 @@
       <c r="F42" t="s">
         <v>54</v>
       </c>
-      <c r="I42" t="s">
-        <v>254</v>
-      </c>
       <c r="J42" t="s">
-        <v>267</v>
+        <v>457</v>
       </c>
       <c r="L42" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="M42" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="N42" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
@@ -3876,7 +3876,7 @@
         <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>400</v>
+        <v>267</v>
       </c>
       <c r="E43" t="s">
         <v>47</v>
@@ -3888,16 +3888,16 @@
         <v>254</v>
       </c>
       <c r="J43" t="s">
-        <v>400</v>
+        <v>267</v>
       </c>
       <c r="L43" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="M43" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="N43" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
@@ -3905,7 +3905,7 @@
         <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>266</v>
+        <v>400</v>
       </c>
       <c r="E44" t="s">
         <v>47</v>
@@ -3917,16 +3917,16 @@
         <v>254</v>
       </c>
       <c r="J44" t="s">
-        <v>266</v>
+        <v>400</v>
       </c>
       <c r="L44" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="M44" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="N44" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
@@ -3934,7 +3934,7 @@
         <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>401</v>
+        <v>266</v>
       </c>
       <c r="E45" t="s">
         <v>47</v>
@@ -3946,16 +3946,16 @@
         <v>254</v>
       </c>
       <c r="J45" t="s">
-        <v>401</v>
+        <v>266</v>
       </c>
       <c r="L45" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="M45" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N45" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
@@ -3963,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>265</v>
+        <v>401</v>
       </c>
       <c r="E46" t="s">
         <v>47</v>
@@ -3975,16 +3975,16 @@
         <v>254</v>
       </c>
       <c r="J46" t="s">
-        <v>265</v>
+        <v>401</v>
       </c>
       <c r="L46" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="N46" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
@@ -3992,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>402</v>
+        <v>265</v>
       </c>
       <c r="E47" t="s">
         <v>47</v>
@@ -4004,16 +4004,16 @@
         <v>254</v>
       </c>
       <c r="J47" t="s">
-        <v>402</v>
+        <v>265</v>
       </c>
       <c r="L47" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="M47" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="N47" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
@@ -4021,40 +4021,28 @@
         <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>397</v>
-      </c>
-      <c r="C48" t="s">
-        <v>297</v>
+        <v>402</v>
       </c>
       <c r="E48" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F48" t="s">
         <v>54</v>
       </c>
       <c r="I48" t="s">
-        <v>297</v>
+        <v>254</v>
       </c>
       <c r="J48" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="L48" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="M48" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="N48" t="s">
-        <v>429</v>
-      </c>
-      <c r="O48" t="s">
-        <v>294</v>
-      </c>
-      <c r="P48" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>421</v>
+        <v>449</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
@@ -4065,7 +4053,7 @@
         <v>397</v>
       </c>
       <c r="C49" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E49" t="s">
         <v>20</v>
@@ -4074,7 +4062,7 @@
         <v>54</v>
       </c>
       <c r="I49" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J49" t="s">
         <v>397</v>
@@ -4089,13 +4077,13 @@
         <v>429</v>
       </c>
       <c r="O49" t="s">
-        <v>416</v>
+        <v>294</v>
       </c>
       <c r="P49" t="s">
-        <v>416</v>
+        <v>294</v>
       </c>
       <c r="Q49" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
@@ -4106,7 +4094,7 @@
         <v>397</v>
       </c>
       <c r="C50" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E50" t="s">
         <v>20</v>
@@ -4115,7 +4103,7 @@
         <v>54</v>
       </c>
       <c r="I50" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J50" t="s">
         <v>397</v>
@@ -4130,13 +4118,13 @@
         <v>429</v>
       </c>
       <c r="O50" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="P50" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q50" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
@@ -4144,10 +4132,10 @@
         <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C51" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E51" t="s">
         <v>20</v>
@@ -4156,28 +4144,28 @@
         <v>54</v>
       </c>
       <c r="I51" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J51" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="L51" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="M51" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N51" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="O51" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="P51" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q51" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
@@ -4188,7 +4176,7 @@
         <v>399</v>
       </c>
       <c r="C52" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E52" t="s">
         <v>20</v>
@@ -4197,7 +4185,7 @@
         <v>54</v>
       </c>
       <c r="I52" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="J52" t="s">
         <v>399</v>
@@ -4212,13 +4200,13 @@
         <v>430</v>
       </c>
       <c r="O52" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="P52" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q52" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
@@ -4229,7 +4217,7 @@
         <v>399</v>
       </c>
       <c r="C53" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E53" t="s">
         <v>20</v>
@@ -4238,7 +4226,7 @@
         <v>54</v>
       </c>
       <c r="I53" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J53" t="s">
         <v>399</v>
@@ -4253,13 +4241,13 @@
         <v>430</v>
       </c>
       <c r="O53" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="P53" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="Q53" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
@@ -4267,40 +4255,40 @@
         <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>399</v>
       </c>
       <c r="C54" t="s">
-        <v>65</v>
+        <v>295</v>
       </c>
       <c r="E54" t="s">
         <v>20</v>
       </c>
       <c r="F54" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="I54" t="s">
-        <v>91</v>
+        <v>295</v>
       </c>
       <c r="J54" t="s">
-        <v>90</v>
+        <v>399</v>
       </c>
       <c r="L54" t="s">
-        <v>92</v>
+        <v>428</v>
       </c>
       <c r="M54" t="s">
-        <v>93</v>
+        <v>432</v>
       </c>
       <c r="N54" t="s">
-        <v>94</v>
+        <v>430</v>
       </c>
       <c r="O54" t="s">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="P54" t="s">
-        <v>71</v>
+        <v>420</v>
       </c>
       <c r="Q54" t="s">
-        <v>72</v>
+        <v>426</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
@@ -4311,7 +4299,7 @@
         <v>90</v>
       </c>
       <c r="C55" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E55" t="s">
         <v>20</v>
@@ -4320,7 +4308,7 @@
         <v>32</v>
       </c>
       <c r="I55" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J55" t="s">
         <v>90</v>
@@ -4335,13 +4323,13 @@
         <v>94</v>
       </c>
       <c r="O55" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P55" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q55" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
@@ -4349,10 +4337,10 @@
         <v>1</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C56" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E56" t="s">
         <v>20</v>
@@ -4361,28 +4349,28 @@
         <v>32</v>
       </c>
       <c r="I56" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="L56" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="M56" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="N56" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="O56" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P56" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q56" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
@@ -4393,7 +4381,7 @@
         <v>96</v>
       </c>
       <c r="C57" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E57" t="s">
         <v>20</v>
@@ -4402,7 +4390,7 @@
         <v>32</v>
       </c>
       <c r="I57" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J57" t="s">
         <v>96</v>
@@ -4417,13 +4405,13 @@
         <v>99</v>
       </c>
       <c r="O57" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P57" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q57" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
@@ -4431,10 +4419,10 @@
         <v>1</v>
       </c>
       <c r="B58" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C58" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E58" t="s">
         <v>20</v>
@@ -4443,28 +4431,28 @@
         <v>32</v>
       </c>
       <c r="I58" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="J58" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L58" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="M58" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="N58" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O58" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="P58" t="s">
-        <v>107</v>
+        <v>75</v>
       </c>
       <c r="Q58" t="s">
-        <v>108</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
@@ -4475,7 +4463,7 @@
         <v>100</v>
       </c>
       <c r="C59" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E59" t="s">
         <v>20</v>
@@ -4484,7 +4472,7 @@
         <v>32</v>
       </c>
       <c r="I59" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="J59" t="s">
         <v>100</v>
@@ -4499,13 +4487,13 @@
         <v>105</v>
       </c>
       <c r="O59" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="P59" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="Q59" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
@@ -4516,7 +4504,7 @@
         <v>100</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E60" t="s">
         <v>20</v>
@@ -4525,7 +4513,7 @@
         <v>32</v>
       </c>
       <c r="I60" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J60" t="s">
         <v>100</v>
@@ -4540,13 +4528,13 @@
         <v>105</v>
       </c>
       <c r="O60" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="P60" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="Q60" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
@@ -4557,7 +4545,7 @@
         <v>100</v>
       </c>
       <c r="C61" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E61" t="s">
         <v>20</v>
@@ -4566,7 +4554,7 @@
         <v>32</v>
       </c>
       <c r="I61" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="J61" t="s">
         <v>100</v>
@@ -4581,13 +4569,13 @@
         <v>105</v>
       </c>
       <c r="O61" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="P61" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Q61" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
@@ -4598,7 +4586,7 @@
         <v>100</v>
       </c>
       <c r="C62" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E62" t="s">
         <v>20</v>
@@ -4607,7 +4595,7 @@
         <v>32</v>
       </c>
       <c r="I62" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J62" t="s">
         <v>100</v>
@@ -4622,13 +4610,13 @@
         <v>105</v>
       </c>
       <c r="O62" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="P62" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="Q62" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
@@ -4636,10 +4624,10 @@
         <v>1</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C63" t="s">
-        <v>65</v>
+        <v>121</v>
       </c>
       <c r="E63" t="s">
         <v>20</v>
@@ -4648,28 +4636,28 @@
         <v>32</v>
       </c>
       <c r="I63" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J63" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="L63" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="M63" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="N63" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="O63" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="P63" t="s">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="Q63" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
@@ -4680,7 +4668,7 @@
         <v>126</v>
       </c>
       <c r="C64" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E64" t="s">
         <v>20</v>
@@ -4689,7 +4677,7 @@
         <v>32</v>
       </c>
       <c r="I64" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J64" t="s">
         <v>126</v>
@@ -4704,13 +4692,13 @@
         <v>129</v>
       </c>
       <c r="O64" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P64" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q64" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
@@ -4718,10 +4706,10 @@
         <v>1</v>
       </c>
       <c r="B65" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C65" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E65" t="s">
         <v>20</v>
@@ -4730,28 +4718,28 @@
         <v>32</v>
       </c>
       <c r="I65" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="J65" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="L65" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M65" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="N65" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="O65" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="P65" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="Q65" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
@@ -4762,7 +4750,7 @@
         <v>130</v>
       </c>
       <c r="C66" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E66" t="s">
         <v>20</v>
@@ -4771,7 +4759,7 @@
         <v>32</v>
       </c>
       <c r="I66" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J66" t="s">
         <v>130</v>
@@ -4786,13 +4774,13 @@
         <v>133</v>
       </c>
       <c r="O66" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P66" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q66" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
@@ -4803,7 +4791,7 @@
         <v>130</v>
       </c>
       <c r="C67" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="E67" t="s">
         <v>20</v>
@@ -4812,7 +4800,7 @@
         <v>32</v>
       </c>
       <c r="I67" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J67" t="s">
         <v>130</v>
@@ -4827,13 +4815,13 @@
         <v>133</v>
       </c>
       <c r="O67" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="P67" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Q67" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
@@ -4841,40 +4829,40 @@
         <v>1</v>
       </c>
       <c r="B68" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C68" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E68" t="s">
         <v>20</v>
       </c>
       <c r="F68" t="s">
-        <v>137</v>
+        <v>32</v>
       </c>
       <c r="I68" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="J68" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="L68" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M68" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="N68" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="O68" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="P68" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="Q68" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
@@ -4885,7 +4873,7 @@
         <v>135</v>
       </c>
       <c r="C69" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="E69" t="s">
         <v>20</v>
@@ -4894,7 +4882,7 @@
         <v>137</v>
       </c>
       <c r="I69" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="J69" t="s">
         <v>138</v>
@@ -4909,13 +4897,13 @@
         <v>141</v>
       </c>
       <c r="O69" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="P69" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q69" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
@@ -4926,7 +4914,7 @@
         <v>135</v>
       </c>
       <c r="C70" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E70" t="s">
         <v>20</v>
@@ -4935,7 +4923,7 @@
         <v>137</v>
       </c>
       <c r="I70" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="J70" t="s">
         <v>138</v>
@@ -4950,13 +4938,13 @@
         <v>141</v>
       </c>
       <c r="O70" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="P70" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Q70" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
@@ -4967,7 +4955,7 @@
         <v>135</v>
       </c>
       <c r="C71" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E71" t="s">
         <v>20</v>
@@ -4976,7 +4964,7 @@
         <v>137</v>
       </c>
       <c r="I71" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J71" t="s">
         <v>138</v>
@@ -4991,13 +4979,13 @@
         <v>141</v>
       </c>
       <c r="O71" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="P71" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Q71" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
@@ -5008,7 +4996,7 @@
         <v>135</v>
       </c>
       <c r="C72" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E72" t="s">
         <v>20</v>
@@ -5017,7 +5005,7 @@
         <v>137</v>
       </c>
       <c r="I72" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="J72" t="s">
         <v>138</v>
@@ -5032,13 +5020,13 @@
         <v>141</v>
       </c>
       <c r="O72" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="P72" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="Q72" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.25">
@@ -5049,7 +5037,7 @@
         <v>135</v>
       </c>
       <c r="C73" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E73" t="s">
         <v>20</v>
@@ -5058,7 +5046,7 @@
         <v>137</v>
       </c>
       <c r="I73" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="J73" t="s">
         <v>138</v>
@@ -5073,13 +5061,13 @@
         <v>141</v>
       </c>
       <c r="O73" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="P73" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="Q73" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
@@ -5090,7 +5078,7 @@
         <v>135</v>
       </c>
       <c r="C74" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E74" t="s">
         <v>20</v>
@@ -5099,7 +5087,7 @@
         <v>137</v>
       </c>
       <c r="I74" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="J74" t="s">
         <v>138</v>
@@ -5114,13 +5102,13 @@
         <v>141</v>
       </c>
       <c r="O74" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="P74" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="Q74" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
@@ -5131,7 +5119,7 @@
         <v>135</v>
       </c>
       <c r="C75" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E75" t="s">
         <v>20</v>
@@ -5140,7 +5128,7 @@
         <v>137</v>
       </c>
       <c r="I75" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="J75" t="s">
         <v>138</v>
@@ -5155,13 +5143,13 @@
         <v>141</v>
       </c>
       <c r="O75" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="P75" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="Q75" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
@@ -5172,7 +5160,7 @@
         <v>135</v>
       </c>
       <c r="C76" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E76" t="s">
         <v>20</v>
@@ -5181,7 +5169,7 @@
         <v>137</v>
       </c>
       <c r="I76" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J76" t="s">
         <v>138</v>
@@ -5196,13 +5184,13 @@
         <v>141</v>
       </c>
       <c r="O76" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P76" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Q76" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
@@ -5213,7 +5201,7 @@
         <v>135</v>
       </c>
       <c r="C77" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E77" t="s">
         <v>20</v>
@@ -5222,7 +5210,7 @@
         <v>137</v>
       </c>
       <c r="I77" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J77" t="s">
         <v>138</v>
@@ -5237,13 +5225,13 @@
         <v>141</v>
       </c>
       <c r="O77" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="P77" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q77" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
@@ -5254,7 +5242,7 @@
         <v>135</v>
       </c>
       <c r="C78" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E78" t="s">
         <v>20</v>
@@ -5263,7 +5251,7 @@
         <v>137</v>
       </c>
       <c r="I78" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="J78" t="s">
         <v>138</v>
@@ -5278,13 +5266,13 @@
         <v>141</v>
       </c>
       <c r="O78" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="P78" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="Q78" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
@@ -5292,28 +5280,40 @@
         <v>1</v>
       </c>
       <c r="B79" t="s">
-        <v>167</v>
+        <v>135</v>
+      </c>
+      <c r="C79" t="s">
+        <v>163</v>
       </c>
       <c r="E79" t="s">
         <v>20</v>
       </c>
       <c r="F79" t="s">
-        <v>168</v>
-      </c>
-      <c r="G79" t="b">
-        <v>1</v>
-      </c>
-      <c r="H79" t="s">
-        <v>135</v>
+        <v>137</v>
+      </c>
+      <c r="I79" t="s">
+        <v>163</v>
+      </c>
+      <c r="J79" t="s">
+        <v>138</v>
       </c>
       <c r="L79" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="M79" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="N79" t="s">
-        <v>171</v>
+        <v>141</v>
+      </c>
+      <c r="O79" t="s">
+        <v>164</v>
+      </c>
+      <c r="P79" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
@@ -5321,40 +5321,28 @@
         <v>1</v>
       </c>
       <c r="B80" t="s">
-        <v>172</v>
-      </c>
-      <c r="C80" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E80" t="s">
         <v>20</v>
       </c>
       <c r="F80" t="s">
-        <v>137</v>
-      </c>
-      <c r="I80" t="s">
-        <v>174</v>
-      </c>
-      <c r="J80" t="s">
-        <v>175</v>
+        <v>168</v>
+      </c>
+      <c r="G80" t="b">
+        <v>1</v>
+      </c>
+      <c r="H80" t="s">
+        <v>135</v>
       </c>
       <c r="L80" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="M80" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="N80" t="s">
-        <v>178</v>
-      </c>
-      <c r="O80" t="s">
-        <v>179</v>
-      </c>
-      <c r="P80" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
@@ -5365,7 +5353,7 @@
         <v>172</v>
       </c>
       <c r="C81" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E81" t="s">
         <v>20</v>
@@ -5374,7 +5362,7 @@
         <v>137</v>
       </c>
       <c r="I81" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="J81" t="s">
         <v>175</v>
@@ -5389,13 +5377,13 @@
         <v>178</v>
       </c>
       <c r="O81" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P81" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q81" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
@@ -5406,7 +5394,7 @@
         <v>172</v>
       </c>
       <c r="C82" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E82" t="s">
         <v>20</v>
@@ -5415,7 +5403,7 @@
         <v>137</v>
       </c>
       <c r="I82" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="J82" t="s">
         <v>175</v>
@@ -5430,13 +5418,13 @@
         <v>178</v>
       </c>
       <c r="O82" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P82" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="Q82" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
@@ -5447,7 +5435,7 @@
         <v>172</v>
       </c>
       <c r="C83" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E83" t="s">
         <v>20</v>
@@ -5456,7 +5444,7 @@
         <v>137</v>
       </c>
       <c r="I83" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="J83" t="s">
         <v>175</v>
@@ -5471,13 +5459,13 @@
         <v>178</v>
       </c>
       <c r="O83" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P83" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="Q83" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
@@ -5488,7 +5476,7 @@
         <v>172</v>
       </c>
       <c r="C84" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E84" t="s">
         <v>20</v>
@@ -5497,7 +5485,7 @@
         <v>137</v>
       </c>
       <c r="I84" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="J84" t="s">
         <v>175</v>
@@ -5512,13 +5500,13 @@
         <v>178</v>
       </c>
       <c r="O84" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P84" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="Q84" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
@@ -5529,7 +5517,7 @@
         <v>172</v>
       </c>
       <c r="C85" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E85" t="s">
         <v>20</v>
@@ -5538,7 +5526,7 @@
         <v>137</v>
       </c>
       <c r="I85" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="J85" t="s">
         <v>175</v>
@@ -5553,13 +5541,13 @@
         <v>178</v>
       </c>
       <c r="O85" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="P85" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q85" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
@@ -5570,7 +5558,7 @@
         <v>172</v>
       </c>
       <c r="C86" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E86" t="s">
         <v>20</v>
@@ -5579,7 +5567,7 @@
         <v>137</v>
       </c>
       <c r="I86" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J86" t="s">
         <v>175</v>
@@ -5594,13 +5582,13 @@
         <v>178</v>
       </c>
       <c r="O86" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="P86" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="Q86" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
@@ -5611,7 +5599,7 @@
         <v>172</v>
       </c>
       <c r="C87" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E87" t="s">
         <v>20</v>
@@ -5620,7 +5608,7 @@
         <v>137</v>
       </c>
       <c r="I87" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J87" t="s">
         <v>175</v>
@@ -5635,13 +5623,13 @@
         <v>178</v>
       </c>
       <c r="O87" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="P87" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="Q87" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
@@ -5652,7 +5640,7 @@
         <v>172</v>
       </c>
       <c r="C88" t="s">
-        <v>134</v>
+        <v>197</v>
       </c>
       <c r="E88" t="s">
         <v>20</v>
@@ -5661,7 +5649,7 @@
         <v>137</v>
       </c>
       <c r="I88" t="s">
-        <v>122</v>
+        <v>197</v>
       </c>
       <c r="J88" t="s">
         <v>175</v>
@@ -5676,13 +5664,13 @@
         <v>178</v>
       </c>
       <c r="O88" t="s">
-        <v>123</v>
+        <v>198</v>
       </c>
       <c r="P88" t="s">
-        <v>124</v>
+        <v>198</v>
       </c>
       <c r="Q88" t="s">
-        <v>125</v>
+        <v>198</v>
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
@@ -5693,7 +5681,7 @@
         <v>172</v>
       </c>
       <c r="C89" t="s">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="E89" t="s">
         <v>20</v>
@@ -5702,7 +5690,7 @@
         <v>137</v>
       </c>
       <c r="I89" t="s">
-        <v>199</v>
+        <v>122</v>
       </c>
       <c r="J89" t="s">
         <v>175</v>
@@ -5717,13 +5705,13 @@
         <v>178</v>
       </c>
       <c r="O89" t="s">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="P89" t="s">
-        <v>161</v>
+        <v>124</v>
       </c>
       <c r="Q89" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
@@ -5731,31 +5719,40 @@
         <v>1</v>
       </c>
       <c r="B90" t="s">
-        <v>200</v>
+        <v>172</v>
+      </c>
+      <c r="C90" t="s">
+        <v>159</v>
       </c>
       <c r="E90" t="s">
         <v>20</v>
       </c>
       <c r="F90" t="s">
-        <v>168</v>
-      </c>
-      <c r="G90" t="b">
-        <v>1</v>
-      </c>
-      <c r="H90" t="s">
-        <v>172</v>
+        <v>137</v>
+      </c>
+      <c r="I90" t="s">
+        <v>199</v>
       </c>
       <c r="J90" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="L90" t="s">
-        <v>201</v>
+        <v>176</v>
       </c>
       <c r="M90" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="N90" t="s">
-        <v>203</v>
+        <v>178</v>
+      </c>
+      <c r="O90" t="s">
+        <v>160</v>
+      </c>
+      <c r="P90" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
@@ -5763,40 +5760,31 @@
         <v>1</v>
       </c>
       <c r="B91" t="s">
-        <v>204</v>
-      </c>
-      <c r="C91" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="E91" t="s">
         <v>20</v>
       </c>
       <c r="F91" t="s">
-        <v>137</v>
-      </c>
-      <c r="I91" t="s">
-        <v>205</v>
+        <v>168</v>
+      </c>
+      <c r="G91" t="b">
+        <v>1</v>
+      </c>
+      <c r="H91" t="s">
+        <v>172</v>
       </c>
       <c r="J91" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L91" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="M91" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="N91" t="s">
-        <v>208</v>
-      </c>
-      <c r="O91" t="s">
-        <v>209</v>
-      </c>
-      <c r="P91" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
@@ -5807,7 +5795,7 @@
         <v>204</v>
       </c>
       <c r="C92" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E92" t="s">
         <v>20</v>
@@ -5816,7 +5804,7 @@
         <v>137</v>
       </c>
       <c r="I92" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="J92" t="s">
         <v>204</v>
@@ -5831,13 +5819,13 @@
         <v>208</v>
       </c>
       <c r="O92" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="P92" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="Q92" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
@@ -5848,7 +5836,7 @@
         <v>204</v>
       </c>
       <c r="C93" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E93" t="s">
         <v>20</v>
@@ -5857,7 +5845,7 @@
         <v>137</v>
       </c>
       <c r="I93" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="J93" t="s">
         <v>204</v>
@@ -5872,13 +5860,13 @@
         <v>208</v>
       </c>
       <c r="O93" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="P93" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q93" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
@@ -5889,7 +5877,7 @@
         <v>204</v>
       </c>
       <c r="C94" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E94" t="s">
         <v>20</v>
@@ -5898,7 +5886,7 @@
         <v>137</v>
       </c>
       <c r="I94" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J94" t="s">
         <v>204</v>
@@ -5913,13 +5901,13 @@
         <v>208</v>
       </c>
       <c r="O94" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="P94" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="Q94" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
@@ -5930,7 +5918,7 @@
         <v>204</v>
       </c>
       <c r="C95" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E95" t="s">
         <v>20</v>
@@ -5939,7 +5927,7 @@
         <v>137</v>
       </c>
       <c r="I95" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="J95" t="s">
         <v>204</v>
@@ -5954,13 +5942,13 @@
         <v>208</v>
       </c>
       <c r="O95" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="P95" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Q95" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
@@ -5971,7 +5959,7 @@
         <v>204</v>
       </c>
       <c r="C96" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E96" t="s">
         <v>20</v>
@@ -5980,7 +5968,7 @@
         <v>137</v>
       </c>
       <c r="I96" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J96" t="s">
         <v>204</v>
@@ -5995,13 +5983,13 @@
         <v>208</v>
       </c>
       <c r="O96" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P96" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="Q96" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
@@ -6012,7 +6000,7 @@
         <v>204</v>
       </c>
       <c r="C97" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E97" t="s">
         <v>20</v>
@@ -6021,7 +6009,7 @@
         <v>137</v>
       </c>
       <c r="I97" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="J97" t="s">
         <v>204</v>
@@ -6036,13 +6024,13 @@
         <v>208</v>
       </c>
       <c r="O97" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="P97" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="Q97" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
@@ -6053,7 +6041,7 @@
         <v>204</v>
       </c>
       <c r="C98" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E98" t="s">
         <v>20</v>
@@ -6062,7 +6050,7 @@
         <v>137</v>
       </c>
       <c r="I98" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J98" t="s">
         <v>204</v>
@@ -6077,13 +6065,13 @@
         <v>208</v>
       </c>
       <c r="O98" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="P98" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="Q98" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
@@ -6094,7 +6082,7 @@
         <v>204</v>
       </c>
       <c r="C99" t="s">
-        <v>159</v>
+        <v>222</v>
       </c>
       <c r="E99" t="s">
         <v>20</v>
@@ -6103,7 +6091,7 @@
         <v>137</v>
       </c>
       <c r="I99" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="J99" t="s">
         <v>204</v>
@@ -6118,13 +6106,13 @@
         <v>208</v>
       </c>
       <c r="O99" t="s">
-        <v>160</v>
+        <v>223</v>
       </c>
       <c r="P99" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
       <c r="Q99" t="s">
-        <v>162</v>
+        <v>223</v>
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
@@ -6135,7 +6123,7 @@
         <v>204</v>
       </c>
       <c r="C100" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E100" t="s">
         <v>20</v>
@@ -6144,7 +6132,7 @@
         <v>137</v>
       </c>
       <c r="I100" t="s">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="J100" t="s">
         <v>204</v>
@@ -6159,13 +6147,13 @@
         <v>208</v>
       </c>
       <c r="O100" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="P100" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="Q100" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
@@ -6173,31 +6161,40 @@
         <v>1</v>
       </c>
       <c r="B101" t="s">
-        <v>225</v>
+        <v>204</v>
+      </c>
+      <c r="C101" t="s">
+        <v>163</v>
       </c>
       <c r="E101" t="s">
         <v>20</v>
       </c>
       <c r="F101" t="s">
-        <v>168</v>
-      </c>
-      <c r="G101" t="b">
-        <v>1</v>
-      </c>
-      <c r="H101" t="s">
+        <v>137</v>
+      </c>
+      <c r="I101" t="s">
+        <v>224</v>
+      </c>
+      <c r="J101" t="s">
         <v>204</v>
       </c>
-      <c r="J101" t="s">
-        <v>225</v>
-      </c>
       <c r="L101" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="M101" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="N101" t="s">
-        <v>228</v>
+        <v>208</v>
+      </c>
+      <c r="O101" t="s">
+        <v>164</v>
+      </c>
+      <c r="P101" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
@@ -6205,40 +6202,31 @@
         <v>1</v>
       </c>
       <c r="B102" t="s">
-        <v>229</v>
-      </c>
-      <c r="C102" t="s">
-        <v>65</v>
+        <v>225</v>
       </c>
       <c r="E102" t="s">
         <v>20</v>
       </c>
       <c r="F102" t="s">
-        <v>32</v>
-      </c>
-      <c r="I102" t="s">
-        <v>91</v>
+        <v>168</v>
+      </c>
+      <c r="G102" t="b">
+        <v>1</v>
+      </c>
+      <c r="H102" t="s">
+        <v>204</v>
       </c>
       <c r="J102" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L102" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="M102" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="N102" t="s">
-        <v>231</v>
-      </c>
-      <c r="O102" t="s">
-        <v>70</v>
-      </c>
-      <c r="P102" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>72</v>
+        <v>228</v>
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
@@ -6249,7 +6237,7 @@
         <v>229</v>
       </c>
       <c r="C103" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E103" t="s">
         <v>20</v>
@@ -6258,7 +6246,7 @@
         <v>32</v>
       </c>
       <c r="I103" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J103" t="s">
         <v>229</v>
@@ -6273,13 +6261,13 @@
         <v>231</v>
       </c>
       <c r="O103" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P103" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q103" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
@@ -6290,7 +6278,7 @@
         <v>229</v>
       </c>
       <c r="C104" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="E104" t="s">
         <v>20</v>
@@ -6299,7 +6287,7 @@
         <v>32</v>
       </c>
       <c r="I104" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J104" t="s">
         <v>229</v>
@@ -6314,13 +6302,13 @@
         <v>231</v>
       </c>
       <c r="O104" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="P104" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Q104" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
@@ -6331,7 +6319,7 @@
         <v>229</v>
       </c>
       <c r="C105" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="E105" t="s">
         <v>20</v>
@@ -6340,7 +6328,7 @@
         <v>32</v>
       </c>
       <c r="I105" t="s">
-        <v>224</v>
+        <v>122</v>
       </c>
       <c r="J105" t="s">
         <v>229</v>
@@ -6355,13 +6343,13 @@
         <v>231</v>
       </c>
       <c r="O105" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="P105" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="Q105" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
@@ -6369,10 +6357,10 @@
         <v>1</v>
       </c>
       <c r="B106" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C106" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="E106" t="s">
         <v>20</v>
@@ -6381,28 +6369,28 @@
         <v>32</v>
       </c>
       <c r="I106" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="J106" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L106" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="M106" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="N106" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O106" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="P106" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="Q106" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
@@ -6413,7 +6401,7 @@
         <v>232</v>
       </c>
       <c r="C107" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E107" t="s">
         <v>20</v>
@@ -6422,7 +6410,7 @@
         <v>32</v>
       </c>
       <c r="I107" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J107" t="s">
         <v>232</v>
@@ -6437,13 +6425,13 @@
         <v>234</v>
       </c>
       <c r="O107" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P107" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q107" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.25">
@@ -6454,7 +6442,7 @@
         <v>232</v>
       </c>
       <c r="C108" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="E108" t="s">
         <v>20</v>
@@ -6463,7 +6451,7 @@
         <v>32</v>
       </c>
       <c r="I108" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J108" t="s">
         <v>232</v>
@@ -6478,13 +6466,13 @@
         <v>234</v>
       </c>
       <c r="O108" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="P108" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Q108" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
@@ -6495,7 +6483,7 @@
         <v>232</v>
       </c>
       <c r="C109" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="E109" t="s">
         <v>20</v>
@@ -6504,7 +6492,7 @@
         <v>32</v>
       </c>
       <c r="I109" t="s">
-        <v>224</v>
+        <v>122</v>
       </c>
       <c r="J109" t="s">
         <v>232</v>
@@ -6519,13 +6507,13 @@
         <v>234</v>
       </c>
       <c r="O109" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="P109" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="Q109" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
@@ -6533,10 +6521,10 @@
         <v>1</v>
       </c>
       <c r="B110" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C110" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="E110" t="s">
         <v>20</v>
@@ -6545,28 +6533,28 @@
         <v>32</v>
       </c>
       <c r="I110" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="J110" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="L110" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="M110" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="N110" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="O110" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="P110" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="Q110" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
@@ -6577,7 +6565,7 @@
         <v>235</v>
       </c>
       <c r="C111" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E111" t="s">
         <v>20</v>
@@ -6586,7 +6574,7 @@
         <v>32</v>
       </c>
       <c r="I111" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J111" t="s">
         <v>235</v>
@@ -6601,13 +6589,13 @@
         <v>237</v>
       </c>
       <c r="O111" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P111" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q111" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
@@ -6618,7 +6606,7 @@
         <v>235</v>
       </c>
       <c r="C112" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="E112" t="s">
         <v>20</v>
@@ -6627,7 +6615,7 @@
         <v>32</v>
       </c>
       <c r="I112" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J112" t="s">
         <v>235</v>
@@ -6642,13 +6630,13 @@
         <v>237</v>
       </c>
       <c r="O112" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="P112" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Q112" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
@@ -6659,7 +6647,7 @@
         <v>235</v>
       </c>
       <c r="C113" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="E113" t="s">
         <v>20</v>
@@ -6668,7 +6656,7 @@
         <v>32</v>
       </c>
       <c r="I113" t="s">
-        <v>224</v>
+        <v>122</v>
       </c>
       <c r="J113" t="s">
         <v>235</v>
@@ -6683,13 +6671,13 @@
         <v>237</v>
       </c>
       <c r="O113" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="P113" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="Q113" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
@@ -6697,10 +6685,10 @@
         <v>1</v>
       </c>
       <c r="B114" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C114" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="E114" t="s">
         <v>20</v>
@@ -6709,28 +6697,28 @@
         <v>32</v>
       </c>
       <c r="I114" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="J114" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="L114" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M114" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="N114" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O114" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="P114" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="Q114" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
@@ -6741,7 +6729,7 @@
         <v>238</v>
       </c>
       <c r="C115" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E115" t="s">
         <v>20</v>
@@ -6750,7 +6738,7 @@
         <v>32</v>
       </c>
       <c r="I115" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J115" t="s">
         <v>238</v>
@@ -6765,13 +6753,13 @@
         <v>240</v>
       </c>
       <c r="O115" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P115" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q115" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
@@ -6782,7 +6770,7 @@
         <v>238</v>
       </c>
       <c r="C116" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="E116" t="s">
         <v>20</v>
@@ -6791,7 +6779,7 @@
         <v>32</v>
       </c>
       <c r="I116" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J116" t="s">
         <v>238</v>
@@ -6806,13 +6794,13 @@
         <v>240</v>
       </c>
       <c r="O116" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="P116" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Q116" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
@@ -6823,7 +6811,7 @@
         <v>238</v>
       </c>
       <c r="C117" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="E117" t="s">
         <v>20</v>
@@ -6832,7 +6820,7 @@
         <v>32</v>
       </c>
       <c r="I117" t="s">
-        <v>224</v>
+        <v>122</v>
       </c>
       <c r="J117" t="s">
         <v>238</v>
@@ -6847,13 +6835,13 @@
         <v>240</v>
       </c>
       <c r="O117" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="P117" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="Q117" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
@@ -6861,10 +6849,10 @@
         <v>1</v>
       </c>
       <c r="B118" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C118" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="E118" t="s">
         <v>20</v>
@@ -6873,28 +6861,28 @@
         <v>32</v>
       </c>
       <c r="I118" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="J118" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="L118" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M118" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N118" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O118" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="P118" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="Q118" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
@@ -6905,7 +6893,7 @@
         <v>241</v>
       </c>
       <c r="C119" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E119" t="s">
         <v>20</v>
@@ -6914,7 +6902,7 @@
         <v>32</v>
       </c>
       <c r="I119" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J119" t="s">
         <v>241</v>
@@ -6929,13 +6917,13 @@
         <v>243</v>
       </c>
       <c r="O119" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P119" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q119" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
@@ -6946,7 +6934,7 @@
         <v>241</v>
       </c>
       <c r="C120" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="E120" t="s">
         <v>20</v>
@@ -6955,7 +6943,7 @@
         <v>32</v>
       </c>
       <c r="I120" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J120" t="s">
         <v>241</v>
@@ -6970,13 +6958,13 @@
         <v>243</v>
       </c>
       <c r="O120" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="P120" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Q120" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
@@ -6987,7 +6975,7 @@
         <v>241</v>
       </c>
       <c r="C121" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="E121" t="s">
         <v>20</v>
@@ -6996,7 +6984,7 @@
         <v>32</v>
       </c>
       <c r="I121" t="s">
-        <v>224</v>
+        <v>122</v>
       </c>
       <c r="J121" t="s">
         <v>241</v>
@@ -7011,13 +6999,13 @@
         <v>243</v>
       </c>
       <c r="O121" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="P121" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="Q121" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
@@ -7025,10 +7013,10 @@
         <v>1</v>
       </c>
       <c r="B122" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C122" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="E122" t="s">
         <v>20</v>
@@ -7037,28 +7025,28 @@
         <v>32</v>
       </c>
       <c r="I122" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="J122" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L122" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="M122" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="N122" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O122" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="P122" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="Q122" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
@@ -7069,7 +7057,7 @@
         <v>244</v>
       </c>
       <c r="C123" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E123" t="s">
         <v>20</v>
@@ -7078,7 +7066,7 @@
         <v>32</v>
       </c>
       <c r="I123" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J123" t="s">
         <v>244</v>
@@ -7093,13 +7081,13 @@
         <v>246</v>
       </c>
       <c r="O123" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P123" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q123" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
@@ -7110,7 +7098,7 @@
         <v>244</v>
       </c>
       <c r="C124" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="E124" t="s">
         <v>20</v>
@@ -7119,7 +7107,7 @@
         <v>32</v>
       </c>
       <c r="I124" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J124" t="s">
         <v>244</v>
@@ -7134,13 +7122,13 @@
         <v>246</v>
       </c>
       <c r="O124" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="P124" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Q124" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
@@ -7151,7 +7139,7 @@
         <v>244</v>
       </c>
       <c r="C125" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="E125" t="s">
         <v>20</v>
@@ -7160,7 +7148,7 @@
         <v>32</v>
       </c>
       <c r="I125" t="s">
-        <v>224</v>
+        <v>122</v>
       </c>
       <c r="J125" t="s">
         <v>244</v>
@@ -7175,13 +7163,13 @@
         <v>246</v>
       </c>
       <c r="O125" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="P125" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="Q125" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
@@ -7189,10 +7177,10 @@
         <v>1</v>
       </c>
       <c r="B126" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C126" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="E126" t="s">
         <v>20</v>
@@ -7201,28 +7189,28 @@
         <v>32</v>
       </c>
       <c r="I126" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="J126" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="L126" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M126" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N126" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O126" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="P126" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="Q126" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
@@ -7233,7 +7221,7 @@
         <v>247</v>
       </c>
       <c r="C127" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E127" t="s">
         <v>20</v>
@@ -7242,7 +7230,7 @@
         <v>32</v>
       </c>
       <c r="I127" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J127" t="s">
         <v>247</v>
@@ -7257,13 +7245,13 @@
         <v>249</v>
       </c>
       <c r="O127" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P127" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q127" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
@@ -7274,7 +7262,7 @@
         <v>247</v>
       </c>
       <c r="C128" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="E128" t="s">
         <v>20</v>
@@ -7283,7 +7271,7 @@
         <v>32</v>
       </c>
       <c r="I128" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J128" t="s">
         <v>247</v>
@@ -7298,13 +7286,13 @@
         <v>249</v>
       </c>
       <c r="O128" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="P128" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Q128" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
@@ -7315,7 +7303,7 @@
         <v>247</v>
       </c>
       <c r="C129" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="E129" t="s">
         <v>20</v>
@@ -7324,7 +7312,7 @@
         <v>32</v>
       </c>
       <c r="I129" t="s">
-        <v>224</v>
+        <v>122</v>
       </c>
       <c r="J129" t="s">
         <v>247</v>
@@ -7339,13 +7327,13 @@
         <v>249</v>
       </c>
       <c r="O129" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="P129" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="Q129" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
@@ -7353,10 +7341,10 @@
         <v>1</v>
       </c>
       <c r="B130" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C130" t="s">
-        <v>65</v>
+        <v>163</v>
       </c>
       <c r="E130" t="s">
         <v>20</v>
@@ -7365,28 +7353,28 @@
         <v>32</v>
       </c>
       <c r="I130" t="s">
-        <v>91</v>
+        <v>224</v>
       </c>
       <c r="J130" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L130" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="M130" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="N130" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="O130" t="s">
-        <v>70</v>
+        <v>164</v>
       </c>
       <c r="P130" t="s">
-        <v>71</v>
+        <v>165</v>
       </c>
       <c r="Q130" t="s">
-        <v>72</v>
+        <v>166</v>
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
@@ -7397,7 +7385,7 @@
         <v>250</v>
       </c>
       <c r="C131" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E131" t="s">
         <v>20</v>
@@ -7406,7 +7394,7 @@
         <v>32</v>
       </c>
       <c r="I131" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J131" t="s">
         <v>250</v>
@@ -7421,13 +7409,13 @@
         <v>252</v>
       </c>
       <c r="O131" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="P131" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="Q131" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
@@ -7438,7 +7426,7 @@
         <v>250</v>
       </c>
       <c r="C132" t="s">
-        <v>134</v>
+        <v>73</v>
       </c>
       <c r="E132" t="s">
         <v>20</v>
@@ -7447,7 +7435,7 @@
         <v>32</v>
       </c>
       <c r="I132" t="s">
-        <v>122</v>
+        <v>95</v>
       </c>
       <c r="J132" t="s">
         <v>250</v>
@@ -7462,13 +7450,13 @@
         <v>252</v>
       </c>
       <c r="O132" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="P132" t="s">
-        <v>124</v>
+        <v>75</v>
       </c>
       <c r="Q132" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
@@ -7479,7 +7467,7 @@
         <v>250</v>
       </c>
       <c r="C133" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="E133" t="s">
         <v>20</v>
@@ -7488,7 +7476,7 @@
         <v>32</v>
       </c>
       <c r="I133" t="s">
-        <v>224</v>
+        <v>122</v>
       </c>
       <c r="J133" t="s">
         <v>250</v>
@@ -7503,13 +7491,13 @@
         <v>252</v>
       </c>
       <c r="O133" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="P133" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="Q133" t="s">
-        <v>166</v>
+        <v>125</v>
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
@@ -7517,40 +7505,40 @@
         <v>1</v>
       </c>
       <c r="B134" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="C134" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
       <c r="E134" t="s">
         <v>20</v>
       </c>
       <c r="F134" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="I134" t="s">
-        <v>274</v>
+        <v>224</v>
       </c>
       <c r="J134" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="L134" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="M134" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="N134" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="O134" t="s">
-        <v>281</v>
+        <v>164</v>
       </c>
       <c r="P134" t="s">
-        <v>289</v>
+        <v>165</v>
       </c>
       <c r="Q134" t="s">
-        <v>285</v>
+        <v>166</v>
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
@@ -7561,7 +7549,7 @@
         <v>269</v>
       </c>
       <c r="C135" t="s">
-        <v>271</v>
+        <v>101</v>
       </c>
       <c r="E135" t="s">
         <v>20</v>
@@ -7570,7 +7558,7 @@
         <v>54</v>
       </c>
       <c r="I135" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="J135" t="s">
         <v>269</v>
@@ -7585,13 +7573,13 @@
         <v>280</v>
       </c>
       <c r="O135" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="P135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Q135" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
@@ -7602,7 +7590,7 @@
         <v>269</v>
       </c>
       <c r="C136" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E136" t="s">
         <v>20</v>
@@ -7611,7 +7599,7 @@
         <v>54</v>
       </c>
       <c r="I136" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J136" t="s">
         <v>269</v>
@@ -7626,13 +7614,13 @@
         <v>280</v>
       </c>
       <c r="O136" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="P136" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="Q136" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
@@ -7643,7 +7631,7 @@
         <v>269</v>
       </c>
       <c r="C137" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E137" t="s">
         <v>20</v>
@@ -7652,7 +7640,7 @@
         <v>54</v>
       </c>
       <c r="I137" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J137" t="s">
         <v>269</v>
@@ -7667,13 +7655,13 @@
         <v>280</v>
       </c>
       <c r="O137" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P137" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q137" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
@@ -7681,16 +7669,22 @@
         <v>1</v>
       </c>
       <c r="B138" t="s">
-        <v>270</v>
+        <v>269</v>
+      </c>
+      <c r="C138" t="s">
+        <v>273</v>
       </c>
       <c r="E138" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F138" t="s">
         <v>54</v>
       </c>
       <c r="I138" t="s">
-        <v>254</v>
+        <v>277</v>
+      </c>
+      <c r="J138" t="s">
+        <v>269</v>
       </c>
       <c r="L138" t="s">
         <v>278</v>
@@ -7701,46 +7695,40 @@
       <c r="N138" t="s">
         <v>280</v>
       </c>
+      <c r="O138" t="s">
+        <v>284</v>
+      </c>
+      <c r="P138" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1</v>
       </c>
       <c r="B139" t="s">
-        <v>458</v>
-      </c>
-      <c r="C139" t="s">
-        <v>459</v>
+        <v>270</v>
       </c>
       <c r="E139" t="s">
-        <v>460</v>
+        <v>47</v>
       </c>
       <c r="F139" t="s">
         <v>54</v>
       </c>
       <c r="I139" t="s">
-        <v>461</v>
-      </c>
-      <c r="J139" t="s">
-        <v>458</v>
+        <v>254</v>
       </c>
       <c r="L139" t="s">
-        <v>462</v>
+        <v>278</v>
       </c>
       <c r="M139" t="s">
-        <v>463</v>
+        <v>279</v>
       </c>
       <c r="N139" t="s">
-        <v>464</v>
-      </c>
-      <c r="O139" t="s">
-        <v>459</v>
-      </c>
-      <c r="P139" t="s">
-        <v>459</v>
-      </c>
-      <c r="Q139" t="s">
-        <v>459</v>
+        <v>280</v>
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
@@ -7751,7 +7739,7 @@
         <v>458</v>
       </c>
       <c r="C140" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="E140" t="s">
         <v>460</v>
@@ -7760,7 +7748,7 @@
         <v>54</v>
       </c>
       <c r="I140" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="J140" t="s">
         <v>458</v>
@@ -7775,13 +7763,13 @@
         <v>464</v>
       </c>
       <c r="O140" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="P140" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
       <c r="Q140" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
@@ -7792,7 +7780,7 @@
         <v>458</v>
       </c>
       <c r="C141" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E141" t="s">
         <v>460</v>
@@ -7801,7 +7789,7 @@
         <v>54</v>
       </c>
       <c r="I141" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="J141" t="s">
         <v>458</v>
@@ -7816,13 +7804,13 @@
         <v>464</v>
       </c>
       <c r="O141" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="P141" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="Q141" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
@@ -7833,7 +7821,7 @@
         <v>458</v>
       </c>
       <c r="C142" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E142" t="s">
         <v>460</v>
@@ -7842,7 +7830,7 @@
         <v>54</v>
       </c>
       <c r="I142" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="J142" t="s">
         <v>458</v>
@@ -7857,13 +7845,13 @@
         <v>464</v>
       </c>
       <c r="O142" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="P142" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="Q142" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
@@ -7874,7 +7862,7 @@
         <v>458</v>
       </c>
       <c r="C143" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E143" t="s">
         <v>460</v>
@@ -7883,7 +7871,7 @@
         <v>54</v>
       </c>
       <c r="I143" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J143" t="s">
         <v>458</v>
@@ -7898,13 +7886,13 @@
         <v>464</v>
       </c>
       <c r="O143" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="P143" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="Q143" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
@@ -7915,7 +7903,7 @@
         <v>458</v>
       </c>
       <c r="C144" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E144" t="s">
         <v>460</v>
@@ -7924,7 +7912,7 @@
         <v>54</v>
       </c>
       <c r="I144" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="J144" t="s">
         <v>458</v>
@@ -7939,13 +7927,13 @@
         <v>464</v>
       </c>
       <c r="O144" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="P144" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="Q144" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
@@ -7956,7 +7944,7 @@
         <v>458</v>
       </c>
       <c r="C145" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E145" t="s">
         <v>460</v>
@@ -7965,7 +7953,7 @@
         <v>54</v>
       </c>
       <c r="I145" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J145" t="s">
         <v>458</v>
@@ -7980,13 +7968,13 @@
         <v>464</v>
       </c>
       <c r="O145" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="P145" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="Q145" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
@@ -7997,7 +7985,7 @@
         <v>458</v>
       </c>
       <c r="C146" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E146" t="s">
         <v>460</v>
@@ -8006,7 +7994,7 @@
         <v>54</v>
       </c>
       <c r="I146" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J146" t="s">
         <v>458</v>
@@ -8021,13 +8009,13 @@
         <v>464</v>
       </c>
       <c r="O146" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="P146" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="Q146" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
@@ -8038,7 +8026,7 @@
         <v>458</v>
       </c>
       <c r="C147" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E147" t="s">
         <v>460</v>
@@ -8047,7 +8035,7 @@
         <v>54</v>
       </c>
       <c r="I147" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J147" t="s">
         <v>458</v>
@@ -8062,13 +8050,13 @@
         <v>464</v>
       </c>
       <c r="O147" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="P147" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="Q147" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
@@ -8079,7 +8067,7 @@
         <v>458</v>
       </c>
       <c r="C148" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="E148" t="s">
         <v>460</v>
@@ -8088,7 +8076,7 @@
         <v>54</v>
       </c>
       <c r="I148" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J148" t="s">
         <v>458</v>
@@ -8103,13 +8091,13 @@
         <v>464</v>
       </c>
       <c r="O148" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="P148" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="Q148" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
@@ -8120,7 +8108,7 @@
         <v>458</v>
       </c>
       <c r="C149" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E149" t="s">
         <v>460</v>
@@ -8129,7 +8117,7 @@
         <v>54</v>
       </c>
       <c r="I149" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J149" t="s">
         <v>458</v>
@@ -8144,13 +8132,13 @@
         <v>464</v>
       </c>
       <c r="O149" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="P149" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="Q149" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
@@ -8161,7 +8149,7 @@
         <v>458</v>
       </c>
       <c r="C150" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E150" t="s">
         <v>460</v>
@@ -8170,7 +8158,7 @@
         <v>54</v>
       </c>
       <c r="I150" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J150" t="s">
         <v>458</v>
@@ -8185,13 +8173,13 @@
         <v>464</v>
       </c>
       <c r="O150" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="P150" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="Q150" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
@@ -8202,7 +8190,7 @@
         <v>458</v>
       </c>
       <c r="C151" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E151" t="s">
         <v>460</v>
@@ -8211,7 +8199,7 @@
         <v>54</v>
       </c>
       <c r="I151" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="J151" t="s">
         <v>458</v>
@@ -8226,13 +8214,13 @@
         <v>464</v>
       </c>
       <c r="O151" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="P151" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="Q151" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
@@ -8243,7 +8231,7 @@
         <v>458</v>
       </c>
       <c r="C152" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E152" t="s">
         <v>460</v>
@@ -8252,7 +8240,7 @@
         <v>54</v>
       </c>
       <c r="I152" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J152" t="s">
         <v>458</v>
@@ -8267,13 +8255,13 @@
         <v>464</v>
       </c>
       <c r="O152" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="P152" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Q152" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
@@ -8284,7 +8272,7 @@
         <v>458</v>
       </c>
       <c r="C153" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E153" t="s">
         <v>460</v>
@@ -8293,7 +8281,7 @@
         <v>54</v>
       </c>
       <c r="I153" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="J153" t="s">
         <v>458</v>
@@ -8308,13 +8296,13 @@
         <v>464</v>
       </c>
       <c r="O153" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="P153" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="Q153" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
@@ -8325,7 +8313,7 @@
         <v>458</v>
       </c>
       <c r="C154" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E154" t="s">
         <v>460</v>
@@ -8334,7 +8322,7 @@
         <v>54</v>
       </c>
       <c r="I154" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="J154" t="s">
         <v>458</v>
@@ -8349,13 +8337,13 @@
         <v>464</v>
       </c>
       <c r="O154" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="P154" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="Q154" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
@@ -8366,7 +8354,7 @@
         <v>458</v>
       </c>
       <c r="C155" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E155" t="s">
         <v>460</v>
@@ -8375,7 +8363,7 @@
         <v>54</v>
       </c>
       <c r="I155" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="J155" t="s">
         <v>458</v>
@@ -8390,13 +8378,13 @@
         <v>464</v>
       </c>
       <c r="O155" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="P155" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="Q155" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
@@ -8407,7 +8395,7 @@
         <v>458</v>
       </c>
       <c r="C156" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E156" t="s">
         <v>460</v>
@@ -8416,7 +8404,7 @@
         <v>54</v>
       </c>
       <c r="I156" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J156" t="s">
         <v>458</v>
@@ -8431,13 +8419,13 @@
         <v>464</v>
       </c>
       <c r="O156" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="P156" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="Q156" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
@@ -8448,7 +8436,7 @@
         <v>458</v>
       </c>
       <c r="C157" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E157" t="s">
         <v>460</v>
@@ -8457,7 +8445,7 @@
         <v>54</v>
       </c>
       <c r="I157" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J157" t="s">
         <v>458</v>
@@ -8472,13 +8460,13 @@
         <v>464</v>
       </c>
       <c r="O157" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="P157" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="Q157" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
@@ -8489,7 +8477,7 @@
         <v>458</v>
       </c>
       <c r="C158" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E158" t="s">
         <v>460</v>
@@ -8498,7 +8486,7 @@
         <v>54</v>
       </c>
       <c r="I158" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="J158" t="s">
         <v>458</v>
@@ -8513,13 +8501,13 @@
         <v>464</v>
       </c>
       <c r="O158" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="P158" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="Q158" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
@@ -8530,7 +8518,7 @@
         <v>458</v>
       </c>
       <c r="C159" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E159" t="s">
         <v>460</v>
@@ -8539,7 +8527,7 @@
         <v>54</v>
       </c>
       <c r="I159" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J159" t="s">
         <v>458</v>
@@ -8554,13 +8542,13 @@
         <v>464</v>
       </c>
       <c r="O159" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="P159" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="Q159" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
@@ -8571,7 +8559,7 @@
         <v>458</v>
       </c>
       <c r="C160" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E160" t="s">
         <v>460</v>
@@ -8580,7 +8568,7 @@
         <v>54</v>
       </c>
       <c r="I160" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="J160" t="s">
         <v>458</v>
@@ -8595,13 +8583,13 @@
         <v>464</v>
       </c>
       <c r="O160" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="P160" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="Q160" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
@@ -8612,7 +8600,7 @@
         <v>458</v>
       </c>
       <c r="C161" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E161" t="s">
         <v>460</v>
@@ -8621,7 +8609,7 @@
         <v>54</v>
       </c>
       <c r="I161" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J161" t="s">
         <v>458</v>
@@ -8636,13 +8624,13 @@
         <v>464</v>
       </c>
       <c r="O161" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="P161" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="Q161" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
@@ -8653,7 +8641,7 @@
         <v>458</v>
       </c>
       <c r="C162" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E162" t="s">
         <v>460</v>
@@ -8662,7 +8650,7 @@
         <v>54</v>
       </c>
       <c r="I162" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="J162" t="s">
         <v>458</v>
@@ -8677,13 +8665,13 @@
         <v>464</v>
       </c>
       <c r="O162" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="P162" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="Q162" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
@@ -8694,7 +8682,7 @@
         <v>458</v>
       </c>
       <c r="C163" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E163" t="s">
         <v>460</v>
@@ -8703,7 +8691,7 @@
         <v>54</v>
       </c>
       <c r="I163" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="J163" t="s">
         <v>458</v>
@@ -8718,13 +8706,13 @@
         <v>464</v>
       </c>
       <c r="O163" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="P163" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="Q163" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
@@ -8732,10 +8720,10 @@
         <v>1</v>
       </c>
       <c r="B164" t="s">
-        <v>513</v>
+        <v>458</v>
       </c>
       <c r="C164" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E164" t="s">
         <v>460</v>
@@ -8744,28 +8732,28 @@
         <v>54</v>
       </c>
       <c r="I164" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="J164" t="s">
-        <v>513</v>
+        <v>458</v>
       </c>
       <c r="L164" t="s">
-        <v>516</v>
+        <v>462</v>
       </c>
       <c r="M164" t="s">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="N164" t="s">
-        <v>518</v>
+        <v>464</v>
       </c>
       <c r="O164" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="P164" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="Q164" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
@@ -8776,7 +8764,7 @@
         <v>513</v>
       </c>
       <c r="C165" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="E165" t="s">
         <v>460</v>
@@ -8785,7 +8773,7 @@
         <v>54</v>
       </c>
       <c r="I165" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="J165" t="s">
         <v>513</v>
@@ -8800,13 +8788,13 @@
         <v>518</v>
       </c>
       <c r="O165" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="P165" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="Q165" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
@@ -8817,7 +8805,7 @@
         <v>513</v>
       </c>
       <c r="C166" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E166" t="s">
         <v>460</v>
@@ -8826,7 +8814,7 @@
         <v>54</v>
       </c>
       <c r="I166" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J166" t="s">
         <v>513</v>
@@ -8841,13 +8829,13 @@
         <v>518</v>
       </c>
       <c r="O166" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="P166" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="Q166" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
@@ -8858,7 +8846,7 @@
         <v>513</v>
       </c>
       <c r="C167" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E167" t="s">
         <v>460</v>
@@ -8867,7 +8855,7 @@
         <v>54</v>
       </c>
       <c r="I167" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="J167" t="s">
         <v>513</v>
@@ -8882,13 +8870,13 @@
         <v>518</v>
       </c>
       <c r="O167" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="P167" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="Q167" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
@@ -8899,7 +8887,7 @@
         <v>513</v>
       </c>
       <c r="C168" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E168" t="s">
         <v>460</v>
@@ -8908,7 +8896,7 @@
         <v>54</v>
       </c>
       <c r="I168" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="J168" t="s">
         <v>513</v>
@@ -8923,13 +8911,13 @@
         <v>518</v>
       </c>
       <c r="O168" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P168" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="Q168" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
@@ -8940,7 +8928,7 @@
         <v>513</v>
       </c>
       <c r="C169" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E169" t="s">
         <v>460</v>
@@ -8949,7 +8937,7 @@
         <v>54</v>
       </c>
       <c r="I169" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="J169" t="s">
         <v>513</v>
@@ -8964,13 +8952,13 @@
         <v>518</v>
       </c>
       <c r="O169" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="P169" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="Q169" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
@@ -8981,7 +8969,7 @@
         <v>513</v>
       </c>
       <c r="C170" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E170" t="s">
         <v>460</v>
@@ -8990,7 +8978,7 @@
         <v>54</v>
       </c>
       <c r="I170" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="J170" t="s">
         <v>513</v>
@@ -9005,13 +8993,13 @@
         <v>518</v>
       </c>
       <c r="O170" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="P170" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="Q170" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
@@ -9022,7 +9010,7 @@
         <v>513</v>
       </c>
       <c r="C171" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E171" t="s">
         <v>460</v>
@@ -9031,7 +9019,7 @@
         <v>54</v>
       </c>
       <c r="I171" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J171" t="s">
         <v>513</v>
@@ -9046,13 +9034,13 @@
         <v>518</v>
       </c>
       <c r="O171" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="P171" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q171" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
@@ -9063,7 +9051,7 @@
         <v>513</v>
       </c>
       <c r="C172" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E172" t="s">
         <v>460</v>
@@ -9072,7 +9060,7 @@
         <v>54</v>
       </c>
       <c r="I172" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="J172" t="s">
         <v>513</v>
@@ -9087,13 +9075,13 @@
         <v>518</v>
       </c>
       <c r="O172" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="P172" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Q172" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
@@ -9104,7 +9092,7 @@
         <v>513</v>
       </c>
       <c r="C173" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E173" t="s">
         <v>460</v>
@@ -9113,7 +9101,7 @@
         <v>54</v>
       </c>
       <c r="I173" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="J173" t="s">
         <v>513</v>
@@ -9128,177 +9116,218 @@
         <v>518</v>
       </c>
       <c r="O173" t="s">
+        <v>533</v>
+      </c>
+      <c r="P173" t="s">
+        <v>533</v>
+      </c>
+      <c r="Q173" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>1</v>
+      </c>
+      <c r="B174" t="s">
+        <v>513</v>
+      </c>
+      <c r="C174" t="s">
         <v>535</v>
       </c>
-      <c r="P173" t="s">
+      <c r="E174" t="s">
+        <v>460</v>
+      </c>
+      <c r="F174" t="s">
+        <v>54</v>
+      </c>
+      <c r="I174" t="s">
+        <v>536</v>
+      </c>
+      <c r="J174" t="s">
+        <v>513</v>
+      </c>
+      <c r="L174" t="s">
+        <v>516</v>
+      </c>
+      <c r="M174" t="s">
+        <v>517</v>
+      </c>
+      <c r="N174" t="s">
+        <v>518</v>
+      </c>
+      <c r="O174" t="s">
         <v>535</v>
       </c>
-      <c r="Q173" t="s">
+      <c r="P174" t="s">
         <v>535</v>
       </c>
+      <c r="Q174" t="s">
+        <v>535</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B29">
+  <conditionalFormatting sqref="B29:B30">
     <cfRule type="duplicateValues" dxfId="53" priority="54"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B40:B53 B26:B28">
+  <conditionalFormatting sqref="B41:B54 B26:B28">
     <cfRule type="duplicateValues" dxfId="52" priority="56"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B65">
+  <conditionalFormatting sqref="B66">
     <cfRule type="duplicateValues" dxfId="51" priority="52"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
+  <conditionalFormatting sqref="B67">
     <cfRule type="duplicateValues" dxfId="50" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B67">
+  <conditionalFormatting sqref="B68">
     <cfRule type="duplicateValues" dxfId="49" priority="50"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B68:B78">
+  <conditionalFormatting sqref="B69:B79">
     <cfRule type="duplicateValues" dxfId="48" priority="49"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B79">
+  <conditionalFormatting sqref="B80">
     <cfRule type="duplicateValues" dxfId="47" priority="47"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B80:B90 B132:B138 B31:B39 B174">
+  <conditionalFormatting sqref="B81:B91 B133:B139 B32:B40 B175">
     <cfRule type="duplicateValues" dxfId="46" priority="39"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B91:B100">
+  <conditionalFormatting sqref="B92:B101">
     <cfRule type="duplicateValues" dxfId="45" priority="33"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B101">
+  <conditionalFormatting sqref="B102">
     <cfRule type="duplicateValues" dxfId="44" priority="32"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B102:B133">
+  <conditionalFormatting sqref="B103:B134">
     <cfRule type="duplicateValues" dxfId="43" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C26:C28">
     <cfRule type="duplicateValues" dxfId="42" priority="55"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C58:C62">
+  <conditionalFormatting sqref="C59:C63">
     <cfRule type="duplicateValues" dxfId="41" priority="53"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C68:C78">
+  <conditionalFormatting sqref="C69:C79">
     <cfRule type="duplicateValues" dxfId="40" priority="48"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C88:C89">
+  <conditionalFormatting sqref="C89:C90">
     <cfRule type="duplicateValues" dxfId="39" priority="38"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C91:C100">
+  <conditionalFormatting sqref="C92:C101">
     <cfRule type="duplicateValues" dxfId="38" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H42">
-    <cfRule type="duplicateValues" dxfId="37" priority="11"/>
+  <conditionalFormatting sqref="C140 C142">
+    <cfRule type="duplicateValues" dxfId="37" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H43">
-    <cfRule type="duplicateValues" dxfId="36" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H44">
-    <cfRule type="duplicateValues" dxfId="35" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H45">
-    <cfRule type="duplicateValues" dxfId="34" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H46">
-    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="8"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H47">
-    <cfRule type="duplicateValues" dxfId="32" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H79">
-    <cfRule type="duplicateValues" dxfId="31" priority="46"/>
+  <conditionalFormatting sqref="H48">
+    <cfRule type="duplicateValues" dxfId="31" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H90:H100 H102:H138 H31:H39 H174">
-    <cfRule type="duplicateValues" dxfId="30" priority="36"/>
+  <conditionalFormatting sqref="H80">
+    <cfRule type="duplicateValues" dxfId="30" priority="46"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H101">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+  <conditionalFormatting sqref="H91:H101 H103:H139 H32:H40 H175">
+    <cfRule type="duplicateValues" dxfId="29" priority="36"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I59:I61">
-    <cfRule type="duplicateValues" dxfId="28" priority="40"/>
+  <conditionalFormatting sqref="H102">
+    <cfRule type="duplicateValues" dxfId="28" priority="30"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I68:I78">
-    <cfRule type="duplicateValues" dxfId="27" priority="45"/>
+  <conditionalFormatting sqref="I60:I62">
+    <cfRule type="duplicateValues" dxfId="27" priority="40"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I89">
-    <cfRule type="duplicateValues" dxfId="26" priority="37"/>
+  <conditionalFormatting sqref="I69:I79">
+    <cfRule type="duplicateValues" dxfId="26" priority="45"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I91:I98 I100">
-    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+  <conditionalFormatting sqref="I90">
+    <cfRule type="duplicateValues" dxfId="25" priority="37"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I99">
-    <cfRule type="duplicateValues" dxfId="24" priority="26"/>
+  <conditionalFormatting sqref="I92:I99 I101">
+    <cfRule type="duplicateValues" dxfId="24" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I105">
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
+  <conditionalFormatting sqref="I100">
+    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I109">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
+  <conditionalFormatting sqref="I106">
+    <cfRule type="duplicateValues" dxfId="22" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I113">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
+  <conditionalFormatting sqref="I110">
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I117">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
+  <conditionalFormatting sqref="I114">
+    <cfRule type="duplicateValues" dxfId="20" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I121">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
+  <conditionalFormatting sqref="I118">
+    <cfRule type="duplicateValues" dxfId="19" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I125">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+  <conditionalFormatting sqref="I122">
+    <cfRule type="duplicateValues" dxfId="18" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I129">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
+  <conditionalFormatting sqref="I126">
+    <cfRule type="duplicateValues" dxfId="17" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I133">
-    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+  <conditionalFormatting sqref="I130">
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J31:J36">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+  <conditionalFormatting sqref="I134">
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J37:J39">
-    <cfRule type="duplicateValues" dxfId="14" priority="12"/>
+  <conditionalFormatting sqref="I140 I142">
+    <cfRule type="duplicateValues" dxfId="14" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J40:J53">
-    <cfRule type="duplicateValues" dxfId="13" priority="3"/>
+  <conditionalFormatting sqref="J32:J37">
+    <cfRule type="duplicateValues" dxfId="13" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J65">
-    <cfRule type="duplicateValues" dxfId="12" priority="43"/>
+  <conditionalFormatting sqref="J38:J40">
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J41:J54">
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J66">
-    <cfRule type="duplicateValues" dxfId="11" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="43"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J67">
-    <cfRule type="duplicateValues" dxfId="10" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="42"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J68:J78">
-    <cfRule type="duplicateValues" dxfId="9" priority="44"/>
+  <conditionalFormatting sqref="J68">
+    <cfRule type="duplicateValues" dxfId="8" priority="41"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J80:J89">
-    <cfRule type="duplicateValues" dxfId="8" priority="34"/>
+  <conditionalFormatting sqref="J69:J79">
+    <cfRule type="duplicateValues" dxfId="7" priority="44"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J91:J100">
-    <cfRule type="duplicateValues" dxfId="7" priority="27"/>
+  <conditionalFormatting sqref="J81:J90">
+    <cfRule type="duplicateValues" dxfId="6" priority="34"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J101">
-    <cfRule type="duplicateValues" dxfId="6" priority="29"/>
+  <conditionalFormatting sqref="J92:J101">
+    <cfRule type="duplicateValues" dxfId="5" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J102:J133">
-    <cfRule type="duplicateValues" dxfId="5" priority="14"/>
+  <conditionalFormatting sqref="J102">
+    <cfRule type="duplicateValues" dxfId="4" priority="29"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J132:J133">
-    <cfRule type="duplicateValues" dxfId="4" priority="15"/>
+  <conditionalFormatting sqref="J103:J134">
+    <cfRule type="duplicateValues" dxfId="3" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J134:J137">
-    <cfRule type="duplicateValues" dxfId="3" priority="68"/>
+  <conditionalFormatting sqref="J133:J134">
+    <cfRule type="duplicateValues" dxfId="2" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J138 J90 J174">
-    <cfRule type="duplicateValues" dxfId="2" priority="35"/>
+  <conditionalFormatting sqref="J135:J138">
+    <cfRule type="duplicateValues" dxfId="1" priority="68"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C139 C141">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I139 I141">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="J139 J91 J175">
+    <cfRule type="duplicateValues" dxfId="0" priority="35"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
